--- a/engineering/drainage-design/retention_volume/Volume_Retention_Deux_Zones_1500_900_1200.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Deux_Zones_1500_900_1200.xlsx
@@ -2024,6 +2024,21 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Inclure V_ditch trapèze? (1=oui, 0=levé seul)</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0 = recommandé si SS_Amont contient déjà le fossé (V=levé seul; Q_overflow garde b,z,L,n,S). 1 = ajoute V_ditch = A_trapèze × L (ancien mode — risque de double volume).</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
@@ -2107,7 +2122,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Longueur pour V_ditch = A × L et Manning</t>
+          <t>L pour Manning Q_overflow (et V_ditch seulement si B25=1)</t>
         </is>
       </c>
     </row>
@@ -2134,14 +2149,13 @@
           <t>Stockage_C (volume)</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>V_pond(levé) + V_ditch</t>
-        </is>
+      <c r="B34">
+        <f>IF(B25=1,"V_pond(levé)+V_ditch","V_pond(levé) seul")</f>
+        <v/>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Volume = bassin (levé) + fossé — Compose_900 + Calcul_C</t>
+          <t>Piloté par B25 — pas de double comptage si le fossé est déjà dans SS_Amont</t>
         </is>
       </c>
     </row>
@@ -2303,17 +2317,16 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Vmax_C (m³) = max(V_pond + V_ditch)</t>
+          <t>Vmax_C (m³) = max(V_total)</t>
         </is>
       </c>
       <c r="B49" s="20">
         <f>Calcul_C!B7</f>
         <v/>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Stockage total routé (levé + fossé)</t>
-        </is>
+      <c r="C49">
+        <f>IF(B25=1,"V_pond+V_ditch (B25=1)","V_pond seul — levé SS_Amont (B25=0)")</f>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -2431,7 +2444,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2) C (Zone 1): Qout = Q_900(WSE)+Q_overflow; V = V_pond(SS_Amont)+V_ditch; WSEmax_C = Calcul_C.</t>
+          <t>2) C (Zone 1): Qout = Q_900+Q_overflow; V = SS_Amont (+V_ditch si B25=1); WSEmax_C = Calcul_C.</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2549,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>• Méthode C: Qout = Q_900 + Q_overflow; V = V_pond + V_ditch — Compose_900 + Calcul_C (B49–B52).</t>
+          <t>• Méthode C: Qout = Q_900 + Q_overflow; V_ditch via B25 (0=levé seul) — Compose_900 + Calcul_C (B49–B52).</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3730,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   C) Qout = Q_900(WSE) + Q_overflow(WSE); V = V_pond + V_ditch → Compose_900 + Calcul_C.</t>
+          <t xml:space="preserve">   C) Qout = Q_900 + Q_overflow; V = V_pond (+ V_ditch si B25=1) → Compose_900 + Calcul_C.</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7129,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Qout = Q_900(WSE) + Q_overflow(WSE). V_total = V_pond(SS_Amont) + V_ditch. Overflow: trapèze au-dessus du crown, Manning. Paramètres jaunes = Parametres!B27–B32.</t>
+          <t>Qout = Q_900(WSE) + Q_overflow(WSE). V_total = V_pond(SS_Amont) + (B25)*V_ditch. Qout = Q_900 + Q_overflow (trapèze Manning) toujours. B25=0 → pas de volume trapèze (levé seul). Paramètres = Parametres!B25–B32.</t>
         </is>
       </c>
     </row>
@@ -7205,6 +7218,17 @@
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Inclure V_ditch (0/1)</t>
+        </is>
+      </c>
+      <c r="B13" s="17">
+        <f>Parametres!B25</f>
+        <v/>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -7279,7 +7303,7 @@
         <v/>
       </c>
       <c r="E15" s="26">
-        <f>D15*$B$11</f>
+        <f>IF($B$13=1,D15*$B$11,0)</f>
         <v/>
       </c>
       <c r="F15" s="26">
@@ -7287,7 +7311,7 @@
         <v/>
       </c>
       <c r="G15" s="34">
-        <f>E15+F15</f>
+        <f>F15+E15</f>
         <v/>
       </c>
       <c r="H15" s="5">
@@ -7324,7 +7348,7 @@
         <v/>
       </c>
       <c r="E16" s="26">
-        <f>D16*$B$11</f>
+        <f>IF($B$13=1,D16*$B$11,0)</f>
         <v/>
       </c>
       <c r="F16" s="26">
@@ -7332,7 +7356,7 @@
         <v/>
       </c>
       <c r="G16" s="34">
-        <f>E16+F16</f>
+        <f>F16+E16</f>
         <v/>
       </c>
       <c r="H16" s="5">
@@ -7369,7 +7393,7 @@
         <v/>
       </c>
       <c r="E17" s="26">
-        <f>D17*$B$11</f>
+        <f>IF($B$13=1,D17*$B$11,0)</f>
         <v/>
       </c>
       <c r="F17" s="26">
@@ -7377,7 +7401,7 @@
         <v/>
       </c>
       <c r="G17" s="34">
-        <f>E17+F17</f>
+        <f>F17+E17</f>
         <v/>
       </c>
       <c r="H17" s="5">
@@ -7414,7 +7438,7 @@
         <v/>
       </c>
       <c r="E18" s="26">
-        <f>D18*$B$11</f>
+        <f>IF($B$13=1,D18*$B$11,0)</f>
         <v/>
       </c>
       <c r="F18" s="26">
@@ -7422,7 +7446,7 @@
         <v/>
       </c>
       <c r="G18" s="34">
-        <f>E18+F18</f>
+        <f>F18+E18</f>
         <v/>
       </c>
       <c r="H18" s="5">
@@ -7459,7 +7483,7 @@
         <v/>
       </c>
       <c r="E19" s="26">
-        <f>D19*$B$11</f>
+        <f>IF($B$13=1,D19*$B$11,0)</f>
         <v/>
       </c>
       <c r="F19" s="26">
@@ -7467,7 +7491,7 @@
         <v/>
       </c>
       <c r="G19" s="34">
-        <f>E19+F19</f>
+        <f>F19+E19</f>
         <v/>
       </c>
       <c r="H19" s="5">
@@ -7504,7 +7528,7 @@
         <v/>
       </c>
       <c r="E20" s="26">
-        <f>D20*$B$11</f>
+        <f>IF($B$13=1,D20*$B$11,0)</f>
         <v/>
       </c>
       <c r="F20" s="26">
@@ -7512,7 +7536,7 @@
         <v/>
       </c>
       <c r="G20" s="34">
-        <f>E20+F20</f>
+        <f>F20+E20</f>
         <v/>
       </c>
       <c r="H20" s="5">
@@ -7549,7 +7573,7 @@
         <v/>
       </c>
       <c r="E21" s="26">
-        <f>D21*$B$11</f>
+        <f>IF($B$13=1,D21*$B$11,0)</f>
         <v/>
       </c>
       <c r="F21" s="26">
@@ -7557,7 +7581,7 @@
         <v/>
       </c>
       <c r="G21" s="34">
-        <f>E21+F21</f>
+        <f>F21+E21</f>
         <v/>
       </c>
       <c r="H21" s="5">
@@ -7594,7 +7618,7 @@
         <v/>
       </c>
       <c r="E22" s="26">
-        <f>D22*$B$11</f>
+        <f>IF($B$13=1,D22*$B$11,0)</f>
         <v/>
       </c>
       <c r="F22" s="26">
@@ -7602,7 +7626,7 @@
         <v/>
       </c>
       <c r="G22" s="34">
-        <f>E22+F22</f>
+        <f>F22+E22</f>
         <v/>
       </c>
       <c r="H22" s="5">
@@ -7639,7 +7663,7 @@
         <v/>
       </c>
       <c r="E23" s="26">
-        <f>D23*$B$11</f>
+        <f>IF($B$13=1,D23*$B$11,0)</f>
         <v/>
       </c>
       <c r="F23" s="26">
@@ -7647,7 +7671,7 @@
         <v/>
       </c>
       <c r="G23" s="34">
-        <f>E23+F23</f>
+        <f>F23+E23</f>
         <v/>
       </c>
       <c r="H23" s="5">
@@ -7684,7 +7708,7 @@
         <v/>
       </c>
       <c r="E24" s="26">
-        <f>D24*$B$11</f>
+        <f>IF($B$13=1,D24*$B$11,0)</f>
         <v/>
       </c>
       <c r="F24" s="26">
@@ -7692,7 +7716,7 @@
         <v/>
       </c>
       <c r="G24" s="34">
-        <f>E24+F24</f>
+        <f>F24+E24</f>
         <v/>
       </c>
       <c r="H24" s="5">
@@ -7729,7 +7753,7 @@
         <v/>
       </c>
       <c r="E25" s="26">
-        <f>D25*$B$11</f>
+        <f>IF($B$13=1,D25*$B$11,0)</f>
         <v/>
       </c>
       <c r="F25" s="26">
@@ -7737,7 +7761,7 @@
         <v/>
       </c>
       <c r="G25" s="34">
-        <f>E25+F25</f>
+        <f>F25+E25</f>
         <v/>
       </c>
       <c r="H25" s="5">
@@ -7774,7 +7798,7 @@
         <v/>
       </c>
       <c r="E26" s="26">
-        <f>D26*$B$11</f>
+        <f>IF($B$13=1,D26*$B$11,0)</f>
         <v/>
       </c>
       <c r="F26" s="26">
@@ -7782,7 +7806,7 @@
         <v/>
       </c>
       <c r="G26" s="34">
-        <f>E26+F26</f>
+        <f>F26+E26</f>
         <v/>
       </c>
       <c r="H26" s="5">
@@ -7819,7 +7843,7 @@
         <v/>
       </c>
       <c r="E27" s="26">
-        <f>D27*$B$11</f>
+        <f>IF($B$13=1,D27*$B$11,0)</f>
         <v/>
       </c>
       <c r="F27" s="26">
@@ -7827,7 +7851,7 @@
         <v/>
       </c>
       <c r="G27" s="34">
-        <f>E27+F27</f>
+        <f>F27+E27</f>
         <v/>
       </c>
       <c r="H27" s="5">
@@ -7864,7 +7888,7 @@
         <v/>
       </c>
       <c r="E28" s="26">
-        <f>D28*$B$11</f>
+        <f>IF($B$13=1,D28*$B$11,0)</f>
         <v/>
       </c>
       <c r="F28" s="26">
@@ -7872,7 +7896,7 @@
         <v/>
       </c>
       <c r="G28" s="34">
-        <f>E28+F28</f>
+        <f>F28+E28</f>
         <v/>
       </c>
       <c r="H28" s="5">
@@ -7909,7 +7933,7 @@
         <v/>
       </c>
       <c r="E29" s="26">
-        <f>D29*$B$11</f>
+        <f>IF($B$13=1,D29*$B$11,0)</f>
         <v/>
       </c>
       <c r="F29" s="26">
@@ -7917,7 +7941,7 @@
         <v/>
       </c>
       <c r="G29" s="34">
-        <f>E29+F29</f>
+        <f>F29+E29</f>
         <v/>
       </c>
       <c r="H29" s="5">
@@ -7954,7 +7978,7 @@
         <v/>
       </c>
       <c r="E30" s="26">
-        <f>D30*$B$11</f>
+        <f>IF($B$13=1,D30*$B$11,0)</f>
         <v/>
       </c>
       <c r="F30" s="26">
@@ -7962,7 +7986,7 @@
         <v/>
       </c>
       <c r="G30" s="34">
-        <f>E30+F30</f>
+        <f>F30+E30</f>
         <v/>
       </c>
       <c r="H30" s="5">
@@ -7999,7 +8023,7 @@
         <v/>
       </c>
       <c r="E31" s="26">
-        <f>D31*$B$11</f>
+        <f>IF($B$13=1,D31*$B$11,0)</f>
         <v/>
       </c>
       <c r="F31" s="26">
@@ -8007,7 +8031,7 @@
         <v/>
       </c>
       <c r="G31" s="34">
-        <f>E31+F31</f>
+        <f>F31+E31</f>
         <v/>
       </c>
       <c r="H31" s="5">
@@ -8044,7 +8068,7 @@
         <v/>
       </c>
       <c r="E32" s="26">
-        <f>D32*$B$11</f>
+        <f>IF($B$13=1,D32*$B$11,0)</f>
         <v/>
       </c>
       <c r="F32" s="26">
@@ -8052,7 +8076,7 @@
         <v/>
       </c>
       <c r="G32" s="34">
-        <f>E32+F32</f>
+        <f>F32+E32</f>
         <v/>
       </c>
       <c r="H32" s="5">
@@ -8089,7 +8113,7 @@
         <v/>
       </c>
       <c r="E33" s="42">
-        <f>D33*$B$11</f>
+        <f>IF($B$13=1,D33*$B$11,0)</f>
         <v/>
       </c>
       <c r="F33" s="42">
@@ -8097,7 +8121,7 @@
         <v/>
       </c>
       <c r="G33" s="34">
-        <f>E33+F33</f>
+        <f>F33+E33</f>
         <v/>
       </c>
       <c r="H33" s="8">
@@ -8134,7 +8158,7 @@
         <v/>
       </c>
       <c r="E34" s="26">
-        <f>D34*$B$11</f>
+        <f>IF($B$13=1,D34*$B$11,0)</f>
         <v/>
       </c>
       <c r="F34" s="26">
@@ -8142,7 +8166,7 @@
         <v/>
       </c>
       <c r="G34" s="34">
-        <f>E34+F34</f>
+        <f>F34+E34</f>
         <v/>
       </c>
       <c r="H34" s="5">
@@ -8179,7 +8203,7 @@
         <v/>
       </c>
       <c r="E35" s="26">
-        <f>D35*$B$11</f>
+        <f>IF($B$13=1,D35*$B$11,0)</f>
         <v/>
       </c>
       <c r="F35" s="26">
@@ -8187,7 +8211,7 @@
         <v/>
       </c>
       <c r="G35" s="34">
-        <f>E35+F35</f>
+        <f>F35+E35</f>
         <v/>
       </c>
       <c r="H35" s="5">
@@ -8224,7 +8248,7 @@
         <v/>
       </c>
       <c r="E36" s="26">
-        <f>D36*$B$11</f>
+        <f>IF($B$13=1,D36*$B$11,0)</f>
         <v/>
       </c>
       <c r="F36" s="26">
@@ -8232,7 +8256,7 @@
         <v/>
       </c>
       <c r="G36" s="34">
-        <f>E36+F36</f>
+        <f>F36+E36</f>
         <v/>
       </c>
       <c r="H36" s="5">
@@ -8269,7 +8293,7 @@
         <v/>
       </c>
       <c r="E37" s="26">
-        <f>D37*$B$11</f>
+        <f>IF($B$13=1,D37*$B$11,0)</f>
         <v/>
       </c>
       <c r="F37" s="26">
@@ -8277,7 +8301,7 @@
         <v/>
       </c>
       <c r="G37" s="34">
-        <f>E37+F37</f>
+        <f>F37+E37</f>
         <v/>
       </c>
       <c r="H37" s="5">
@@ -8314,7 +8338,7 @@
         <v/>
       </c>
       <c r="E38" s="26">
-        <f>D38*$B$11</f>
+        <f>IF($B$13=1,D38*$B$11,0)</f>
         <v/>
       </c>
       <c r="F38" s="26">
@@ -8322,7 +8346,7 @@
         <v/>
       </c>
       <c r="G38" s="34">
-        <f>E38+F38</f>
+        <f>F38+E38</f>
         <v/>
       </c>
       <c r="H38" s="5">
@@ -8359,7 +8383,7 @@
         <v/>
       </c>
       <c r="E39" s="26">
-        <f>D39*$B$11</f>
+        <f>IF($B$13=1,D39*$B$11,0)</f>
         <v/>
       </c>
       <c r="F39" s="26">
@@ -8367,7 +8391,7 @@
         <v/>
       </c>
       <c r="G39" s="34">
-        <f>E39+F39</f>
+        <f>F39+E39</f>
         <v/>
       </c>
       <c r="H39" s="5">
@@ -8404,7 +8428,7 @@
         <v/>
       </c>
       <c r="E40" s="26">
-        <f>D40*$B$11</f>
+        <f>IF($B$13=1,D40*$B$11,0)</f>
         <v/>
       </c>
       <c r="F40" s="26">
@@ -8412,7 +8436,7 @@
         <v/>
       </c>
       <c r="G40" s="34">
-        <f>E40+F40</f>
+        <f>F40+E40</f>
         <v/>
       </c>
       <c r="H40" s="5">
@@ -8449,7 +8473,7 @@
         <v/>
       </c>
       <c r="E41" s="26">
-        <f>D41*$B$11</f>
+        <f>IF($B$13=1,D41*$B$11,0)</f>
         <v/>
       </c>
       <c r="F41" s="26">
@@ -8457,7 +8481,7 @@
         <v/>
       </c>
       <c r="G41" s="34">
-        <f>E41+F41</f>
+        <f>F41+E41</f>
         <v/>
       </c>
       <c r="H41" s="5">
@@ -8494,7 +8518,7 @@
         <v/>
       </c>
       <c r="E42" s="26">
-        <f>D42*$B$11</f>
+        <f>IF($B$13=1,D42*$B$11,0)</f>
         <v/>
       </c>
       <c r="F42" s="26">
@@ -8502,7 +8526,7 @@
         <v/>
       </c>
       <c r="G42" s="34">
-        <f>E42+F42</f>
+        <f>F42+E42</f>
         <v/>
       </c>
       <c r="H42" s="5">
@@ -8539,7 +8563,7 @@
         <v/>
       </c>
       <c r="E43" s="26">
-        <f>D43*$B$11</f>
+        <f>IF($B$13=1,D43*$B$11,0)</f>
         <v/>
       </c>
       <c r="F43" s="26">
@@ -8547,7 +8571,7 @@
         <v/>
       </c>
       <c r="G43" s="34">
-        <f>E43+F43</f>
+        <f>F43+E43</f>
         <v/>
       </c>
       <c r="H43" s="5">
@@ -8584,7 +8608,7 @@
         <v/>
       </c>
       <c r="E44" s="26">
-        <f>D44*$B$11</f>
+        <f>IF($B$13=1,D44*$B$11,0)</f>
         <v/>
       </c>
       <c r="F44" s="26">
@@ -8592,7 +8616,7 @@
         <v/>
       </c>
       <c r="G44" s="34">
-        <f>E44+F44</f>
+        <f>F44+E44</f>
         <v/>
       </c>
       <c r="H44" s="5">
@@ -8629,7 +8653,7 @@
         <v/>
       </c>
       <c r="E45" s="26">
-        <f>D45*$B$11</f>
+        <f>IF($B$13=1,D45*$B$11,0)</f>
         <v/>
       </c>
       <c r="F45" s="26">
@@ -8637,7 +8661,7 @@
         <v/>
       </c>
       <c r="G45" s="34">
-        <f>E45+F45</f>
+        <f>F45+E45</f>
         <v/>
       </c>
       <c r="H45" s="5">
@@ -8674,7 +8698,7 @@
         <v/>
       </c>
       <c r="E46" s="26">
-        <f>D46*$B$11</f>
+        <f>IF($B$13=1,D46*$B$11,0)</f>
         <v/>
       </c>
       <c r="F46" s="26">
@@ -8682,7 +8706,7 @@
         <v/>
       </c>
       <c r="G46" s="34">
-        <f>E46+F46</f>
+        <f>F46+E46</f>
         <v/>
       </c>
       <c r="H46" s="5">
@@ -8719,7 +8743,7 @@
         <v/>
       </c>
       <c r="E47" s="26">
-        <f>D47*$B$11</f>
+        <f>IF($B$13=1,D47*$B$11,0)</f>
         <v/>
       </c>
       <c r="F47" s="26">
@@ -8727,7 +8751,7 @@
         <v/>
       </c>
       <c r="G47" s="34">
-        <f>E47+F47</f>
+        <f>F47+E47</f>
         <v/>
       </c>
       <c r="H47" s="5">
@@ -8764,7 +8788,7 @@
         <v/>
       </c>
       <c r="E48" s="26">
-        <f>D48*$B$11</f>
+        <f>IF($B$13=1,D48*$B$11,0)</f>
         <v/>
       </c>
       <c r="F48" s="26">
@@ -8772,7 +8796,7 @@
         <v/>
       </c>
       <c r="G48" s="34">
-        <f>E48+F48</f>
+        <f>F48+E48</f>
         <v/>
       </c>
       <c r="H48" s="5">
@@ -8809,7 +8833,7 @@
         <v/>
       </c>
       <c r="E49" s="26">
-        <f>D49*$B$11</f>
+        <f>IF($B$13=1,D49*$B$11,0)</f>
         <v/>
       </c>
       <c r="F49" s="26">
@@ -8817,7 +8841,7 @@
         <v/>
       </c>
       <c r="G49" s="34">
-        <f>E49+F49</f>
+        <f>F49+E49</f>
         <v/>
       </c>
       <c r="H49" s="5">
@@ -8854,7 +8878,7 @@
         <v/>
       </c>
       <c r="E50" s="26">
-        <f>D50*$B$11</f>
+        <f>IF($B$13=1,D50*$B$11,0)</f>
         <v/>
       </c>
       <c r="F50" s="26">
@@ -8862,7 +8886,7 @@
         <v/>
       </c>
       <c r="G50" s="34">
-        <f>E50+F50</f>
+        <f>F50+E50</f>
         <v/>
       </c>
       <c r="H50" s="5">
@@ -8899,7 +8923,7 @@
         <v/>
       </c>
       <c r="E51" s="26">
-        <f>D51*$B$11</f>
+        <f>IF($B$13=1,D51*$B$11,0)</f>
         <v/>
       </c>
       <c r="F51" s="26">
@@ -8907,7 +8931,7 @@
         <v/>
       </c>
       <c r="G51" s="34">
-        <f>E51+F51</f>
+        <f>F51+E51</f>
         <v/>
       </c>
       <c r="H51" s="5">
@@ -8944,7 +8968,7 @@
         <v/>
       </c>
       <c r="E52" s="26">
-        <f>D52*$B$11</f>
+        <f>IF($B$13=1,D52*$B$11,0)</f>
         <v/>
       </c>
       <c r="F52" s="26">
@@ -8952,7 +8976,7 @@
         <v/>
       </c>
       <c r="G52" s="34">
-        <f>E52+F52</f>
+        <f>F52+E52</f>
         <v/>
       </c>
       <c r="H52" s="5">
@@ -8989,7 +9013,7 @@
         <v/>
       </c>
       <c r="E53" s="26">
-        <f>D53*$B$11</f>
+        <f>IF($B$13=1,D53*$B$11,0)</f>
         <v/>
       </c>
       <c r="F53" s="26">
@@ -8997,7 +9021,7 @@
         <v/>
       </c>
       <c r="G53" s="34">
-        <f>E53+F53</f>
+        <f>F53+E53</f>
         <v/>
       </c>
       <c r="H53" s="5">
@@ -9034,7 +9058,7 @@
         <v/>
       </c>
       <c r="E54" s="26">
-        <f>D54*$B$11</f>
+        <f>IF($B$13=1,D54*$B$11,0)</f>
         <v/>
       </c>
       <c r="F54" s="26">
@@ -9042,7 +9066,7 @@
         <v/>
       </c>
       <c r="G54" s="34">
-        <f>E54+F54</f>
+        <f>F54+E54</f>
         <v/>
       </c>
       <c r="H54" s="5">
@@ -9079,7 +9103,7 @@
         <v/>
       </c>
       <c r="E55" s="26">
-        <f>D55*$B$11</f>
+        <f>IF($B$13=1,D55*$B$11,0)</f>
         <v/>
       </c>
       <c r="F55" s="26">
@@ -9087,7 +9111,7 @@
         <v/>
       </c>
       <c r="G55" s="34">
-        <f>E55+F55</f>
+        <f>F55+E55</f>
         <v/>
       </c>
       <c r="H55" s="5">
@@ -9124,7 +9148,7 @@
         <v/>
       </c>
       <c r="E56" s="26">
-        <f>D56*$B$11</f>
+        <f>IF($B$13=1,D56*$B$11,0)</f>
         <v/>
       </c>
       <c r="F56" s="26">
@@ -9132,7 +9156,7 @@
         <v/>
       </c>
       <c r="G56" s="34">
-        <f>E56+F56</f>
+        <f>F56+E56</f>
         <v/>
       </c>
       <c r="H56" s="5">
@@ -9169,7 +9193,7 @@
         <v/>
       </c>
       <c r="E57" s="26">
-        <f>D57*$B$11</f>
+        <f>IF($B$13=1,D57*$B$11,0)</f>
         <v/>
       </c>
       <c r="F57" s="26">
@@ -9177,7 +9201,7 @@
         <v/>
       </c>
       <c r="G57" s="34">
-        <f>E57+F57</f>
+        <f>F57+E57</f>
         <v/>
       </c>
       <c r="H57" s="5">
@@ -9214,7 +9238,7 @@
         <v/>
       </c>
       <c r="E58" s="26">
-        <f>D58*$B$11</f>
+        <f>IF($B$13=1,D58*$B$11,0)</f>
         <v/>
       </c>
       <c r="F58" s="26">
@@ -9222,7 +9246,7 @@
         <v/>
       </c>
       <c r="G58" s="34">
-        <f>E58+F58</f>
+        <f>F58+E58</f>
         <v/>
       </c>
       <c r="H58" s="5">
@@ -9259,7 +9283,7 @@
         <v/>
       </c>
       <c r="E59" s="26">
-        <f>D59*$B$11</f>
+        <f>IF($B$13=1,D59*$B$11,0)</f>
         <v/>
       </c>
       <c r="F59" s="26">
@@ -9267,7 +9291,7 @@
         <v/>
       </c>
       <c r="G59" s="34">
-        <f>E59+F59</f>
+        <f>F59+E59</f>
         <v/>
       </c>
       <c r="H59" s="5">
@@ -9304,7 +9328,7 @@
         <v/>
       </c>
       <c r="E60" s="26">
-        <f>D60*$B$11</f>
+        <f>IF($B$13=1,D60*$B$11,0)</f>
         <v/>
       </c>
       <c r="F60" s="26">
@@ -9312,7 +9336,7 @@
         <v/>
       </c>
       <c r="G60" s="34">
-        <f>E60+F60</f>
+        <f>F60+E60</f>
         <v/>
       </c>
       <c r="H60" s="5">
@@ -9349,7 +9373,7 @@
         <v/>
       </c>
       <c r="E61" s="26">
-        <f>D61*$B$11</f>
+        <f>IF($B$13=1,D61*$B$11,0)</f>
         <v/>
       </c>
       <c r="F61" s="26">
@@ -9357,7 +9381,7 @@
         <v/>
       </c>
       <c r="G61" s="34">
-        <f>E61+F61</f>
+        <f>F61+E61</f>
         <v/>
       </c>
       <c r="H61" s="5">
@@ -9394,7 +9418,7 @@
         <v/>
       </c>
       <c r="E62" s="26">
-        <f>D62*$B$11</f>
+        <f>IF($B$13=1,D62*$B$11,0)</f>
         <v/>
       </c>
       <c r="F62" s="26">
@@ -9402,7 +9426,7 @@
         <v/>
       </c>
       <c r="G62" s="34">
-        <f>E62+F62</f>
+        <f>F62+E62</f>
         <v/>
       </c>
       <c r="H62" s="5">
@@ -9439,7 +9463,7 @@
         <v/>
       </c>
       <c r="E63" s="26">
-        <f>D63*$B$11</f>
+        <f>IF($B$13=1,D63*$B$11,0)</f>
         <v/>
       </c>
       <c r="F63" s="26">
@@ -9447,7 +9471,7 @@
         <v/>
       </c>
       <c r="G63" s="34">
-        <f>E63+F63</f>
+        <f>F63+E63</f>
         <v/>
       </c>
       <c r="H63" s="5">
@@ -9484,7 +9508,7 @@
         <v/>
       </c>
       <c r="E64" s="26">
-        <f>D64*$B$11</f>
+        <f>IF($B$13=1,D64*$B$11,0)</f>
         <v/>
       </c>
       <c r="F64" s="26">
@@ -9492,7 +9516,7 @@
         <v/>
       </c>
       <c r="G64" s="34">
-        <f>E64+F64</f>
+        <f>F64+E64</f>
         <v/>
       </c>
       <c r="H64" s="5">
@@ -9529,7 +9553,7 @@
         <v/>
       </c>
       <c r="E65" s="26">
-        <f>D65*$B$11</f>
+        <f>IF($B$13=1,D65*$B$11,0)</f>
         <v/>
       </c>
       <c r="F65" s="26">
@@ -9537,7 +9561,7 @@
         <v/>
       </c>
       <c r="G65" s="34">
-        <f>E65+F65</f>
+        <f>F65+E65</f>
         <v/>
       </c>
       <c r="H65" s="5">
@@ -9574,7 +9598,7 @@
         <v/>
       </c>
       <c r="E66" s="26">
-        <f>D66*$B$11</f>
+        <f>IF($B$13=1,D66*$B$11,0)</f>
         <v/>
       </c>
       <c r="F66" s="26">
@@ -9582,7 +9606,7 @@
         <v/>
       </c>
       <c r="G66" s="34">
-        <f>E66+F66</f>
+        <f>F66+E66</f>
         <v/>
       </c>
       <c r="H66" s="5">
@@ -9619,7 +9643,7 @@
         <v/>
       </c>
       <c r="E67" s="26">
-        <f>D67*$B$11</f>
+        <f>IF($B$13=1,D67*$B$11,0)</f>
         <v/>
       </c>
       <c r="F67" s="26">
@@ -9627,7 +9651,7 @@
         <v/>
       </c>
       <c r="G67" s="34">
-        <f>E67+F67</f>
+        <f>F67+E67</f>
         <v/>
       </c>
       <c r="H67" s="5">
@@ -9664,7 +9688,7 @@
         <v/>
       </c>
       <c r="E68" s="26">
-        <f>D68*$B$11</f>
+        <f>IF($B$13=1,D68*$B$11,0)</f>
         <v/>
       </c>
       <c r="F68" s="26">
@@ -9672,7 +9696,7 @@
         <v/>
       </c>
       <c r="G68" s="34">
-        <f>E68+F68</f>
+        <f>F68+E68</f>
         <v/>
       </c>
       <c r="H68" s="5">
@@ -9709,7 +9733,7 @@
         <v/>
       </c>
       <c r="E69" s="26">
-        <f>D69*$B$11</f>
+        <f>IF($B$13=1,D69*$B$11,0)</f>
         <v/>
       </c>
       <c r="F69" s="26">
@@ -9717,7 +9741,7 @@
         <v/>
       </c>
       <c r="G69" s="34">
-        <f>E69+F69</f>
+        <f>F69+E69</f>
         <v/>
       </c>
       <c r="H69" s="5">
@@ -9754,7 +9778,7 @@
         <v/>
       </c>
       <c r="E70" s="26">
-        <f>D70*$B$11</f>
+        <f>IF($B$13=1,D70*$B$11,0)</f>
         <v/>
       </c>
       <c r="F70" s="26">
@@ -9762,7 +9786,7 @@
         <v/>
       </c>
       <c r="G70" s="34">
-        <f>E70+F70</f>
+        <f>F70+E70</f>
         <v/>
       </c>
       <c r="H70" s="5">
@@ -9799,7 +9823,7 @@
         <v/>
       </c>
       <c r="E71" s="26">
-        <f>D71*$B$11</f>
+        <f>IF($B$13=1,D71*$B$11,0)</f>
         <v/>
       </c>
       <c r="F71" s="26">
@@ -9807,7 +9831,7 @@
         <v/>
       </c>
       <c r="G71" s="34">
-        <f>E71+F71</f>
+        <f>F71+E71</f>
         <v/>
       </c>
       <c r="H71" s="5">
@@ -9844,7 +9868,7 @@
         <v/>
       </c>
       <c r="E72" s="26">
-        <f>D72*$B$11</f>
+        <f>IF($B$13=1,D72*$B$11,0)</f>
         <v/>
       </c>
       <c r="F72" s="26">
@@ -9852,7 +9876,7 @@
         <v/>
       </c>
       <c r="G72" s="34">
-        <f>E72+F72</f>
+        <f>F72+E72</f>
         <v/>
       </c>
       <c r="H72" s="5">
@@ -9889,7 +9913,7 @@
         <v/>
       </c>
       <c r="E73" s="26">
-        <f>D73*$B$11</f>
+        <f>IF($B$13=1,D73*$B$11,0)</f>
         <v/>
       </c>
       <c r="F73" s="26">
@@ -9897,7 +9921,7 @@
         <v/>
       </c>
       <c r="G73" s="34">
-        <f>E73+F73</f>
+        <f>F73+E73</f>
         <v/>
       </c>
       <c r="H73" s="5">
@@ -9934,7 +9958,7 @@
         <v/>
       </c>
       <c r="E74" s="26">
-        <f>D74*$B$11</f>
+        <f>IF($B$13=1,D74*$B$11,0)</f>
         <v/>
       </c>
       <c r="F74" s="26">
@@ -9942,7 +9966,7 @@
         <v/>
       </c>
       <c r="G74" s="34">
-        <f>E74+F74</f>
+        <f>F74+E74</f>
         <v/>
       </c>
       <c r="H74" s="5">
@@ -9979,7 +10003,7 @@
         <v/>
       </c>
       <c r="E75" s="26">
-        <f>D75*$B$11</f>
+        <f>IF($B$13=1,D75*$B$11,0)</f>
         <v/>
       </c>
       <c r="F75" s="26">
@@ -9987,7 +10011,7 @@
         <v/>
       </c>
       <c r="G75" s="34">
-        <f>E75+F75</f>
+        <f>F75+E75</f>
         <v/>
       </c>
       <c r="H75" s="5">
@@ -10024,7 +10048,7 @@
         <v/>
       </c>
       <c r="E76" s="26">
-        <f>D76*$B$11</f>
+        <f>IF($B$13=1,D76*$B$11,0)</f>
         <v/>
       </c>
       <c r="F76" s="26">
@@ -10032,7 +10056,7 @@
         <v/>
       </c>
       <c r="G76" s="34">
-        <f>E76+F76</f>
+        <f>F76+E76</f>
         <v/>
       </c>
       <c r="H76" s="5">
@@ -10069,7 +10093,7 @@
         <v/>
       </c>
       <c r="E77" s="26">
-        <f>D77*$B$11</f>
+        <f>IF($B$13=1,D77*$B$11,0)</f>
         <v/>
       </c>
       <c r="F77" s="26">
@@ -10077,7 +10101,7 @@
         <v/>
       </c>
       <c r="G77" s="34">
-        <f>E77+F77</f>
+        <f>F77+E77</f>
         <v/>
       </c>
       <c r="H77" s="5">
@@ -10114,7 +10138,7 @@
         <v/>
       </c>
       <c r="E78" s="26">
-        <f>D78*$B$11</f>
+        <f>IF($B$13=1,D78*$B$11,0)</f>
         <v/>
       </c>
       <c r="F78" s="26">
@@ -10122,7 +10146,7 @@
         <v/>
       </c>
       <c r="G78" s="34">
-        <f>E78+F78</f>
+        <f>F78+E78</f>
         <v/>
       </c>
       <c r="H78" s="5">
@@ -10159,7 +10183,7 @@
         <v/>
       </c>
       <c r="E79" s="26">
-        <f>D79*$B$11</f>
+        <f>IF($B$13=1,D79*$B$11,0)</f>
         <v/>
       </c>
       <c r="F79" s="26">
@@ -10167,7 +10191,7 @@
         <v/>
       </c>
       <c r="G79" s="34">
-        <f>E79+F79</f>
+        <f>F79+E79</f>
         <v/>
       </c>
       <c r="H79" s="5">
@@ -10204,7 +10228,7 @@
         <v/>
       </c>
       <c r="E80" s="26">
-        <f>D80*$B$11</f>
+        <f>IF($B$13=1,D80*$B$11,0)</f>
         <v/>
       </c>
       <c r="F80" s="26">
@@ -10212,7 +10236,7 @@
         <v/>
       </c>
       <c r="G80" s="34">
-        <f>E80+F80</f>
+        <f>F80+E80</f>
         <v/>
       </c>
       <c r="H80" s="5">
@@ -10249,7 +10273,7 @@
         <v/>
       </c>
       <c r="E81" s="26">
-        <f>D81*$B$11</f>
+        <f>IF($B$13=1,D81*$B$11,0)</f>
         <v/>
       </c>
       <c r="F81" s="26">
@@ -10257,7 +10281,7 @@
         <v/>
       </c>
       <c r="G81" s="34">
-        <f>E81+F81</f>
+        <f>F81+E81</f>
         <v/>
       </c>
       <c r="H81" s="5">
@@ -10294,7 +10318,7 @@
         <v/>
       </c>
       <c r="E82" s="26">
-        <f>D82*$B$11</f>
+        <f>IF($B$13=1,D82*$B$11,0)</f>
         <v/>
       </c>
       <c r="F82" s="26">
@@ -10302,7 +10326,7 @@
         <v/>
       </c>
       <c r="G82" s="34">
-        <f>E82+F82</f>
+        <f>F82+E82</f>
         <v/>
       </c>
       <c r="H82" s="5">
@@ -10339,7 +10363,7 @@
         <v/>
       </c>
       <c r="E83" s="26">
-        <f>D83*$B$11</f>
+        <f>IF($B$13=1,D83*$B$11,0)</f>
         <v/>
       </c>
       <c r="F83" s="26">
@@ -10347,7 +10371,7 @@
         <v/>
       </c>
       <c r="G83" s="34">
-        <f>E83+F83</f>
+        <f>F83+E83</f>
         <v/>
       </c>
       <c r="H83" s="5">
@@ -10384,7 +10408,7 @@
         <v/>
       </c>
       <c r="E84" s="26">
-        <f>D84*$B$11</f>
+        <f>IF($B$13=1,D84*$B$11,0)</f>
         <v/>
       </c>
       <c r="F84" s="26">
@@ -10392,7 +10416,7 @@
         <v/>
       </c>
       <c r="G84" s="34">
-        <f>E84+F84</f>
+        <f>F84+E84</f>
         <v/>
       </c>
       <c r="H84" s="5">
@@ -10429,7 +10453,7 @@
         <v/>
       </c>
       <c r="E85" s="26">
-        <f>D85*$B$11</f>
+        <f>IF($B$13=1,D85*$B$11,0)</f>
         <v/>
       </c>
       <c r="F85" s="26">
@@ -10437,7 +10461,7 @@
         <v/>
       </c>
       <c r="G85" s="34">
-        <f>E85+F85</f>
+        <f>F85+E85</f>
         <v/>
       </c>
       <c r="H85" s="5">
@@ -10474,7 +10498,7 @@
         <v/>
       </c>
       <c r="E86" s="26">
-        <f>D86*$B$11</f>
+        <f>IF($B$13=1,D86*$B$11,0)</f>
         <v/>
       </c>
       <c r="F86" s="26">
@@ -10482,7 +10506,7 @@
         <v/>
       </c>
       <c r="G86" s="34">
-        <f>E86+F86</f>
+        <f>F86+E86</f>
         <v/>
       </c>
       <c r="H86" s="5">
@@ -10519,7 +10543,7 @@
         <v/>
       </c>
       <c r="E87" s="26">
-        <f>D87*$B$11</f>
+        <f>IF($B$13=1,D87*$B$11,0)</f>
         <v/>
       </c>
       <c r="F87" s="26">
@@ -10527,7 +10551,7 @@
         <v/>
       </c>
       <c r="G87" s="34">
-        <f>E87+F87</f>
+        <f>F87+E87</f>
         <v/>
       </c>
       <c r="H87" s="5">
@@ -10564,7 +10588,7 @@
         <v/>
       </c>
       <c r="E88" s="26">
-        <f>D88*$B$11</f>
+        <f>IF($B$13=1,D88*$B$11,0)</f>
         <v/>
       </c>
       <c r="F88" s="26">
@@ -10572,7 +10596,7 @@
         <v/>
       </c>
       <c r="G88" s="34">
-        <f>E88+F88</f>
+        <f>F88+E88</f>
         <v/>
       </c>
       <c r="H88" s="5">
@@ -10609,7 +10633,7 @@
         <v/>
       </c>
       <c r="E89" s="26">
-        <f>D89*$B$11</f>
+        <f>IF($B$13=1,D89*$B$11,0)</f>
         <v/>
       </c>
       <c r="F89" s="26">
@@ -10617,7 +10641,7 @@
         <v/>
       </c>
       <c r="G89" s="34">
-        <f>E89+F89</f>
+        <f>F89+E89</f>
         <v/>
       </c>
       <c r="H89" s="5">
@@ -10654,7 +10678,7 @@
         <v/>
       </c>
       <c r="E90" s="26">
-        <f>D90*$B$11</f>
+        <f>IF($B$13=1,D90*$B$11,0)</f>
         <v/>
       </c>
       <c r="F90" s="26">
@@ -10662,7 +10686,7 @@
         <v/>
       </c>
       <c r="G90" s="34">
-        <f>E90+F90</f>
+        <f>F90+E90</f>
         <v/>
       </c>
       <c r="H90" s="5">
@@ -10699,7 +10723,7 @@
         <v/>
       </c>
       <c r="E91" s="26">
-        <f>D91*$B$11</f>
+        <f>IF($B$13=1,D91*$B$11,0)</f>
         <v/>
       </c>
       <c r="F91" s="26">
@@ -10707,7 +10731,7 @@
         <v/>
       </c>
       <c r="G91" s="34">
-        <f>E91+F91</f>
+        <f>F91+E91</f>
         <v/>
       </c>
       <c r="H91" s="5">
@@ -10744,7 +10768,7 @@
         <v/>
       </c>
       <c r="E92" s="26">
-        <f>D92*$B$11</f>
+        <f>IF($B$13=1,D92*$B$11,0)</f>
         <v/>
       </c>
       <c r="F92" s="26">
@@ -10752,7 +10776,7 @@
         <v/>
       </c>
       <c r="G92" s="34">
-        <f>E92+F92</f>
+        <f>F92+E92</f>
         <v/>
       </c>
       <c r="H92" s="5">
@@ -10789,7 +10813,7 @@
         <v/>
       </c>
       <c r="E93" s="26">
-        <f>D93*$B$11</f>
+        <f>IF($B$13=1,D93*$B$11,0)</f>
         <v/>
       </c>
       <c r="F93" s="26">
@@ -10797,7 +10821,7 @@
         <v/>
       </c>
       <c r="G93" s="34">
-        <f>E93+F93</f>
+        <f>F93+E93</f>
         <v/>
       </c>
       <c r="H93" s="5">
@@ -10834,7 +10858,7 @@
         <v/>
       </c>
       <c r="E94" s="26">
-        <f>D94*$B$11</f>
+        <f>IF($B$13=1,D94*$B$11,0)</f>
         <v/>
       </c>
       <c r="F94" s="26">
@@ -10842,7 +10866,7 @@
         <v/>
       </c>
       <c r="G94" s="34">
-        <f>E94+F94</f>
+        <f>F94+E94</f>
         <v/>
       </c>
       <c r="H94" s="5">
@@ -10879,7 +10903,7 @@
         <v/>
       </c>
       <c r="E95" s="26">
-        <f>D95*$B$11</f>
+        <f>IF($B$13=1,D95*$B$11,0)</f>
         <v/>
       </c>
       <c r="F95" s="26">
@@ -10887,7 +10911,7 @@
         <v/>
       </c>
       <c r="G95" s="34">
-        <f>E95+F95</f>
+        <f>F95+E95</f>
         <v/>
       </c>
       <c r="H95" s="5">
@@ -10924,7 +10948,7 @@
         <v/>
       </c>
       <c r="E96" s="26">
-        <f>D96*$B$11</f>
+        <f>IF($B$13=1,D96*$B$11,0)</f>
         <v/>
       </c>
       <c r="F96" s="26">
@@ -10932,7 +10956,7 @@
         <v/>
       </c>
       <c r="G96" s="34">
-        <f>E96+F96</f>
+        <f>F96+E96</f>
         <v/>
       </c>
       <c r="H96" s="5">
@@ -10969,7 +10993,7 @@
         <v/>
       </c>
       <c r="E97" s="26">
-        <f>D97*$B$11</f>
+        <f>IF($B$13=1,D97*$B$11,0)</f>
         <v/>
       </c>
       <c r="F97" s="26">
@@ -10977,7 +11001,7 @@
         <v/>
       </c>
       <c r="G97" s="34">
-        <f>E97+F97</f>
+        <f>F97+E97</f>
         <v/>
       </c>
       <c r="H97" s="5">
@@ -11014,7 +11038,7 @@
         <v/>
       </c>
       <c r="E98" s="26">
-        <f>D98*$B$11</f>
+        <f>IF($B$13=1,D98*$B$11,0)</f>
         <v/>
       </c>
       <c r="F98" s="26">
@@ -11022,7 +11046,7 @@
         <v/>
       </c>
       <c r="G98" s="34">
-        <f>E98+F98</f>
+        <f>F98+E98</f>
         <v/>
       </c>
       <c r="H98" s="5">
@@ -11059,7 +11083,7 @@
         <v/>
       </c>
       <c r="E99" s="26">
-        <f>D99*$B$11</f>
+        <f>IF($B$13=1,D99*$B$11,0)</f>
         <v/>
       </c>
       <c r="F99" s="26">
@@ -11067,7 +11091,7 @@
         <v/>
       </c>
       <c r="G99" s="34">
-        <f>E99+F99</f>
+        <f>F99+E99</f>
         <v/>
       </c>
       <c r="H99" s="5">
@@ -11104,7 +11128,7 @@
         <v/>
       </c>
       <c r="E100" s="26">
-        <f>D100*$B$11</f>
+        <f>IF($B$13=1,D100*$B$11,0)</f>
         <v/>
       </c>
       <c r="F100" s="26">
@@ -11112,7 +11136,7 @@
         <v/>
       </c>
       <c r="G100" s="34">
-        <f>E100+F100</f>
+        <f>F100+E100</f>
         <v/>
       </c>
       <c r="H100" s="5">
@@ -11149,7 +11173,7 @@
         <v/>
       </c>
       <c r="E101" s="26">
-        <f>D101*$B$11</f>
+        <f>IF($B$13=1,D101*$B$11,0)</f>
         <v/>
       </c>
       <c r="F101" s="26">
@@ -11157,7 +11181,7 @@
         <v/>
       </c>
       <c r="G101" s="34">
-        <f>E101+F101</f>
+        <f>F101+E101</f>
         <v/>
       </c>
       <c r="H101" s="5">
@@ -11194,7 +11218,7 @@
         <v/>
       </c>
       <c r="E102" s="26">
-        <f>D102*$B$11</f>
+        <f>IF($B$13=1,D102*$B$11,0)</f>
         <v/>
       </c>
       <c r="F102" s="26">
@@ -11202,7 +11226,7 @@
         <v/>
       </c>
       <c r="G102" s="34">
-        <f>E102+F102</f>
+        <f>F102+E102</f>
         <v/>
       </c>
       <c r="H102" s="5">
@@ -11239,7 +11263,7 @@
         <v/>
       </c>
       <c r="E103" s="26">
-        <f>D103*$B$11</f>
+        <f>IF($B$13=1,D103*$B$11,0)</f>
         <v/>
       </c>
       <c r="F103" s="26">
@@ -11247,7 +11271,7 @@
         <v/>
       </c>
       <c r="G103" s="34">
-        <f>E103+F103</f>
+        <f>F103+E103</f>
         <v/>
       </c>
       <c r="H103" s="5">
@@ -11284,7 +11308,7 @@
         <v/>
       </c>
       <c r="E104" s="26">
-        <f>D104*$B$11</f>
+        <f>IF($B$13=1,D104*$B$11,0)</f>
         <v/>
       </c>
       <c r="F104" s="26">
@@ -11292,7 +11316,7 @@
         <v/>
       </c>
       <c r="G104" s="34">
-        <f>E104+F104</f>
+        <f>F104+E104</f>
         <v/>
       </c>
       <c r="H104" s="5">
@@ -11329,7 +11353,7 @@
         <v/>
       </c>
       <c r="E105" s="26">
-        <f>D105*$B$11</f>
+        <f>IF($B$13=1,D105*$B$11,0)</f>
         <v/>
       </c>
       <c r="F105" s="26">
@@ -11337,7 +11361,7 @@
         <v/>
       </c>
       <c r="G105" s="34">
-        <f>E105+F105</f>
+        <f>F105+E105</f>
         <v/>
       </c>
       <c r="H105" s="5">
@@ -11374,7 +11398,7 @@
         <v/>
       </c>
       <c r="E106" s="26">
-        <f>D106*$B$11</f>
+        <f>IF($B$13=1,D106*$B$11,0)</f>
         <v/>
       </c>
       <c r="F106" s="26">
@@ -11382,7 +11406,7 @@
         <v/>
       </c>
       <c r="G106" s="34">
-        <f>E106+F106</f>
+        <f>F106+E106</f>
         <v/>
       </c>
       <c r="H106" s="5">
@@ -11419,7 +11443,7 @@
         <v/>
       </c>
       <c r="E107" s="26">
-        <f>D107*$B$11</f>
+        <f>IF($B$13=1,D107*$B$11,0)</f>
         <v/>
       </c>
       <c r="F107" s="26">
@@ -11427,7 +11451,7 @@
         <v/>
       </c>
       <c r="G107" s="34">
-        <f>E107+F107</f>
+        <f>F107+E107</f>
         <v/>
       </c>
       <c r="H107" s="5">
@@ -11477,14 +11501,14 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>Méthode C — routage avec Qout composé + V = V_pond + V_ditch</t>
+          <t>Méthode C — routage Qout composé; V = V_total (B25 pilote V_ditch)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="40" t="inlineStr">
         <is>
-          <t>À chaque pas: WSE lu sur Compose_900!V_total → Qout sur Compose_900. ΔV = (Qin_moy − Qout)×Δt. Si V≈0, Qout = MIN(Qin, Q_plein).</t>
+          <t>À chaque pas: WSE lu sur Compose_900!V_total → Qout sur Compose_900. V_total = V_pond + V_ditch seulement si Parametres!B25=1; sinon V=levé SS_Amont. Q_overflow reste actif (b,z,L,n,S). ΔV = (Qin_moy − Qout)×Δt.</t>
         </is>
       </c>
     </row>
@@ -12332,10 +12356,9 @@
         <f>Parametres!B51</f>
         <v/>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Vmax_C inclut V_ditch</t>
-        </is>
+      <c r="D26">
+        <f>IF(Parametres!B25=1,"Vmax_C inclut V_ditch","Vmax_C = levé seul (B25=0)")</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/engineering/drainage-design/retention_volume/Volume_Retention_Deux_Zones_1500_900_1200.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Deux_Zones_1500_900_1200.xlsx
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
+        <fgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
+        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -128,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -144,42 +144,43 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1703,7 +1704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2574,8 +2575,167 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="24" t="inlineStr">
+        <is>
+          <t>Vitesses de référence — V = Q / A_plein (pleine section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="25" t="inlineStr">
+        <is>
+          <t>A_plein = π D²/4. V_eq = Q/A_plein. Si le tuyau est partiellement rempli, la vitesse réelle Q/A(h) est plus élevée pour le même Q — voir Courbe_QH_900 col. V. Critères typiques fossé/tuyau: souvent 0.6–3 ou 4 m/s selon municipalité (à confirmer).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Ouvrage</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>D (m)</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>A_plein (m²)</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Q ref (m³/s)</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>V_eq (m/s)</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>Source Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Ø1500 (entrée)</t>
+        </is>
+      </c>
+      <c r="B86" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C86" s="5">
+        <f>PI()*B86^2/4</f>
+        <v/>
+      </c>
+      <c r="D86" s="5">
+        <f>Hydrogramme!B4</f>
+        <v/>
+      </c>
+      <c r="E86" s="27">
+        <f>IF(C86&lt;=0,0,D86/C86)</f>
+        <v/>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>Qpointe hydrogramme</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Ø900 (contrôle)</t>
+        </is>
+      </c>
+      <c r="B87" s="26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C87" s="5">
+        <f>PI()*B87^2/4</f>
+        <v/>
+      </c>
+      <c r="D87" s="5">
+        <f>B18</f>
+        <v/>
+      </c>
+      <c r="E87" s="27">
+        <f>IF(C87&lt;=0,0,D87/C87)</f>
+        <v/>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Q_plein Manning (B18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Ø1200 (aval)</t>
+        </is>
+      </c>
+      <c r="B88" s="26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C88" s="5">
+        <f>PI()*B88^2/4</f>
+        <v/>
+      </c>
+      <c r="D88" s="11" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="E88" s="27">
+        <f>IF(C88&lt;=0,0,D88/C88)</f>
+        <v/>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>Q_plein Ø1200 (édit. si besoin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>V_Ø900 @ Qout Calcul_A (m/s)</t>
+        </is>
+      </c>
+      <c r="B89" s="22">
+        <f>IF(C87&lt;=0,0,Calcul_A!B2/C87)</f>
+        <v/>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Qout constant Méthode A / A_plein Ø900</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>V_Ø1200 @ Qout Calcul_Aval_A (m/s)</t>
+        </is>
+      </c>
+      <c r="B90" s="22">
+        <f>IF(C88&lt;=0,0,Calcul_Aval_A!B5/C88)</f>
+        <v/>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Qout Aval / A_plein Ø1200</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="A67:H67"/>
     <mergeCell ref="A77:H77"/>
     <mergeCell ref="A73:H73"/>
@@ -2588,6 +2748,7 @@
     <mergeCell ref="A66:H66"/>
     <mergeCell ref="A80:H80"/>
     <mergeCell ref="A9:H10"/>
+    <mergeCell ref="A83:H84"/>
     <mergeCell ref="A71:H71"/>
     <mergeCell ref="A76:H76"/>
     <mergeCell ref="A62:H62"/>
@@ -2672,241 +2833,241 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="32">
+      <c r="A6" s="26">
         <f>SS_Amont!A11</f>
         <v/>
       </c>
-      <c r="B6" s="45">
+      <c r="B6" s="46">
         <f>SS_Amont!B11</f>
         <v/>
       </c>
-      <c r="C6" s="45">
+      <c r="C6" s="46">
         <f>SS_Aval!B11</f>
         <v/>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="47">
         <f>B6+C6</f>
         <v/>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="29">
         <f>SS_Amont!E11</f>
         <v/>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="29">
         <f>SS_Aval!E11</f>
         <v/>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="36">
         <f>E6+F6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="32">
+      <c r="A7" s="26">
         <f>SS_Amont!A12</f>
         <v/>
       </c>
-      <c r="B7" s="45">
+      <c r="B7" s="46">
         <f>SS_Amont!B12</f>
         <v/>
       </c>
-      <c r="C7" s="45">
+      <c r="C7" s="46">
         <f>SS_Aval!B12</f>
         <v/>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="47">
         <f>B7+C7</f>
         <v/>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="29">
         <f>SS_Amont!E12</f>
         <v/>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="29">
         <f>SS_Aval!E12</f>
         <v/>
       </c>
-      <c r="G7" s="34">
+      <c r="G7" s="36">
         <f>E7+F7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="32">
+      <c r="A8" s="26">
         <f>SS_Amont!A13</f>
         <v/>
       </c>
-      <c r="B8" s="45">
+      <c r="B8" s="46">
         <f>SS_Amont!B13</f>
         <v/>
       </c>
-      <c r="C8" s="45">
+      <c r="C8" s="46">
         <f>SS_Aval!B13</f>
         <v/>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="47">
         <f>B8+C8</f>
         <v/>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="29">
         <f>SS_Amont!E13</f>
         <v/>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="29">
         <f>SS_Aval!E13</f>
         <v/>
       </c>
-      <c r="G8" s="34">
+      <c r="G8" s="36">
         <f>E8+F8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32">
+      <c r="A9" s="26">
         <f>SS_Amont!A14</f>
         <v/>
       </c>
-      <c r="B9" s="45">
+      <c r="B9" s="46">
         <f>SS_Amont!B14</f>
         <v/>
       </c>
-      <c r="C9" s="45">
+      <c r="C9" s="46">
         <f>SS_Aval!B14</f>
         <v/>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="47">
         <f>B9+C9</f>
         <v/>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="29">
         <f>SS_Amont!E14</f>
         <v/>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="29">
         <f>SS_Aval!E14</f>
         <v/>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="36">
         <f>E9+F9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32">
+      <c r="A10" s="26">
         <f>SS_Amont!A15</f>
         <v/>
       </c>
-      <c r="B10" s="45">
+      <c r="B10" s="46">
         <f>SS_Amont!B15</f>
         <v/>
       </c>
-      <c r="C10" s="45">
+      <c r="C10" s="46">
         <f>SS_Aval!B15</f>
         <v/>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="47">
         <f>B10+C10</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="29">
         <f>SS_Amont!E15</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="29">
         <f>SS_Aval!E15</f>
         <v/>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="36">
         <f>E10+F10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="32">
+      <c r="A11" s="26">
         <f>SS_Amont!A16</f>
         <v/>
       </c>
-      <c r="B11" s="45">
+      <c r="B11" s="46">
         <f>SS_Amont!B16</f>
         <v/>
       </c>
-      <c r="C11" s="45">
+      <c r="C11" s="46">
         <f>SS_Aval!B16</f>
         <v/>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="47">
         <f>B11+C11</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="29">
         <f>SS_Amont!E16</f>
         <v/>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="29">
         <f>SS_Aval!E16</f>
         <v/>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="36">
         <f>E11+F11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="32">
+      <c r="A12" s="26">
         <f>SS_Amont!A17</f>
         <v/>
       </c>
-      <c r="B12" s="45">
+      <c r="B12" s="46">
         <f>SS_Amont!B17</f>
         <v/>
       </c>
-      <c r="C12" s="45">
+      <c r="C12" s="46">
         <f>SS_Aval!B17</f>
         <v/>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="47">
         <f>B12+C12</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="29">
         <f>SS_Amont!E17</f>
         <v/>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="29">
         <f>SS_Aval!E17</f>
         <v/>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="36">
         <f>E12+F12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="32">
+      <c r="A13" s="26">
         <f>SS_Amont!A18</f>
         <v/>
       </c>
-      <c r="B13" s="45">
+      <c r="B13" s="46">
         <f>SS_Amont!B18</f>
         <v/>
       </c>
-      <c r="C13" s="45">
+      <c r="C13" s="46">
         <f>SS_Aval!B18</f>
         <v/>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="47">
         <f>B13+C13</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="29">
         <f>SS_Amont!E18</f>
         <v/>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="29">
         <f>SS_Aval!E18</f>
         <v/>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="36">
         <f>E13+F13</f>
         <v/>
       </c>
@@ -2925,7 +3086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2937,6 +3098,8 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2947,7 +3110,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="40" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>Qin_aval ≈ débit livré par le Ø900 (Calcul_A colonne C = Qcap Ø900 quand le bassin amont stocke). Qout_aval = Parametres capacité Ø1200. Stockage sur SS_Aval. Souvent Vmax_Aval faible si Q_1200 ≫ Q_900.</t>
         </is>
@@ -2960,7 +3123,7 @@
           <t>Qout_Aval (m³/s)</t>
         </is>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="33">
         <f>4.93</f>
         <v/>
       </c>
@@ -2976,7 +3139,7 @@
           <t>Vmax_Aval_A (m³)</t>
         </is>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="34">
         <f>MAX(H10:H22)</f>
         <v/>
       </c>
@@ -3038,9 +3201,19 @@
           <t>Stockage?</t>
         </is>
       </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>V_livré_Ø900 (m/s)</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>V_Ø1200 (m/s)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="26">
+      <c r="A10" s="29">
         <f>Calcul_A!A8</f>
         <v/>
       </c>
@@ -3048,7 +3221,7 @@
         <f>Calcul_A!C8</f>
         <v/>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="26">
         <f>$B$5</f>
         <v/>
       </c>
@@ -3065,16 +3238,24 @@
       <c r="G10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="33" t="n">
+      <c r="H10" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="4">
         <f>IF(H10&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J10" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,B10/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="K10" s="27">
+        <f>IF(Parametres!$C$88&lt;=0,0,C10/Parametres!$C$88)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="26">
+      <c r="A11" s="29">
         <f>Calcul_A!A9</f>
         <v/>
       </c>
@@ -3082,7 +3263,7 @@
         <f>Calcul_A!C9</f>
         <v/>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="26">
         <f>$B$5</f>
         <v/>
       </c>
@@ -3090,19 +3271,19 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="29">
         <f>(A11-A10)*60</f>
         <v/>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="29">
         <f>0.5*(B10+B11)*E11</f>
         <v/>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="29">
         <f>F11-(H11-H10)</f>
         <v/>
       </c>
-      <c r="H11" s="34">
+      <c r="H11" s="36">
         <f>MAX(0,H10+0.5*(D10+D11)*E11)</f>
         <v/>
       </c>
@@ -3110,9 +3291,17 @@
         <f>IF(H11&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J11" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,B11/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="K11" s="27">
+        <f>IF(Parametres!$C$88&lt;=0,0,C11/Parametres!$C$88)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="26">
+      <c r="A12" s="29">
         <f>Calcul_A!A10</f>
         <v/>
       </c>
@@ -3120,7 +3309,7 @@
         <f>Calcul_A!C10</f>
         <v/>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="26">
         <f>$B$5</f>
         <v/>
       </c>
@@ -3128,19 +3317,19 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="29">
         <f>(A12-A11)*60</f>
         <v/>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="29">
         <f>0.5*(B11+B12)*E12</f>
         <v/>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="29">
         <f>F12-(H12-H11)</f>
         <v/>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="36">
         <f>MAX(0,H11+0.5*(D11+D12)*E12)</f>
         <v/>
       </c>
@@ -3148,9 +3337,17 @@
         <f>IF(H12&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J12" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,B12/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="K12" s="27">
+        <f>IF(Parametres!$C$88&lt;=0,0,C12/Parametres!$C$88)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="26">
+      <c r="A13" s="29">
         <f>Calcul_A!A11</f>
         <v/>
       </c>
@@ -3158,7 +3355,7 @@
         <f>Calcul_A!C11</f>
         <v/>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="26">
         <f>$B$5</f>
         <v/>
       </c>
@@ -3166,19 +3363,19 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="29">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="29">
         <f>0.5*(B12+B13)*E13</f>
         <v/>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="29">
         <f>F13-(H13-H12)</f>
         <v/>
       </c>
-      <c r="H13" s="34">
+      <c r="H13" s="36">
         <f>MAX(0,H12+0.5*(D12+D13)*E13)</f>
         <v/>
       </c>
@@ -3186,9 +3383,17 @@
         <f>IF(H13&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J13" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,B13/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="K13" s="27">
+        <f>IF(Parametres!$C$88&lt;=0,0,C13/Parametres!$C$88)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="26">
+      <c r="A14" s="29">
         <f>Calcul_A!A12</f>
         <v/>
       </c>
@@ -3196,7 +3401,7 @@
         <f>Calcul_A!C12</f>
         <v/>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="26">
         <f>$B$5</f>
         <v/>
       </c>
@@ -3204,19 +3409,19 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="29">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="29">
         <f>0.5*(B13+B14)*E14</f>
         <v/>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="29">
         <f>F14-(H14-H13)</f>
         <v/>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="36">
         <f>MAX(0,H13+0.5*(D13+D14)*E14)</f>
         <v/>
       </c>
@@ -3224,9 +3429,17 @@
         <f>IF(H14&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J14" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,B14/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="K14" s="27">
+        <f>IF(Parametres!$C$88&lt;=0,0,C14/Parametres!$C$88)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="26">
+      <c r="A15" s="29">
         <f>Calcul_A!A13</f>
         <v/>
       </c>
@@ -3234,7 +3447,7 @@
         <f>Calcul_A!C13</f>
         <v/>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="26">
         <f>$B$5</f>
         <v/>
       </c>
@@ -3242,19 +3455,19 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="29">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="29">
         <f>0.5*(B14+B15)*E15</f>
         <v/>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="29">
         <f>F15-(H15-H14)</f>
         <v/>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="36">
         <f>MAX(0,H14+0.5*(D14+D15)*E15)</f>
         <v/>
       </c>
@@ -3262,9 +3475,17 @@
         <f>IF(H15&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J15" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,B15/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="K15" s="27">
+        <f>IF(Parametres!$C$88&lt;=0,0,C15/Parametres!$C$88)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="26">
+      <c r="A16" s="29">
         <f>Calcul_A!A14</f>
         <v/>
       </c>
@@ -3272,7 +3493,7 @@
         <f>Calcul_A!C14</f>
         <v/>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="26">
         <f>$B$5</f>
         <v/>
       </c>
@@ -3280,19 +3501,19 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="29">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="29">
         <f>0.5*(B15+B16)*E16</f>
         <v/>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="29">
         <f>F16-(H16-H15)</f>
         <v/>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="36">
         <f>MAX(0,H15+0.5*(D15+D16)*E16)</f>
         <v/>
       </c>
@@ -3300,9 +3521,17 @@
         <f>IF(H16&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J16" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,B16/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="K16" s="27">
+        <f>IF(Parametres!$C$88&lt;=0,0,C16/Parametres!$C$88)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="26">
+      <c r="A17" s="29">
         <f>Calcul_A!A15</f>
         <v/>
       </c>
@@ -3310,7 +3539,7 @@
         <f>Calcul_A!C15</f>
         <v/>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="26">
         <f>$B$5</f>
         <v/>
       </c>
@@ -3318,19 +3547,19 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="29">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="29">
         <f>0.5*(B16+B17)*E17</f>
         <v/>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="29">
         <f>F17-(H17-H16)</f>
         <v/>
       </c>
-      <c r="H17" s="34">
+      <c r="H17" s="36">
         <f>MAX(0,H16+0.5*(D16+D17)*E17)</f>
         <v/>
       </c>
@@ -3338,9 +3567,17 @@
         <f>IF(H17&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J17" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,B17/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="K17" s="27">
+        <f>IF(Parametres!$C$88&lt;=0,0,C17/Parametres!$C$88)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="26">
+      <c r="A18" s="29">
         <f>Calcul_A!A16</f>
         <v/>
       </c>
@@ -3348,7 +3585,7 @@
         <f>Calcul_A!C16</f>
         <v/>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="26">
         <f>$B$5</f>
         <v/>
       </c>
@@ -3356,19 +3593,19 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="29">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="29">
         <f>0.5*(B17+B18)*E18</f>
         <v/>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="29">
         <f>F18-(H18-H17)</f>
         <v/>
       </c>
-      <c r="H18" s="34">
+      <c r="H18" s="36">
         <f>MAX(0,H17+0.5*(D17+D18)*E18)</f>
         <v/>
       </c>
@@ -3376,9 +3613,17 @@
         <f>IF(H18&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J18" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,B18/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="K18" s="27">
+        <f>IF(Parametres!$C$88&lt;=0,0,C18/Parametres!$C$88)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="26">
+      <c r="A19" s="29">
         <f>Calcul_A!A17</f>
         <v/>
       </c>
@@ -3386,7 +3631,7 @@
         <f>Calcul_A!C17</f>
         <v/>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="26">
         <f>$B$5</f>
         <v/>
       </c>
@@ -3394,19 +3639,19 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="29">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="29">
         <f>0.5*(B18+B19)*E19</f>
         <v/>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="29">
         <f>F19-(H19-H18)</f>
         <v/>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="36">
         <f>MAX(0,H18+0.5*(D18+D19)*E19)</f>
         <v/>
       </c>
@@ -3414,9 +3659,17 @@
         <f>IF(H19&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J19" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,B19/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="K19" s="27">
+        <f>IF(Parametres!$C$88&lt;=0,0,C19/Parametres!$C$88)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="26">
+      <c r="A20" s="29">
         <f>Calcul_A!A18</f>
         <v/>
       </c>
@@ -3424,7 +3677,7 @@
         <f>Calcul_A!C18</f>
         <v/>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="26">
         <f>$B$5</f>
         <v/>
       </c>
@@ -3432,19 +3685,19 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="29">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="29">
         <f>0.5*(B19+B20)*E20</f>
         <v/>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="29">
         <f>F20-(H20-H19)</f>
         <v/>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="36">
         <f>MAX(0,H19+0.5*(D19+D20)*E20)</f>
         <v/>
       </c>
@@ -3452,9 +3705,17 @@
         <f>IF(H20&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J20" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,B20/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="K20" s="27">
+        <f>IF(Parametres!$C$88&lt;=0,0,C20/Parametres!$C$88)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="26">
+      <c r="A21" s="29">
         <f>Calcul_A!A19</f>
         <v/>
       </c>
@@ -3462,7 +3723,7 @@
         <f>Calcul_A!C19</f>
         <v/>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="26">
         <f>$B$5</f>
         <v/>
       </c>
@@ -3470,19 +3731,19 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="29">
         <f>(A21-A20)*60</f>
         <v/>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="29">
         <f>0.5*(B20+B21)*E21</f>
         <v/>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="29">
         <f>F21-(H21-H20)</f>
         <v/>
       </c>
-      <c r="H21" s="34">
+      <c r="H21" s="36">
         <f>MAX(0,H20+0.5*(D20+D21)*E21)</f>
         <v/>
       </c>
@@ -3490,9 +3751,17 @@
         <f>IF(H21&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J21" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,B21/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="K21" s="27">
+        <f>IF(Parametres!$C$88&lt;=0,0,C21/Parametres!$C$88)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="26">
+      <c r="A22" s="29">
         <f>Calcul_A!A20</f>
         <v/>
       </c>
@@ -3500,7 +3769,7 @@
         <f>Calcul_A!C20</f>
         <v/>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="26">
         <f>$B$5</f>
         <v/>
       </c>
@@ -3508,24 +3777,32 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="29">
         <f>(A22-A21)*60</f>
         <v/>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="29">
         <f>0.5*(B21+B22)*E22</f>
         <v/>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="29">
         <f>F22-(H22-H21)</f>
         <v/>
       </c>
-      <c r="H22" s="34">
+      <c r="H22" s="36">
         <f>MAX(0,H21+0.5*(D21+D22)*E22)</f>
         <v/>
       </c>
       <c r="I22" s="4">
         <f>IF(H22&gt;0.5,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="J22" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,B22/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="K22" s="27">
+        <f>IF(Parametres!$C$88&lt;=0,0,C22/Parametres!$C$88)</f>
         <v/>
       </c>
     </row>
@@ -3550,7 +3827,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="47" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>Où sont les fichiers HY-8 / capacité ?</t>
         </is>
@@ -3683,7 +3960,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>Méthode — volume de rétention</t>
         </is>
@@ -3845,7 +4122,7 @@
           <t>t pointe (min)</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="28" t="n">
         <v>22.5</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -3877,10 +4154,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="B8" s="27" t="n">
+      <c r="B8" s="30" t="n">
         <v>0.081042</v>
       </c>
       <c r="C8" s="5">
@@ -3894,10 +4171,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="27" t="n">
+      <c r="B9" s="30" t="n">
         <v>0.121875</v>
       </c>
       <c r="C9" s="5">
@@ -3907,10 +4184,10 @@
       <c r="D9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B10" s="27" t="n">
+      <c r="B10" s="30" t="n">
         <v>0.193438</v>
       </c>
       <c r="C10" s="5">
@@ -3920,10 +4197,10 @@
       <c r="D10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="n">
+      <c r="A11" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="B11" s="27" t="n">
+      <c r="B11" s="30" t="n">
         <v>0.333542</v>
       </c>
       <c r="C11" s="5">
@@ -3933,10 +4210,10 @@
       <c r="D11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="n">
+      <c r="A12" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="B12" s="27" t="n">
+      <c r="B12" s="30" t="n">
         <v>0.657188</v>
       </c>
       <c r="C12" s="5">
@@ -3946,10 +4223,10 @@
       <c r="D12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="n">
+      <c r="A13" s="29" t="n">
         <v>22.5</v>
       </c>
-      <c r="B13" s="27" t="n">
+      <c r="B13" s="30" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="8">
@@ -3963,10 +4240,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="n">
+      <c r="A14" s="29" t="n">
         <v>27.5</v>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="30" t="n">
         <v>0.608958</v>
       </c>
       <c r="C14" s="5">
@@ -3976,10 +4253,10 @@
       <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="n">
+      <c r="A15" s="29" t="n">
         <v>32.5</v>
       </c>
-      <c r="B15" s="27" t="n">
+      <c r="B15" s="30" t="n">
         <v>0.401771</v>
       </c>
       <c r="C15" s="5">
@@ -3989,10 +4266,10 @@
       <c r="D15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="n">
+      <c r="A16" s="29" t="n">
         <v>37.5</v>
       </c>
-      <c r="B16" s="27" t="n">
+      <c r="B16" s="30" t="n">
         <v>0.280104</v>
       </c>
       <c r="C16" s="5">
@@ -4002,10 +4279,10 @@
       <c r="D16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="n">
+      <c r="A17" s="29" t="n">
         <v>42.5</v>
       </c>
-      <c r="B17" s="27" t="n">
+      <c r="B17" s="30" t="n">
         <v>0.203438</v>
       </c>
       <c r="C17" s="5">
@@ -4015,10 +4292,10 @@
       <c r="D17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="n">
+      <c r="A18" s="29" t="n">
         <v>47.5</v>
       </c>
-      <c r="B18" s="27" t="n">
+      <c r="B18" s="30" t="n">
         <v>0.152292</v>
       </c>
       <c r="C18" s="5">
@@ -4028,10 +4305,10 @@
       <c r="D18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="n">
+      <c r="A19" s="29" t="n">
         <v>52.5</v>
       </c>
-      <c r="B19" s="27" t="n">
+      <c r="B19" s="30" t="n">
         <v>0.116771</v>
       </c>
       <c r="C19" s="5">
@@ -4041,10 +4318,10 @@
       <c r="D19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="n">
+      <c r="A20" s="29" t="n">
         <v>57.5</v>
       </c>
-      <c r="B20" s="27" t="n">
+      <c r="B20" s="30" t="n">
         <v>0.091146</v>
       </c>
       <c r="C20" s="5">
@@ -4059,7 +4336,7 @@
           <t>Qin max (contrôle)</t>
         </is>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="31">
         <f>MAX(C8:C20)</f>
         <v/>
       </c>
@@ -4075,7 +4352,7 @@
           <t>Qcap Ø900 (réf.)</t>
         </is>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="32">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -4095,7 +4372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4107,6 +4384,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4122,7 +4400,7 @@
           <t>Qout (m³/s)</t>
         </is>
       </c>
-      <c r="B2" s="30">
+      <c r="B2" s="33">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -4133,13 +4411,20 @@
           <t>Vmax (m³)</t>
         </is>
       </c>
-      <c r="B3" s="31">
+      <c r="B3" s="34">
         <f>MAX(H8:H20)</f>
         <v/>
       </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Maximum du volume stocké cumulé</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>V_Ø900 = Qout / A_plein Ø900 (Parametres C87)</t>
         </is>
       </c>
     </row>
@@ -4213,9 +4498,14 @@
           <t>Stockage?</t>
         </is>
       </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>V_Ø900 (m/s)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="26">
+      <c r="A8" s="29">
         <f>Hydrogramme!A8</f>
         <v/>
       </c>
@@ -4223,7 +4513,7 @@
         <f>Hydrogramme!C8</f>
         <v/>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="26">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4240,16 +4530,20 @@
       <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="33" t="n">
+      <c r="H8" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="4">
         <f>IF(H8&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J8" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,C8/Parametres!$C$87)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="26">
+      <c r="A9" s="29">
         <f>Hydrogramme!A9</f>
         <v/>
       </c>
@@ -4257,7 +4551,7 @@
         <f>Hydrogramme!C9</f>
         <v/>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="26">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4265,19 +4559,19 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="29">
         <f>(A9-A8)*60</f>
         <v/>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="29">
         <f>0.5*(B8+B9)*E9</f>
         <v/>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="29">
         <f>F9-(H9-H8)</f>
         <v/>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="36">
         <f>MAX(0,H8+0.5*(D8+D9)*E9)</f>
         <v/>
       </c>
@@ -4285,9 +4579,13 @@
         <f>IF(H9&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J9" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,C9/Parametres!$C$87)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="26">
+      <c r="A10" s="29">
         <f>Hydrogramme!A10</f>
         <v/>
       </c>
@@ -4295,7 +4593,7 @@
         <f>Hydrogramme!C10</f>
         <v/>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="26">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4303,19 +4601,19 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="29">
         <f>(A10-A9)*60</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="29">
         <f>0.5*(B9+B10)*E10</f>
         <v/>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="29">
         <f>F10-(H10-H9)</f>
         <v/>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="36">
         <f>MAX(0,H9+0.5*(D9+D10)*E10)</f>
         <v/>
       </c>
@@ -4323,9 +4621,13 @@
         <f>IF(H10&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J10" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,C10/Parametres!$C$87)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="26">
+      <c r="A11" s="29">
         <f>Hydrogramme!A11</f>
         <v/>
       </c>
@@ -4333,7 +4635,7 @@
         <f>Hydrogramme!C11</f>
         <v/>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="26">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4341,19 +4643,19 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="29">
         <f>(A11-A10)*60</f>
         <v/>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="29">
         <f>0.5*(B10+B11)*E11</f>
         <v/>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="29">
         <f>F11-(H11-H10)</f>
         <v/>
       </c>
-      <c r="H11" s="34">
+      <c r="H11" s="36">
         <f>MAX(0,H10+0.5*(D10+D11)*E11)</f>
         <v/>
       </c>
@@ -4361,9 +4663,13 @@
         <f>IF(H11&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J11" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,C11/Parametres!$C$87)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="26">
+      <c r="A12" s="29">
         <f>Hydrogramme!A12</f>
         <v/>
       </c>
@@ -4371,7 +4677,7 @@
         <f>Hydrogramme!C12</f>
         <v/>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="26">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4379,19 +4685,19 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="29">
         <f>(A12-A11)*60</f>
         <v/>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="29">
         <f>0.5*(B11+B12)*E12</f>
         <v/>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="29">
         <f>F12-(H12-H11)</f>
         <v/>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="36">
         <f>MAX(0,H11+0.5*(D11+D12)*E12)</f>
         <v/>
       </c>
@@ -4399,9 +4705,13 @@
         <f>IF(H12&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J12" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,C12/Parametres!$C$87)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="26">
+      <c r="A13" s="29">
         <f>Hydrogramme!A13</f>
         <v/>
       </c>
@@ -4409,7 +4719,7 @@
         <f>Hydrogramme!C13</f>
         <v/>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="26">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4417,19 +4727,19 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="29">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="29">
         <f>0.5*(B12+B13)*E13</f>
         <v/>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="29">
         <f>F13-(H13-H12)</f>
         <v/>
       </c>
-      <c r="H13" s="34">
+      <c r="H13" s="36">
         <f>MAX(0,H12+0.5*(D12+D13)*E13)</f>
         <v/>
       </c>
@@ -4437,9 +4747,13 @@
         <f>IF(H13&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J13" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,C13/Parametres!$C$87)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="26">
+      <c r="A14" s="29">
         <f>Hydrogramme!A14</f>
         <v/>
       </c>
@@ -4447,7 +4761,7 @@
         <f>Hydrogramme!C14</f>
         <v/>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="26">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4455,19 +4769,19 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="29">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="29">
         <f>0.5*(B13+B14)*E14</f>
         <v/>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="29">
         <f>F14-(H14-H13)</f>
         <v/>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="36">
         <f>MAX(0,H13+0.5*(D13+D14)*E14)</f>
         <v/>
       </c>
@@ -4475,9 +4789,13 @@
         <f>IF(H14&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J14" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,C14/Parametres!$C$87)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="26">
+      <c r="A15" s="29">
         <f>Hydrogramme!A15</f>
         <v/>
       </c>
@@ -4485,7 +4803,7 @@
         <f>Hydrogramme!C15</f>
         <v/>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="26">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4493,19 +4811,19 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="29">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="29">
         <f>0.5*(B14+B15)*E15</f>
         <v/>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="29">
         <f>F15-(H15-H14)</f>
         <v/>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="36">
         <f>MAX(0,H14+0.5*(D14+D15)*E15)</f>
         <v/>
       </c>
@@ -4513,9 +4831,13 @@
         <f>IF(H15&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J15" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,C15/Parametres!$C$87)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="26">
+      <c r="A16" s="29">
         <f>Hydrogramme!A16</f>
         <v/>
       </c>
@@ -4523,7 +4845,7 @@
         <f>Hydrogramme!C16</f>
         <v/>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="26">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4531,19 +4853,19 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="29">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="29">
         <f>0.5*(B15+B16)*E16</f>
         <v/>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="29">
         <f>F16-(H16-H15)</f>
         <v/>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="36">
         <f>MAX(0,H15+0.5*(D15+D16)*E16)</f>
         <v/>
       </c>
@@ -4551,9 +4873,13 @@
         <f>IF(H16&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J16" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,C16/Parametres!$C$87)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="26">
+      <c r="A17" s="29">
         <f>Hydrogramme!A17</f>
         <v/>
       </c>
@@ -4561,7 +4887,7 @@
         <f>Hydrogramme!C17</f>
         <v/>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="26">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4569,19 +4895,19 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="29">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="29">
         <f>0.5*(B16+B17)*E17</f>
         <v/>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="29">
         <f>F17-(H17-H16)</f>
         <v/>
       </c>
-      <c r="H17" s="34">
+      <c r="H17" s="36">
         <f>MAX(0,H16+0.5*(D16+D17)*E17)</f>
         <v/>
       </c>
@@ -4589,9 +4915,13 @@
         <f>IF(H17&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J17" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,C17/Parametres!$C$87)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="26">
+      <c r="A18" s="29">
         <f>Hydrogramme!A18</f>
         <v/>
       </c>
@@ -4599,7 +4929,7 @@
         <f>Hydrogramme!C18</f>
         <v/>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="26">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4607,19 +4937,19 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="29">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="29">
         <f>0.5*(B17+B18)*E18</f>
         <v/>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="29">
         <f>F18-(H18-H17)</f>
         <v/>
       </c>
-      <c r="H18" s="34">
+      <c r="H18" s="36">
         <f>MAX(0,H17+0.5*(D17+D18)*E18)</f>
         <v/>
       </c>
@@ -4627,9 +4957,13 @@
         <f>IF(H18&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J18" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,C18/Parametres!$C$87)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="26">
+      <c r="A19" s="29">
         <f>Hydrogramme!A19</f>
         <v/>
       </c>
@@ -4637,7 +4971,7 @@
         <f>Hydrogramme!C19</f>
         <v/>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="26">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4645,19 +4979,19 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="29">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="29">
         <f>0.5*(B18+B19)*E19</f>
         <v/>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="29">
         <f>F19-(H19-H18)</f>
         <v/>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="36">
         <f>MAX(0,H18+0.5*(D18+D19)*E19)</f>
         <v/>
       </c>
@@ -4665,9 +4999,13 @@
         <f>IF(H19&gt;0.5,"oui","non")</f>
         <v/>
       </c>
+      <c r="J19" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,C19/Parametres!$C$87)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="26">
+      <c r="A20" s="29">
         <f>Hydrogramme!A20</f>
         <v/>
       </c>
@@ -4675,7 +5013,7 @@
         <f>Hydrogramme!C20</f>
         <v/>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="26">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4683,24 +5021,28 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="29">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="29">
         <f>0.5*(B19+B20)*E20</f>
         <v/>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="29">
         <f>F20-(H20-H19)</f>
         <v/>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="36">
         <f>MAX(0,H19+0.5*(D19+D20)*E20)</f>
         <v/>
       </c>
       <c r="I20" s="4">
         <f>IF(H20&gt;0.5,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="J20" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,C20/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -4719,12 +5061,14 @@
   <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4769,32 +5113,32 @@
           <t>béton typ. 0.012–0.015</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>entrée</t>
         </is>
       </c>
-      <c r="F6" s="35" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="G6" s="35" t="inlineStr">
+      <c r="G6" s="37" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H6" s="35" t="inlineStr">
+      <c r="H6" s="37" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I6" s="35" t="inlineStr">
+      <c r="I6" s="37" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J6" s="35" t="inlineStr">
+      <c r="J6" s="37" t="inlineStr">
         <is>
           <t>Ke</t>
         </is>
@@ -4910,7 +5254,7 @@
           <t>S0 = (Zin-Zout)/L</t>
         </is>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="38">
         <f>(B9-B10)/B8</f>
         <v/>
       </c>
@@ -4941,7 +5285,7 @@
           <t>Entrée (texte exact)</t>
         </is>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>square_edge</t>
         </is>
@@ -4958,7 +5302,7 @@
           <t>Q_plein Manning (réf.)</t>
         </is>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="31">
         <f>(1/B6)*(PI()*B7^2/4)*((B7/4)^(2/3))*SQRT(B11)</f>
         <v/>
       </c>
@@ -4974,7 +5318,7 @@
           <t>K (lu)</t>
         </is>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="40">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,2,FALSE),0.0098)</f>
         <v/>
       </c>
@@ -4985,7 +5329,7 @@
           <t>M (lu)</t>
         </is>
       </c>
-      <c r="B18" s="38">
+      <c r="B18" s="40">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,3,FALSE),2)</f>
         <v/>
       </c>
@@ -4996,7 +5340,7 @@
           <t>c (lu)</t>
         </is>
       </c>
-      <c r="B19" s="38">
+      <c r="B19" s="40">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,4,FALSE),0.0398)</f>
         <v/>
       </c>
@@ -5007,7 +5351,7 @@
           <t>Y (lu)</t>
         </is>
       </c>
-      <c r="B20" s="38">
+      <c r="B20" s="40">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,5,FALSE),0.67)</f>
         <v/>
       </c>
@@ -5018,9 +5362,16 @@
           <t>Ke (lu)</t>
         </is>
       </c>
-      <c r="B21" s="38">
+      <c r="B21" s="40">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,6,FALSE),0.5)</f>
         <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>V_gouv = Q_gouvernant / A_ecoul (segment circulaire si HW&lt;D, sinon A_plein)</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -5054,12 +5405,22 @@
           <t>Contrôle</t>
         </is>
       </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>A_ecoul (m²)</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>V_gouv (m/s)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="n">
+      <c r="A24" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="26">
         <f>$B$9+A24</f>
         <v/>
       </c>
@@ -5079,12 +5440,20 @@
         <f>IF(A24&lt;=0,"—",IF(C24&lt;=D24,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G24" s="5">
+        <f>IF(A24&lt;=0,0,IF(A24&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A24/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A24/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H24" s="27">
+        <f>IF(G24&lt;=0,0,E24/G24)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="n">
+      <c r="A25" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="26">
         <f>$B$9+A25</f>
         <v/>
       </c>
@@ -5104,12 +5473,20 @@
         <f>IF(A25&lt;=0,"—",IF(C25&lt;=D25,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G25" s="5">
+        <f>IF(A25&lt;=0,0,IF(A25&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A25/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A25/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H25" s="27">
+        <f>IF(G25&lt;=0,0,E25/G25)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="32" t="n">
+      <c r="A26" s="26" t="n">
         <v>0.1</v>
       </c>
-      <c r="B26" s="32">
+      <c r="B26" s="26">
         <f>$B$9+A26</f>
         <v/>
       </c>
@@ -5129,12 +5506,20 @@
         <f>IF(A26&lt;=0,"—",IF(C26&lt;=D26,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G26" s="5">
+        <f>IF(A26&lt;=0,0,IF(A26&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A26/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A26/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H26" s="27">
+        <f>IF(G26&lt;=0,0,E26/G26)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="n">
+      <c r="A27" s="26" t="n">
         <v>0.15</v>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="26">
         <f>$B$9+A27</f>
         <v/>
       </c>
@@ -5154,12 +5539,20 @@
         <f>IF(A27&lt;=0,"—",IF(C27&lt;=D27,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G27" s="5">
+        <f>IF(A27&lt;=0,0,IF(A27&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A27/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A27/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H27" s="27">
+        <f>IF(G27&lt;=0,0,E27/G27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="n">
+      <c r="A28" s="26" t="n">
         <v>0.2</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="26">
         <f>$B$9+A28</f>
         <v/>
       </c>
@@ -5179,12 +5572,20 @@
         <f>IF(A28&lt;=0,"—",IF(C28&lt;=D28,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G28" s="5">
+        <f>IF(A28&lt;=0,0,IF(A28&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A28/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A28/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H28" s="27">
+        <f>IF(G28&lt;=0,0,E28/G28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="n">
+      <c r="A29" s="26" t="n">
         <v>0.25</v>
       </c>
-      <c r="B29" s="32">
+      <c r="B29" s="26">
         <f>$B$9+A29</f>
         <v/>
       </c>
@@ -5204,12 +5605,20 @@
         <f>IF(A29&lt;=0,"—",IF(C29&lt;=D29,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G29" s="5">
+        <f>IF(A29&lt;=0,0,IF(A29&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A29/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A29/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H29" s="27">
+        <f>IF(G29&lt;=0,0,E29/G29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="n">
+      <c r="A30" s="26" t="n">
         <v>0.3</v>
       </c>
-      <c r="B30" s="32">
+      <c r="B30" s="26">
         <f>$B$9+A30</f>
         <v/>
       </c>
@@ -5229,12 +5638,20 @@
         <f>IF(A30&lt;=0,"—",IF(C30&lt;=D30,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G30" s="5">
+        <f>IF(A30&lt;=0,0,IF(A30&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A30/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A30/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H30" s="27">
+        <f>IF(G30&lt;=0,0,E30/G30)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="32" t="n">
+      <c r="A31" s="26" t="n">
         <v>0.35</v>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="26">
         <f>$B$9+A31</f>
         <v/>
       </c>
@@ -5254,12 +5671,20 @@
         <f>IF(A31&lt;=0,"—",IF(C31&lt;=D31,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G31" s="5">
+        <f>IF(A31&lt;=0,0,IF(A31&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A31/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A31/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H31" s="27">
+        <f>IF(G31&lt;=0,0,E31/G31)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="n">
+      <c r="A32" s="26" t="n">
         <v>0.4</v>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="26">
         <f>$B$9+A32</f>
         <v/>
       </c>
@@ -5279,12 +5704,20 @@
         <f>IF(A32&lt;=0,"—",IF(C32&lt;=D32,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G32" s="5">
+        <f>IF(A32&lt;=0,0,IF(A32&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A32/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A32/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H32" s="27">
+        <f>IF(G32&lt;=0,0,E32/G32)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="32" t="n">
+      <c r="A33" s="26" t="n">
         <v>0.45</v>
       </c>
-      <c r="B33" s="32">
+      <c r="B33" s="26">
         <f>$B$9+A33</f>
         <v/>
       </c>
@@ -5304,12 +5737,20 @@
         <f>IF(A33&lt;=0,"—",IF(C33&lt;=D33,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G33" s="5">
+        <f>IF(A33&lt;=0,0,IF(A33&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A33/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A33/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H33" s="27">
+        <f>IF(G33&lt;=0,0,E33/G33)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="32" t="n">
+      <c r="A34" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="B34" s="32">
+      <c r="B34" s="26">
         <f>$B$9+A34</f>
         <v/>
       </c>
@@ -5329,12 +5770,20 @@
         <f>IF(A34&lt;=0,"—",IF(C34&lt;=D34,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G34" s="5">
+        <f>IF(A34&lt;=0,0,IF(A34&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A34/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A34/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H34" s="27">
+        <f>IF(G34&lt;=0,0,E34/G34)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="32" t="n">
+      <c r="A35" s="26" t="n">
         <v>0.55</v>
       </c>
-      <c r="B35" s="32">
+      <c r="B35" s="26">
         <f>$B$9+A35</f>
         <v/>
       </c>
@@ -5354,12 +5803,20 @@
         <f>IF(A35&lt;=0,"—",IF(C35&lt;=D35,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G35" s="5">
+        <f>IF(A35&lt;=0,0,IF(A35&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A35/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A35/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H35" s="27">
+        <f>IF(G35&lt;=0,0,E35/G35)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="32" t="n">
+      <c r="A36" s="26" t="n">
         <v>0.6</v>
       </c>
-      <c r="B36" s="32">
+      <c r="B36" s="26">
         <f>$B$9+A36</f>
         <v/>
       </c>
@@ -5379,12 +5836,20 @@
         <f>IF(A36&lt;=0,"—",IF(C36&lt;=D36,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G36" s="5">
+        <f>IF(A36&lt;=0,0,IF(A36&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A36/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A36/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H36" s="27">
+        <f>IF(G36&lt;=0,0,E36/G36)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="32" t="n">
+      <c r="A37" s="26" t="n">
         <v>0.65</v>
       </c>
-      <c r="B37" s="32">
+      <c r="B37" s="26">
         <f>$B$9+A37</f>
         <v/>
       </c>
@@ -5404,12 +5869,20 @@
         <f>IF(A37&lt;=0,"—",IF(C37&lt;=D37,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G37" s="5">
+        <f>IF(A37&lt;=0,0,IF(A37&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A37/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A37/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H37" s="27">
+        <f>IF(G37&lt;=0,0,E37/G37)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="n">
+      <c r="A38" s="26" t="n">
         <v>0.7</v>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="26">
         <f>$B$9+A38</f>
         <v/>
       </c>
@@ -5429,12 +5902,20 @@
         <f>IF(A38&lt;=0,"—",IF(C38&lt;=D38,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G38" s="5">
+        <f>IF(A38&lt;=0,0,IF(A38&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A38/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A38/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H38" s="27">
+        <f>IF(G38&lt;=0,0,E38/G38)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="32" t="n">
+      <c r="A39" s="26" t="n">
         <v>0.75</v>
       </c>
-      <c r="B39" s="32">
+      <c r="B39" s="26">
         <f>$B$9+A39</f>
         <v/>
       </c>
@@ -5454,12 +5935,20 @@
         <f>IF(A39&lt;=0,"—",IF(C39&lt;=D39,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G39" s="5">
+        <f>IF(A39&lt;=0,0,IF(A39&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A39/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A39/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H39" s="27">
+        <f>IF(G39&lt;=0,0,E39/G39)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="32" t="n">
+      <c r="A40" s="26" t="n">
         <v>0.8</v>
       </c>
-      <c r="B40" s="32">
+      <c r="B40" s="26">
         <f>$B$9+A40</f>
         <v/>
       </c>
@@ -5479,12 +5968,20 @@
         <f>IF(A40&lt;=0,"—",IF(C40&lt;=D40,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G40" s="5">
+        <f>IF(A40&lt;=0,0,IF(A40&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A40/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A40/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H40" s="27">
+        <f>IF(G40&lt;=0,0,E40/G40)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="32" t="n">
+      <c r="A41" s="26" t="n">
         <v>0.85</v>
       </c>
-      <c r="B41" s="32">
+      <c r="B41" s="26">
         <f>$B$9+A41</f>
         <v/>
       </c>
@@ -5504,12 +6001,20 @@
         <f>IF(A41&lt;=0,"—",IF(C41&lt;=D41,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G41" s="5">
+        <f>IF(A41&lt;=0,0,IF(A41&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A41/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A41/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H41" s="27">
+        <f>IF(G41&lt;=0,0,E41/G41)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="32" t="n">
+      <c r="A42" s="26" t="n">
         <v>0.9</v>
       </c>
-      <c r="B42" s="32">
+      <c r="B42" s="26">
         <f>$B$9+A42</f>
         <v/>
       </c>
@@ -5529,12 +6034,20 @@
         <f>IF(A42&lt;=0,"—",IF(C42&lt;=D42,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G42" s="5">
+        <f>IF(A42&lt;=0,0,IF(A42&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A42/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A42/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H42" s="27">
+        <f>IF(G42&lt;=0,0,E42/G42)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="32" t="n">
+      <c r="A43" s="26" t="n">
         <v>0.95</v>
       </c>
-      <c r="B43" s="32">
+      <c r="B43" s="26">
         <f>$B$9+A43</f>
         <v/>
       </c>
@@ -5554,12 +6067,20 @@
         <f>IF(A43&lt;=0,"—",IF(C43&lt;=D43,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G43" s="5">
+        <f>IF(A43&lt;=0,0,IF(A43&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A43/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A43/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H43" s="27">
+        <f>IF(G43&lt;=0,0,E43/G43)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="32" t="n">
+      <c r="A44" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="B44" s="32">
+      <c r="B44" s="26">
         <f>$B$9+A44</f>
         <v/>
       </c>
@@ -5579,12 +6100,20 @@
         <f>IF(A44&lt;=0,"—",IF(C44&lt;=D44,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G44" s="5">
+        <f>IF(A44&lt;=0,0,IF(A44&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A44/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A44/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H44" s="27">
+        <f>IF(G44&lt;=0,0,E44/G44)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="32" t="n">
+      <c r="A45" s="26" t="n">
         <v>1.05</v>
       </c>
-      <c r="B45" s="32">
+      <c r="B45" s="26">
         <f>$B$9+A45</f>
         <v/>
       </c>
@@ -5604,12 +6133,20 @@
         <f>IF(A45&lt;=0,"—",IF(C45&lt;=D45,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G45" s="5">
+        <f>IF(A45&lt;=0,0,IF(A45&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A45/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A45/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H45" s="27">
+        <f>IF(G45&lt;=0,0,E45/G45)</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="32" t="n">
+      <c r="A46" s="26" t="n">
         <v>1.1</v>
       </c>
-      <c r="B46" s="32">
+      <c r="B46" s="26">
         <f>$B$9+A46</f>
         <v/>
       </c>
@@ -5629,12 +6166,20 @@
         <f>IF(A46&lt;=0,"—",IF(C46&lt;=D46,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G46" s="5">
+        <f>IF(A46&lt;=0,0,IF(A46&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A46/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A46/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H46" s="27">
+        <f>IF(G46&lt;=0,0,E46/G46)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="32" t="n">
+      <c r="A47" s="26" t="n">
         <v>1.15</v>
       </c>
-      <c r="B47" s="32">
+      <c r="B47" s="26">
         <f>$B$9+A47</f>
         <v/>
       </c>
@@ -5654,12 +6199,20 @@
         <f>IF(A47&lt;=0,"—",IF(C47&lt;=D47,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G47" s="5">
+        <f>IF(A47&lt;=0,0,IF(A47&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A47/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A47/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H47" s="27">
+        <f>IF(G47&lt;=0,0,E47/G47)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="32" t="n">
+      <c r="A48" s="26" t="n">
         <v>1.2</v>
       </c>
-      <c r="B48" s="32">
+      <c r="B48" s="26">
         <f>$B$9+A48</f>
         <v/>
       </c>
@@ -5679,12 +6232,20 @@
         <f>IF(A48&lt;=0,"—",IF(C48&lt;=D48,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G48" s="5">
+        <f>IF(A48&lt;=0,0,IF(A48&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A48/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A48/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H48" s="27">
+        <f>IF(G48&lt;=0,0,E48/G48)</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="32" t="n">
+      <c r="A49" s="26" t="n">
         <v>1.25</v>
       </c>
-      <c r="B49" s="32">
+      <c r="B49" s="26">
         <f>$B$9+A49</f>
         <v/>
       </c>
@@ -5704,12 +6265,20 @@
         <f>IF(A49&lt;=0,"—",IF(C49&lt;=D49,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G49" s="5">
+        <f>IF(A49&lt;=0,0,IF(A49&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A49/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A49/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H49" s="27">
+        <f>IF(G49&lt;=0,0,E49/G49)</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="32" t="n">
+      <c r="A50" s="26" t="n">
         <v>1.3</v>
       </c>
-      <c r="B50" s="32">
+      <c r="B50" s="26">
         <f>$B$9+A50</f>
         <v/>
       </c>
@@ -5729,12 +6298,20 @@
         <f>IF(A50&lt;=0,"—",IF(C50&lt;=D50,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G50" s="5">
+        <f>IF(A50&lt;=0,0,IF(A50&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A50/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A50/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H50" s="27">
+        <f>IF(G50&lt;=0,0,E50/G50)</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="32" t="n">
+      <c r="A51" s="26" t="n">
         <v>1.35</v>
       </c>
-      <c r="B51" s="32">
+      <c r="B51" s="26">
         <f>$B$9+A51</f>
         <v/>
       </c>
@@ -5754,12 +6331,20 @@
         <f>IF(A51&lt;=0,"—",IF(C51&lt;=D51,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G51" s="5">
+        <f>IF(A51&lt;=0,0,IF(A51&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A51/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A51/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H51" s="27">
+        <f>IF(G51&lt;=0,0,E51/G51)</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="32" t="n">
+      <c r="A52" s="26" t="n">
         <v>1.4</v>
       </c>
-      <c r="B52" s="32">
+      <c r="B52" s="26">
         <f>$B$9+A52</f>
         <v/>
       </c>
@@ -5779,12 +6364,20 @@
         <f>IF(A52&lt;=0,"—",IF(C52&lt;=D52,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G52" s="5">
+        <f>IF(A52&lt;=0,0,IF(A52&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A52/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A52/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H52" s="27">
+        <f>IF(G52&lt;=0,0,E52/G52)</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="32" t="n">
+      <c r="A53" s="26" t="n">
         <v>1.45</v>
       </c>
-      <c r="B53" s="32">
+      <c r="B53" s="26">
         <f>$B$9+A53</f>
         <v/>
       </c>
@@ -5804,12 +6397,20 @@
         <f>IF(A53&lt;=0,"—",IF(C53&lt;=D53,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G53" s="5">
+        <f>IF(A53&lt;=0,0,IF(A53&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A53/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A53/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H53" s="27">
+        <f>IF(G53&lt;=0,0,E53/G53)</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="32" t="n">
+      <c r="A54" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="B54" s="32">
+      <c r="B54" s="26">
         <f>$B$9+A54</f>
         <v/>
       </c>
@@ -5829,12 +6430,20 @@
         <f>IF(A54&lt;=0,"—",IF(C54&lt;=D54,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G54" s="5">
+        <f>IF(A54&lt;=0,0,IF(A54&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A54/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A54/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H54" s="27">
+        <f>IF(G54&lt;=0,0,E54/G54)</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="32" t="n">
+      <c r="A55" s="26" t="n">
         <v>1.55</v>
       </c>
-      <c r="B55" s="32">
+      <c r="B55" s="26">
         <f>$B$9+A55</f>
         <v/>
       </c>
@@ -5854,12 +6463,20 @@
         <f>IF(A55&lt;=0,"—",IF(C55&lt;=D55,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G55" s="5">
+        <f>IF(A55&lt;=0,0,IF(A55&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A55/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A55/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H55" s="27">
+        <f>IF(G55&lt;=0,0,E55/G55)</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="32" t="n">
+      <c r="A56" s="26" t="n">
         <v>1.6</v>
       </c>
-      <c r="B56" s="32">
+      <c r="B56" s="26">
         <f>$B$9+A56</f>
         <v/>
       </c>
@@ -5879,12 +6496,20 @@
         <f>IF(A56&lt;=0,"—",IF(C56&lt;=D56,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G56" s="5">
+        <f>IF(A56&lt;=0,0,IF(A56&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A56/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A56/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H56" s="27">
+        <f>IF(G56&lt;=0,0,E56/G56)</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="32" t="n">
+      <c r="A57" s="26" t="n">
         <v>1.65</v>
       </c>
-      <c r="B57" s="32">
+      <c r="B57" s="26">
         <f>$B$9+A57</f>
         <v/>
       </c>
@@ -5904,12 +6529,20 @@
         <f>IF(A57&lt;=0,"—",IF(C57&lt;=D57,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G57" s="5">
+        <f>IF(A57&lt;=0,0,IF(A57&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A57/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A57/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H57" s="27">
+        <f>IF(G57&lt;=0,0,E57/G57)</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="32" t="n">
+      <c r="A58" s="26" t="n">
         <v>1.7</v>
       </c>
-      <c r="B58" s="32">
+      <c r="B58" s="26">
         <f>$B$9+A58</f>
         <v/>
       </c>
@@ -5929,12 +6562,20 @@
         <f>IF(A58&lt;=0,"—",IF(C58&lt;=D58,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G58" s="5">
+        <f>IF(A58&lt;=0,0,IF(A58&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A58/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A58/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H58" s="27">
+        <f>IF(G58&lt;=0,0,E58/G58)</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="32" t="n">
+      <c r="A59" s="26" t="n">
         <v>1.75</v>
       </c>
-      <c r="B59" s="32">
+      <c r="B59" s="26">
         <f>$B$9+A59</f>
         <v/>
       </c>
@@ -5954,12 +6595,20 @@
         <f>IF(A59&lt;=0,"—",IF(C59&lt;=D59,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G59" s="5">
+        <f>IF(A59&lt;=0,0,IF(A59&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A59/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A59/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H59" s="27">
+        <f>IF(G59&lt;=0,0,E59/G59)</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="32" t="n">
+      <c r="A60" s="26" t="n">
         <v>1.8</v>
       </c>
-      <c r="B60" s="32">
+      <c r="B60" s="26">
         <f>$B$9+A60</f>
         <v/>
       </c>
@@ -5979,12 +6628,20 @@
         <f>IF(A60&lt;=0,"—",IF(C60&lt;=D60,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G60" s="5">
+        <f>IF(A60&lt;=0,0,IF(A60&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A60/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A60/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H60" s="27">
+        <f>IF(G60&lt;=0,0,E60/G60)</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="32" t="n">
+      <c r="A61" s="26" t="n">
         <v>1.85</v>
       </c>
-      <c r="B61" s="32">
+      <c r="B61" s="26">
         <f>$B$9+A61</f>
         <v/>
       </c>
@@ -6004,12 +6661,20 @@
         <f>IF(A61&lt;=0,"—",IF(C61&lt;=D61,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G61" s="5">
+        <f>IF(A61&lt;=0,0,IF(A61&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A61/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A61/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H61" s="27">
+        <f>IF(G61&lt;=0,0,E61/G61)</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="32" t="n">
+      <c r="A62" s="26" t="n">
         <v>1.9</v>
       </c>
-      <c r="B62" s="32">
+      <c r="B62" s="26">
         <f>$B$9+A62</f>
         <v/>
       </c>
@@ -6029,12 +6694,20 @@
         <f>IF(A62&lt;=0,"—",IF(C62&lt;=D62,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G62" s="5">
+        <f>IF(A62&lt;=0,0,IF(A62&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A62/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A62/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H62" s="27">
+        <f>IF(G62&lt;=0,0,E62/G62)</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="32" t="n">
+      <c r="A63" s="26" t="n">
         <v>1.95</v>
       </c>
-      <c r="B63" s="32">
+      <c r="B63" s="26">
         <f>$B$9+A63</f>
         <v/>
       </c>
@@ -6054,12 +6727,20 @@
         <f>IF(A63&lt;=0,"—",IF(C63&lt;=D63,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G63" s="5">
+        <f>IF(A63&lt;=0,0,IF(A63&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A63/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A63/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H63" s="27">
+        <f>IF(G63&lt;=0,0,E63/G63)</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="32" t="n">
+      <c r="A64" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B64" s="32">
+      <c r="B64" s="26">
         <f>$B$9+A64</f>
         <v/>
       </c>
@@ -6079,12 +6760,20 @@
         <f>IF(A64&lt;=0,"—",IF(C64&lt;=D64,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G64" s="5">
+        <f>IF(A64&lt;=0,0,IF(A64&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A64/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A64/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H64" s="27">
+        <f>IF(G64&lt;=0,0,E64/G64)</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="32" t="n">
+      <c r="A65" s="26" t="n">
         <v>2.05</v>
       </c>
-      <c r="B65" s="32">
+      <c r="B65" s="26">
         <f>$B$9+A65</f>
         <v/>
       </c>
@@ -6104,12 +6793,20 @@
         <f>IF(A65&lt;=0,"—",IF(C65&lt;=D65,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G65" s="5">
+        <f>IF(A65&lt;=0,0,IF(A65&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A65/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A65/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H65" s="27">
+        <f>IF(G65&lt;=0,0,E65/G65)</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="32" t="n">
+      <c r="A66" s="26" t="n">
         <v>2.1</v>
       </c>
-      <c r="B66" s="32">
+      <c r="B66" s="26">
         <f>$B$9+A66</f>
         <v/>
       </c>
@@ -6129,12 +6826,20 @@
         <f>IF(A66&lt;=0,"—",IF(C66&lt;=D66,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G66" s="5">
+        <f>IF(A66&lt;=0,0,IF(A66&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A66/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A66/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H66" s="27">
+        <f>IF(G66&lt;=0,0,E66/G66)</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="32" t="n">
+      <c r="A67" s="26" t="n">
         <v>2.15</v>
       </c>
-      <c r="B67" s="32">
+      <c r="B67" s="26">
         <f>$B$9+A67</f>
         <v/>
       </c>
@@ -6154,12 +6859,20 @@
         <f>IF(A67&lt;=0,"—",IF(C67&lt;=D67,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G67" s="5">
+        <f>IF(A67&lt;=0,0,IF(A67&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A67/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A67/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H67" s="27">
+        <f>IF(G67&lt;=0,0,E67/G67)</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="32" t="n">
+      <c r="A68" s="26" t="n">
         <v>2.2</v>
       </c>
-      <c r="B68" s="32">
+      <c r="B68" s="26">
         <f>$B$9+A68</f>
         <v/>
       </c>
@@ -6179,12 +6892,20 @@
         <f>IF(A68&lt;=0,"—",IF(C68&lt;=D68,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G68" s="5">
+        <f>IF(A68&lt;=0,0,IF(A68&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A68/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A68/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H68" s="27">
+        <f>IF(G68&lt;=0,0,E68/G68)</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="32" t="n">
+      <c r="A69" s="26" t="n">
         <v>2.25</v>
       </c>
-      <c r="B69" s="32">
+      <c r="B69" s="26">
         <f>$B$9+A69</f>
         <v/>
       </c>
@@ -6204,12 +6925,20 @@
         <f>IF(A69&lt;=0,"—",IF(C69&lt;=D69,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G69" s="5">
+        <f>IF(A69&lt;=0,0,IF(A69&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A69/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A69/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H69" s="27">
+        <f>IF(G69&lt;=0,0,E69/G69)</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="32" t="n">
+      <c r="A70" s="26" t="n">
         <v>2.3</v>
       </c>
-      <c r="B70" s="32">
+      <c r="B70" s="26">
         <f>$B$9+A70</f>
         <v/>
       </c>
@@ -6229,12 +6958,20 @@
         <f>IF(A70&lt;=0,"—",IF(C70&lt;=D70,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G70" s="5">
+        <f>IF(A70&lt;=0,0,IF(A70&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A70/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A70/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H70" s="27">
+        <f>IF(G70&lt;=0,0,E70/G70)</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="32" t="n">
+      <c r="A71" s="26" t="n">
         <v>2.35</v>
       </c>
-      <c r="B71" s="32">
+      <c r="B71" s="26">
         <f>$B$9+A71</f>
         <v/>
       </c>
@@ -6254,12 +6991,20 @@
         <f>IF(A71&lt;=0,"—",IF(C71&lt;=D71,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G71" s="5">
+        <f>IF(A71&lt;=0,0,IF(A71&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A71/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A71/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H71" s="27">
+        <f>IF(G71&lt;=0,0,E71/G71)</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="39" t="n">
+      <c r="A72" s="41" t="n">
         <v>2.4</v>
       </c>
-      <c r="B72" s="39">
+      <c r="B72" s="41">
         <f>$B$9+A72</f>
         <v/>
       </c>
@@ -6279,12 +7024,20 @@
         <f>IF(A72&lt;=0,"—",IF(C72&lt;=D72,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G72" s="8">
+        <f>IF(A72&lt;=0,0,IF(A72&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A72/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A72/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H72" s="41">
+        <f>IF(G72&lt;=0,0,E72/G72)</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="32" t="n">
+      <c r="A73" s="26" t="n">
         <v>2.45</v>
       </c>
-      <c r="B73" s="32">
+      <c r="B73" s="26">
         <f>$B$9+A73</f>
         <v/>
       </c>
@@ -6304,12 +7057,20 @@
         <f>IF(A73&lt;=0,"—",IF(C73&lt;=D73,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G73" s="5">
+        <f>IF(A73&lt;=0,0,IF(A73&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A73/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A73/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H73" s="27">
+        <f>IF(G73&lt;=0,0,E73/G73)</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="32" t="n">
+      <c r="A74" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="B74" s="32">
+      <c r="B74" s="26">
         <f>$B$9+A74</f>
         <v/>
       </c>
@@ -6329,12 +7090,20 @@
         <f>IF(A74&lt;=0,"—",IF(C74&lt;=D74,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G74" s="5">
+        <f>IF(A74&lt;=0,0,IF(A74&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A74/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A74/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H74" s="27">
+        <f>IF(G74&lt;=0,0,E74/G74)</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="32" t="n">
+      <c r="A75" s="26" t="n">
         <v>2.55</v>
       </c>
-      <c r="B75" s="32">
+      <c r="B75" s="26">
         <f>$B$9+A75</f>
         <v/>
       </c>
@@ -6354,12 +7123,20 @@
         <f>IF(A75&lt;=0,"—",IF(C75&lt;=D75,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G75" s="5">
+        <f>IF(A75&lt;=0,0,IF(A75&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A75/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A75/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H75" s="27">
+        <f>IF(G75&lt;=0,0,E75/G75)</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="32" t="n">
+      <c r="A76" s="26" t="n">
         <v>2.6</v>
       </c>
-      <c r="B76" s="32">
+      <c r="B76" s="26">
         <f>$B$9+A76</f>
         <v/>
       </c>
@@ -6379,12 +7156,20 @@
         <f>IF(A76&lt;=0,"—",IF(C76&lt;=D76,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G76" s="5">
+        <f>IF(A76&lt;=0,0,IF(A76&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A76/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A76/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H76" s="27">
+        <f>IF(G76&lt;=0,0,E76/G76)</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="32" t="n">
+      <c r="A77" s="26" t="n">
         <v>2.65</v>
       </c>
-      <c r="B77" s="32">
+      <c r="B77" s="26">
         <f>$B$9+A77</f>
         <v/>
       </c>
@@ -6404,12 +7189,20 @@
         <f>IF(A77&lt;=0,"—",IF(C77&lt;=D77,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G77" s="5">
+        <f>IF(A77&lt;=0,0,IF(A77&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A77/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A77/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H77" s="27">
+        <f>IF(G77&lt;=0,0,E77/G77)</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="32" t="n">
+      <c r="A78" s="26" t="n">
         <v>2.7</v>
       </c>
-      <c r="B78" s="32">
+      <c r="B78" s="26">
         <f>$B$9+A78</f>
         <v/>
       </c>
@@ -6429,12 +7222,20 @@
         <f>IF(A78&lt;=0,"—",IF(C78&lt;=D78,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G78" s="5">
+        <f>IF(A78&lt;=0,0,IF(A78&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A78/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A78/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H78" s="27">
+        <f>IF(G78&lt;=0,0,E78/G78)</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="32" t="n">
+      <c r="A79" s="26" t="n">
         <v>2.75</v>
       </c>
-      <c r="B79" s="32">
+      <c r="B79" s="26">
         <f>$B$9+A79</f>
         <v/>
       </c>
@@ -6454,12 +7255,20 @@
         <f>IF(A79&lt;=0,"—",IF(C79&lt;=D79,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G79" s="5">
+        <f>IF(A79&lt;=0,0,IF(A79&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A79/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A79/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H79" s="27">
+        <f>IF(G79&lt;=0,0,E79/G79)</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="32" t="n">
+      <c r="A80" s="26" t="n">
         <v>2.8</v>
       </c>
-      <c r="B80" s="32">
+      <c r="B80" s="26">
         <f>$B$9+A80</f>
         <v/>
       </c>
@@ -6479,12 +7288,20 @@
         <f>IF(A80&lt;=0,"—",IF(C80&lt;=D80,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G80" s="5">
+        <f>IF(A80&lt;=0,0,IF(A80&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A80/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A80/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H80" s="27">
+        <f>IF(G80&lt;=0,0,E80/G80)</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="32" t="n">
+      <c r="A81" s="26" t="n">
         <v>2.85</v>
       </c>
-      <c r="B81" s="32">
+      <c r="B81" s="26">
         <f>$B$9+A81</f>
         <v/>
       </c>
@@ -6504,12 +7321,20 @@
         <f>IF(A81&lt;=0,"—",IF(C81&lt;=D81,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G81" s="5">
+        <f>IF(A81&lt;=0,0,IF(A81&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A81/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A81/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H81" s="27">
+        <f>IF(G81&lt;=0,0,E81/G81)</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="32" t="n">
+      <c r="A82" s="26" t="n">
         <v>2.9</v>
       </c>
-      <c r="B82" s="32">
+      <c r="B82" s="26">
         <f>$B$9+A82</f>
         <v/>
       </c>
@@ -6529,12 +7354,20 @@
         <f>IF(A82&lt;=0,"—",IF(C82&lt;=D82,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G82" s="5">
+        <f>IF(A82&lt;=0,0,IF(A82&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A82/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A82/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H82" s="27">
+        <f>IF(G82&lt;=0,0,E82/G82)</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="32" t="n">
+      <c r="A83" s="26" t="n">
         <v>2.95</v>
       </c>
-      <c r="B83" s="32">
+      <c r="B83" s="26">
         <f>$B$9+A83</f>
         <v/>
       </c>
@@ -6554,12 +7387,20 @@
         <f>IF(A83&lt;=0,"—",IF(C83&lt;=D83,"inlet","outlet"))</f>
         <v/>
       </c>
+      <c r="G83" s="5">
+        <f>IF(A83&lt;=0,0,IF(A83&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A83/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A83/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H83" s="27">
+        <f>IF(G83&lt;=0,0,E83/G83)</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="32" t="n">
+      <c r="A84" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B84" s="32">
+      <c r="B84" s="26">
         <f>$B$9+A84</f>
         <v/>
       </c>
@@ -6577,6 +7418,14 @@
       </c>
       <c r="F84" s="4">
         <f>IF(A84&lt;=0,"—",IF(C84&lt;=D84,"inlet","outlet"))</f>
+        <v/>
+      </c>
+      <c r="G84" s="5">
+        <f>IF(A84&lt;=0,0,IF(A84&lt;$B$7,(($B$7/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A84/$B$7)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A84/$B$7)))))),(PI()*($B$7/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="H84" s="27">
+        <f>IF(G84&lt;=0,0,E84/G84)</f>
         <v/>
       </c>
     </row>
@@ -6595,7 +7444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6605,6 +7454,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6615,7 +7465,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="40" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>H = V / Aire_constante (Parametres!B24) — raccourci, PAS le levé SS_Amont. Qout interpolé sur Courbe_QH_900!E (Q gouvernant). Si V≈0, Qout = MIN(Qin, Q_plein). ΔV = (Qin_moy - Qout)*Δt. Après routage, WSEmax_B réel est lu sur SS_Amont via Vmax_B (Parametres B45).</t>
         </is>
@@ -6628,7 +7478,7 @@
           <t>Aire (m²)</t>
         </is>
       </c>
-      <c r="B5" s="41">
+      <c r="B5" s="42">
         <f>Parametres!B24</f>
         <v/>
       </c>
@@ -6639,7 +7489,7 @@
           <t>Q_plein réf. (m³/s)</t>
         </is>
       </c>
-      <c r="B6" s="41">
+      <c r="B6" s="42">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -6650,7 +7500,7 @@
           <t>Vmax_B (m³)</t>
         </is>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="34">
         <f>MAX(G12:G24)</f>
         <v/>
       </c>
@@ -6700,6 +7550,11 @@
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>V (m³)</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>V_Ø900 (m/s)</t>
         </is>
       </c>
     </row>
@@ -6722,11 +7577,15 @@
         <f>MIN(B12,$B$6)</f>
         <v/>
       </c>
-      <c r="F12" s="26" t="n">
+      <c r="F12" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="34" t="n">
+      <c r="G12" s="36" t="n">
         <v>0</v>
+      </c>
+      <c r="H12" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,E12/Parametres!$C$87)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -6750,12 +7609,16 @@
         <f>IF(G12&lt;=0.01,MIN(0.5*(B12+B13),$B$6),D13)</f>
         <v/>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="29">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="36">
         <f>MAX(0,G12+(0.5*(B12+B13)-E13)*F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,E13/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -6780,12 +7643,16 @@
         <f>IF(G13&lt;=0.01,MIN(0.5*(B13+B14),$B$6),D14)</f>
         <v/>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="29">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="36">
         <f>MAX(0,G13+(0.5*(B13+B14)-E14)*F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,E14/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -6810,12 +7677,16 @@
         <f>IF(G14&lt;=0.01,MIN(0.5*(B14+B15),$B$6),D15)</f>
         <v/>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="29">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="36">
         <f>MAX(0,G14+(0.5*(B14+B15)-E15)*F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,E15/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -6840,12 +7711,16 @@
         <f>IF(G15&lt;=0.01,MIN(0.5*(B15+B16),$B$6),D16)</f>
         <v/>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="29">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="36">
         <f>MAX(0,G15+(0.5*(B15+B16)-E16)*F16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,E16/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -6870,12 +7745,16 @@
         <f>IF(G16&lt;=0.01,MIN(0.5*(B16+B17),$B$6),D17)</f>
         <v/>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="29">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="G17" s="34">
+      <c r="G17" s="36">
         <f>MAX(0,G16+(0.5*(B16+B17)-E17)*F17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,E17/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -6900,12 +7779,16 @@
         <f>IF(G17&lt;=0.01,MIN(0.5*(B17+B18),$B$6),D18)</f>
         <v/>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="29">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="36">
         <f>MAX(0,G17+(0.5*(B17+B18)-E18)*F18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,E18/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -6930,12 +7813,16 @@
         <f>IF(G18&lt;=0.01,MIN(0.5*(B18+B19),$B$6),D19)</f>
         <v/>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="29">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="36">
         <f>MAX(0,G18+(0.5*(B18+B19)-E19)*F19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,E19/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -6960,12 +7847,16 @@
         <f>IF(G19&lt;=0.01,MIN(0.5*(B19+B20),$B$6),D20)</f>
         <v/>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="29">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="36">
         <f>MAX(0,G19+(0.5*(B19+B20)-E20)*F20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,E20/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -6990,12 +7881,16 @@
         <f>IF(G20&lt;=0.01,MIN(0.5*(B20+B21),$B$6),D21)</f>
         <v/>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="29">
         <f>(A21-A20)*60</f>
         <v/>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="36">
         <f>MAX(0,G20+(0.5*(B20+B21)-E21)*F21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,E21/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -7020,12 +7915,16 @@
         <f>IF(G21&lt;=0.01,MIN(0.5*(B21+B22),$B$6),D22)</f>
         <v/>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="29">
         <f>(A22-A21)*60</f>
         <v/>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="36">
         <f>MAX(0,G21+(0.5*(B21+B22)-E22)*F22)</f>
+        <v/>
+      </c>
+      <c r="H22" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,E22/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -7050,12 +7949,16 @@
         <f>IF(G22&lt;=0.01,MIN(0.5*(B22+B23),$B$6),D23)</f>
         <v/>
       </c>
-      <c r="F23" s="26">
+      <c r="F23" s="29">
         <f>(A23-A22)*60</f>
         <v/>
       </c>
-      <c r="G23" s="34">
+      <c r="G23" s="36">
         <f>MAX(0,G22+(0.5*(B22+B23)-E23)*F23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,E23/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -7080,12 +7983,16 @@
         <f>IF(G23&lt;=0.01,MIN(0.5*(B23+B24),$B$6),D24)</f>
         <v/>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="29">
         <f>(A24-A23)*60</f>
         <v/>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="36">
         <f>MAX(0,G23+(0.5*(B23+B24)-E24)*F24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,E24/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -7103,7 +8010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7117,6 +8024,8 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7285,16 +8194,26 @@
           <t>Overflow?</t>
         </is>
       </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>V_Ø900 (m/s)</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>V_overflow (m/s)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="n">
+      <c r="A15" s="26" t="n">
         <v>34.88</v>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="26">
         <f>A15-$B$12</f>
         <v/>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="26">
         <f>MAX(0,A15-$B$6)</f>
         <v/>
       </c>
@@ -7302,15 +8221,15 @@
         <f>IF(C15&lt;=0,0,($B$7+$B$9*C15)*C15)</f>
         <v/>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="29">
         <f>IF($B$13=1,D15*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="29">
         <f>IF(A15&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A15&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A15,SS_Amont!$A$11:$A$18,1))+(A15-INDEX(SS_Amont!$A$11:$A$18,MATCH(A15,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A15,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A15,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A15,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A15,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="36">
         <f>F15+E15</f>
         <v/>
       </c>
@@ -7330,16 +8249,24 @@
         <f>IF(C15&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L15" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H15/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M15" s="27">
+        <f>IF(D15&lt;=0,0,I15/D15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="n">
+      <c r="A16" s="26" t="n">
         <v>34.93</v>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="26">
         <f>A16-$B$12</f>
         <v/>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="26">
         <f>MAX(0,A16-$B$6)</f>
         <v/>
       </c>
@@ -7347,15 +8274,15 @@
         <f>IF(C16&lt;=0,0,($B$7+$B$9*C16)*C16)</f>
         <v/>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="29">
         <f>IF($B$13=1,D16*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="29">
         <f>IF(A16&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A16&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A16,SS_Amont!$A$11:$A$18,1))+(A16-INDEX(SS_Amont!$A$11:$A$18,MATCH(A16,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A16,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A16,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A16,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A16,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="36">
         <f>F16+E16</f>
         <v/>
       </c>
@@ -7375,16 +8302,24 @@
         <f>IF(C16&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L16" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H16/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M16" s="27">
+        <f>IF(D16&lt;=0,0,I16/D16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="n">
+      <c r="A17" s="26" t="n">
         <v>34.98</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="26">
         <f>A17-$B$12</f>
         <v/>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="26">
         <f>MAX(0,A17-$B$6)</f>
         <v/>
       </c>
@@ -7392,15 +8327,15 @@
         <f>IF(C17&lt;=0,0,($B$7+$B$9*C17)*C17)</f>
         <v/>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="29">
         <f>IF($B$13=1,D17*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="29">
         <f>IF(A17&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A17&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A17,SS_Amont!$A$11:$A$18,1))+(A17-INDEX(SS_Amont!$A$11:$A$18,MATCH(A17,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A17,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A17,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A17,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A17,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G17" s="34">
+      <c r="G17" s="36">
         <f>F17+E17</f>
         <v/>
       </c>
@@ -7420,16 +8355,24 @@
         <f>IF(C17&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L17" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H17/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M17" s="27">
+        <f>IF(D17&lt;=0,0,I17/D17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="n">
+      <c r="A18" s="26" t="n">
         <v>35.03</v>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="26">
         <f>A18-$B$12</f>
         <v/>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="26">
         <f>MAX(0,A18-$B$6)</f>
         <v/>
       </c>
@@ -7437,15 +8380,15 @@
         <f>IF(C18&lt;=0,0,($B$7+$B$9*C18)*C18)</f>
         <v/>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="29">
         <f>IF($B$13=1,D18*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="29">
         <f>IF(A18&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A18&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A18,SS_Amont!$A$11:$A$18,1))+(A18-INDEX(SS_Amont!$A$11:$A$18,MATCH(A18,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A18,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A18,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A18,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A18,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="36">
         <f>F18+E18</f>
         <v/>
       </c>
@@ -7465,16 +8408,24 @@
         <f>IF(C18&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L18" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H18/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M18" s="27">
+        <f>IF(D18&lt;=0,0,I18/D18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="n">
+      <c r="A19" s="26" t="n">
         <v>35.08</v>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="26">
         <f>A19-$B$12</f>
         <v/>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="26">
         <f>MAX(0,A19-$B$6)</f>
         <v/>
       </c>
@@ -7482,15 +8433,15 @@
         <f>IF(C19&lt;=0,0,($B$7+$B$9*C19)*C19)</f>
         <v/>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="29">
         <f>IF($B$13=1,D19*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="29">
         <f>IF(A19&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A19&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A19,SS_Amont!$A$11:$A$18,1))+(A19-INDEX(SS_Amont!$A$11:$A$18,MATCH(A19,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A19,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A19,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A19,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A19,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="36">
         <f>F19+E19</f>
         <v/>
       </c>
@@ -7510,16 +8461,24 @@
         <f>IF(C19&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L19" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H19/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M19" s="27">
+        <f>IF(D19&lt;=0,0,I19/D19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="n">
+      <c r="A20" s="26" t="n">
         <v>35.13</v>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="26">
         <f>A20-$B$12</f>
         <v/>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="26">
         <f>MAX(0,A20-$B$6)</f>
         <v/>
       </c>
@@ -7527,15 +8486,15 @@
         <f>IF(C20&lt;=0,0,($B$7+$B$9*C20)*C20)</f>
         <v/>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="29">
         <f>IF($B$13=1,D20*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="29">
         <f>IF(A20&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A20&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A20,SS_Amont!$A$11:$A$18,1))+(A20-INDEX(SS_Amont!$A$11:$A$18,MATCH(A20,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A20,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A20,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A20,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A20,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="36">
         <f>F20+E20</f>
         <v/>
       </c>
@@ -7555,16 +8514,24 @@
         <f>IF(C20&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L20" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H20/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M20" s="27">
+        <f>IF(D20&lt;=0,0,I20/D20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="n">
+      <c r="A21" s="26" t="n">
         <v>35.18</v>
       </c>
-      <c r="B21" s="32">
+      <c r="B21" s="26">
         <f>A21-$B$12</f>
         <v/>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="26">
         <f>MAX(0,A21-$B$6)</f>
         <v/>
       </c>
@@ -7572,15 +8539,15 @@
         <f>IF(C21&lt;=0,0,($B$7+$B$9*C21)*C21)</f>
         <v/>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="29">
         <f>IF($B$13=1,D21*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="29">
         <f>IF(A21&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A21&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A21,SS_Amont!$A$11:$A$18,1))+(A21-INDEX(SS_Amont!$A$11:$A$18,MATCH(A21,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A21,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A21,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A21,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A21,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="36">
         <f>F21+E21</f>
         <v/>
       </c>
@@ -7600,16 +8567,24 @@
         <f>IF(C21&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L21" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H21/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M21" s="27">
+        <f>IF(D21&lt;=0,0,I21/D21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="n">
+      <c r="A22" s="26" t="n">
         <v>35.23</v>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="26">
         <f>A22-$B$12</f>
         <v/>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="26">
         <f>MAX(0,A22-$B$6)</f>
         <v/>
       </c>
@@ -7617,15 +8592,15 @@
         <f>IF(C22&lt;=0,0,($B$7+$B$9*C22)*C22)</f>
         <v/>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="29">
         <f>IF($B$13=1,D22*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="29">
         <f>IF(A22&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A22&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A22,SS_Amont!$A$11:$A$18,1))+(A22-INDEX(SS_Amont!$A$11:$A$18,MATCH(A22,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A22,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A22,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A22,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A22,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="36">
         <f>F22+E22</f>
         <v/>
       </c>
@@ -7645,16 +8620,24 @@
         <f>IF(C22&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L22" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H22/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M22" s="27">
+        <f>IF(D22&lt;=0,0,I22/D22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="n">
+      <c r="A23" s="26" t="n">
         <v>35.28</v>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="26">
         <f>A23-$B$12</f>
         <v/>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="26">
         <f>MAX(0,A23-$B$6)</f>
         <v/>
       </c>
@@ -7662,15 +8645,15 @@
         <f>IF(C23&lt;=0,0,($B$7+$B$9*C23)*C23)</f>
         <v/>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="29">
         <f>IF($B$13=1,D23*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F23" s="26">
+      <c r="F23" s="29">
         <f>IF(A23&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A23&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A23,SS_Amont!$A$11:$A$18,1))+(A23-INDEX(SS_Amont!$A$11:$A$18,MATCH(A23,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A23,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A23,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A23,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A23,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G23" s="34">
+      <c r="G23" s="36">
         <f>F23+E23</f>
         <v/>
       </c>
@@ -7690,16 +8673,24 @@
         <f>IF(C23&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L23" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H23/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M23" s="27">
+        <f>IF(D23&lt;=0,0,I23/D23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="n">
+      <c r="A24" s="26" t="n">
         <v>35.33</v>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="26">
         <f>A24-$B$12</f>
         <v/>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="26">
         <f>MAX(0,A24-$B$6)</f>
         <v/>
       </c>
@@ -7707,15 +8698,15 @@
         <f>IF(C24&lt;=0,0,($B$7+$B$9*C24)*C24)</f>
         <v/>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="29">
         <f>IF($B$13=1,D24*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="29">
         <f>IF(A24&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A24&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A24,SS_Amont!$A$11:$A$18,1))+(A24-INDEX(SS_Amont!$A$11:$A$18,MATCH(A24,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A24,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A24,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A24,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A24,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="36">
         <f>F24+E24</f>
         <v/>
       </c>
@@ -7735,16 +8726,24 @@
         <f>IF(C24&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L24" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H24/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M24" s="27">
+        <f>IF(D24&lt;=0,0,I24/D24)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="n">
+      <c r="A25" s="26" t="n">
         <v>35.38</v>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="26">
         <f>A25-$B$12</f>
         <v/>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="26">
         <f>MAX(0,A25-$B$6)</f>
         <v/>
       </c>
@@ -7752,15 +8751,15 @@
         <f>IF(C25&lt;=0,0,($B$7+$B$9*C25)*C25)</f>
         <v/>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="29">
         <f>IF($B$13=1,D25*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="29">
         <f>IF(A25&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A25&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A25,SS_Amont!$A$11:$A$18,1))+(A25-INDEX(SS_Amont!$A$11:$A$18,MATCH(A25,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A25,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A25,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A25,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A25,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="36">
         <f>F25+E25</f>
         <v/>
       </c>
@@ -7780,16 +8779,24 @@
         <f>IF(C25&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L25" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H25/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M25" s="27">
+        <f>IF(D25&lt;=0,0,I25/D25)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="32" t="n">
+      <c r="A26" s="26" t="n">
         <v>35.43</v>
       </c>
-      <c r="B26" s="32">
+      <c r="B26" s="26">
         <f>A26-$B$12</f>
         <v/>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="26">
         <f>MAX(0,A26-$B$6)</f>
         <v/>
       </c>
@@ -7797,15 +8804,15 @@
         <f>IF(C26&lt;=0,0,($B$7+$B$9*C26)*C26)</f>
         <v/>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="29">
         <f>IF($B$13=1,D26*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F26" s="26">
+      <c r="F26" s="29">
         <f>IF(A26&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A26&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A26,SS_Amont!$A$11:$A$18,1))+(A26-INDEX(SS_Amont!$A$11:$A$18,MATCH(A26,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A26,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A26,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A26,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A26,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="36">
         <f>F26+E26</f>
         <v/>
       </c>
@@ -7825,16 +8832,24 @@
         <f>IF(C26&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L26" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H26/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M26" s="27">
+        <f>IF(D26&lt;=0,0,I26/D26)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="n">
+      <c r="A27" s="26" t="n">
         <v>35.48</v>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="26">
         <f>A27-$B$12</f>
         <v/>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="26">
         <f>MAX(0,A27-$B$6)</f>
         <v/>
       </c>
@@ -7842,15 +8857,15 @@
         <f>IF(C27&lt;=0,0,($B$7+$B$9*C27)*C27)</f>
         <v/>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="29">
         <f>IF($B$13=1,D27*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F27" s="26">
+      <c r="F27" s="29">
         <f>IF(A27&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A27&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A27,SS_Amont!$A$11:$A$18,1))+(A27-INDEX(SS_Amont!$A$11:$A$18,MATCH(A27,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A27,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A27,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A27,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A27,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="36">
         <f>F27+E27</f>
         <v/>
       </c>
@@ -7870,16 +8885,24 @@
         <f>IF(C27&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L27" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H27/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M27" s="27">
+        <f>IF(D27&lt;=0,0,I27/D27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="n">
+      <c r="A28" s="26" t="n">
         <v>35.53</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="26">
         <f>A28-$B$12</f>
         <v/>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="26">
         <f>MAX(0,A28-$B$6)</f>
         <v/>
       </c>
@@ -7887,15 +8910,15 @@
         <f>IF(C28&lt;=0,0,($B$7+$B$9*C28)*C28)</f>
         <v/>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="29">
         <f>IF($B$13=1,D28*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F28" s="26">
+      <c r="F28" s="29">
         <f>IF(A28&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A28&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A28,SS_Amont!$A$11:$A$18,1))+(A28-INDEX(SS_Amont!$A$11:$A$18,MATCH(A28,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A28,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A28,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A28,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A28,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="36">
         <f>F28+E28</f>
         <v/>
       </c>
@@ -7915,16 +8938,24 @@
         <f>IF(C28&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L28" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H28/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M28" s="27">
+        <f>IF(D28&lt;=0,0,I28/D28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="n">
+      <c r="A29" s="26" t="n">
         <v>35.58</v>
       </c>
-      <c r="B29" s="32">
+      <c r="B29" s="26">
         <f>A29-$B$12</f>
         <v/>
       </c>
-      <c r="C29" s="32">
+      <c r="C29" s="26">
         <f>MAX(0,A29-$B$6)</f>
         <v/>
       </c>
@@ -7932,15 +8963,15 @@
         <f>IF(C29&lt;=0,0,($B$7+$B$9*C29)*C29)</f>
         <v/>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="29">
         <f>IF($B$13=1,D29*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F29" s="26">
+      <c r="F29" s="29">
         <f>IF(A29&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A29&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A29,SS_Amont!$A$11:$A$18,1))+(A29-INDEX(SS_Amont!$A$11:$A$18,MATCH(A29,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A29,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A29,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A29,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A29,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G29" s="34">
+      <c r="G29" s="36">
         <f>F29+E29</f>
         <v/>
       </c>
@@ -7960,16 +8991,24 @@
         <f>IF(C29&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L29" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H29/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M29" s="27">
+        <f>IF(D29&lt;=0,0,I29/D29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="n">
+      <c r="A30" s="26" t="n">
         <v>35.63</v>
       </c>
-      <c r="B30" s="32">
+      <c r="B30" s="26">
         <f>A30-$B$12</f>
         <v/>
       </c>
-      <c r="C30" s="32">
+      <c r="C30" s="26">
         <f>MAX(0,A30-$B$6)</f>
         <v/>
       </c>
@@ -7977,15 +9016,15 @@
         <f>IF(C30&lt;=0,0,($B$7+$B$9*C30)*C30)</f>
         <v/>
       </c>
-      <c r="E30" s="26">
+      <c r="E30" s="29">
         <f>IF($B$13=1,D30*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F30" s="26">
+      <c r="F30" s="29">
         <f>IF(A30&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A30&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A30,SS_Amont!$A$11:$A$18,1))+(A30-INDEX(SS_Amont!$A$11:$A$18,MATCH(A30,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A30,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A30,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A30,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A30,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="36">
         <f>F30+E30</f>
         <v/>
       </c>
@@ -8005,16 +9044,24 @@
         <f>IF(C30&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L30" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H30/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M30" s="27">
+        <f>IF(D30&lt;=0,0,I30/D30)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="32" t="n">
+      <c r="A31" s="26" t="n">
         <v>35.68</v>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="26">
         <f>A31-$B$12</f>
         <v/>
       </c>
-      <c r="C31" s="32">
+      <c r="C31" s="26">
         <f>MAX(0,A31-$B$6)</f>
         <v/>
       </c>
@@ -8022,15 +9069,15 @@
         <f>IF(C31&lt;=0,0,($B$7+$B$9*C31)*C31)</f>
         <v/>
       </c>
-      <c r="E31" s="26">
+      <c r="E31" s="29">
         <f>IF($B$13=1,D31*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F31" s="26">
+      <c r="F31" s="29">
         <f>IF(A31&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A31&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A31,SS_Amont!$A$11:$A$18,1))+(A31-INDEX(SS_Amont!$A$11:$A$18,MATCH(A31,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A31,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A31,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A31,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A31,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="36">
         <f>F31+E31</f>
         <v/>
       </c>
@@ -8050,16 +9097,24 @@
         <f>IF(C31&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L31" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H31/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M31" s="27">
+        <f>IF(D31&lt;=0,0,I31/D31)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="n">
+      <c r="A32" s="26" t="n">
         <v>35.73</v>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="26">
         <f>A32-$B$12</f>
         <v/>
       </c>
-      <c r="C32" s="32">
+      <c r="C32" s="26">
         <f>MAX(0,A32-$B$6)</f>
         <v/>
       </c>
@@ -8067,15 +9122,15 @@
         <f>IF(C32&lt;=0,0,($B$7+$B$9*C32)*C32)</f>
         <v/>
       </c>
-      <c r="E32" s="26">
+      <c r="E32" s="29">
         <f>IF($B$13=1,D32*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F32" s="26">
+      <c r="F32" s="29">
         <f>IF(A32&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A32&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A32,SS_Amont!$A$11:$A$18,1))+(A32-INDEX(SS_Amont!$A$11:$A$18,MATCH(A32,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A32,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A32,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A32,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A32,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G32" s="34">
+      <c r="G32" s="36">
         <f>F32+E32</f>
         <v/>
       </c>
@@ -8095,16 +9150,24 @@
         <f>IF(C32&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L32" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H32/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M32" s="27">
+        <f>IF(D32&lt;=0,0,I32/D32)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="39" t="n">
+      <c r="A33" s="41" t="n">
         <v>35.78</v>
       </c>
-      <c r="B33" s="39">
+      <c r="B33" s="41">
         <f>A33-$B$12</f>
         <v/>
       </c>
-      <c r="C33" s="39">
+      <c r="C33" s="41">
         <f>MAX(0,A33-$B$6)</f>
         <v/>
       </c>
@@ -8112,15 +9175,15 @@
         <f>IF(C33&lt;=0,0,($B$7+$B$9*C33)*C33)</f>
         <v/>
       </c>
-      <c r="E33" s="42">
+      <c r="E33" s="43">
         <f>IF($B$13=1,D33*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F33" s="42">
+      <c r="F33" s="43">
         <f>IF(A33&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A33&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A33,SS_Amont!$A$11:$A$18,1))+(A33-INDEX(SS_Amont!$A$11:$A$18,MATCH(A33,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A33,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A33,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A33,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A33,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="36">
         <f>F33+E33</f>
         <v/>
       </c>
@@ -8140,16 +9203,24 @@
         <f>IF(C33&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L33" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H33/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M33" s="27">
+        <f>IF(D33&lt;=0,0,I33/D33)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="32" t="n">
+      <c r="A34" s="26" t="n">
         <v>35.83</v>
       </c>
-      <c r="B34" s="32">
+      <c r="B34" s="26">
         <f>A34-$B$12</f>
         <v/>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="26">
         <f>MAX(0,A34-$B$6)</f>
         <v/>
       </c>
@@ -8157,15 +9228,15 @@
         <f>IF(C34&lt;=0,0,($B$7+$B$9*C34)*C34)</f>
         <v/>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="29">
         <f>IF($B$13=1,D34*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F34" s="26">
+      <c r="F34" s="29">
         <f>IF(A34&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A34&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A34,SS_Amont!$A$11:$A$18,1))+(A34-INDEX(SS_Amont!$A$11:$A$18,MATCH(A34,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A34,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A34,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A34,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A34,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="36">
         <f>F34+E34</f>
         <v/>
       </c>
@@ -8185,16 +9256,24 @@
         <f>IF(C34&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L34" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H34/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M34" s="27">
+        <f>IF(D34&lt;=0,0,I34/D34)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="32" t="n">
+      <c r="A35" s="26" t="n">
         <v>35.88</v>
       </c>
-      <c r="B35" s="32">
+      <c r="B35" s="26">
         <f>A35-$B$12</f>
         <v/>
       </c>
-      <c r="C35" s="32">
+      <c r="C35" s="26">
         <f>MAX(0,A35-$B$6)</f>
         <v/>
       </c>
@@ -8202,15 +9281,15 @@
         <f>IF(C35&lt;=0,0,($B$7+$B$9*C35)*C35)</f>
         <v/>
       </c>
-      <c r="E35" s="26">
+      <c r="E35" s="29">
         <f>IF($B$13=1,D35*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F35" s="26">
+      <c r="F35" s="29">
         <f>IF(A35&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A35&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A35,SS_Amont!$A$11:$A$18,1))+(A35-INDEX(SS_Amont!$A$11:$A$18,MATCH(A35,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A35,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A35,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A35,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A35,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="36">
         <f>F35+E35</f>
         <v/>
       </c>
@@ -8230,16 +9309,24 @@
         <f>IF(C35&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L35" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H35/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M35" s="27">
+        <f>IF(D35&lt;=0,0,I35/D35)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="32" t="n">
+      <c r="A36" s="26" t="n">
         <v>35.93</v>
       </c>
-      <c r="B36" s="32">
+      <c r="B36" s="26">
         <f>A36-$B$12</f>
         <v/>
       </c>
-      <c r="C36" s="32">
+      <c r="C36" s="26">
         <f>MAX(0,A36-$B$6)</f>
         <v/>
       </c>
@@ -8247,15 +9334,15 @@
         <f>IF(C36&lt;=0,0,($B$7+$B$9*C36)*C36)</f>
         <v/>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="29">
         <f>IF($B$13=1,D36*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F36" s="26">
+      <c r="F36" s="29">
         <f>IF(A36&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A36&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A36,SS_Amont!$A$11:$A$18,1))+(A36-INDEX(SS_Amont!$A$11:$A$18,MATCH(A36,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A36,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A36,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A36,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A36,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="36">
         <f>F36+E36</f>
         <v/>
       </c>
@@ -8275,16 +9362,24 @@
         <f>IF(C36&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L36" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H36/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M36" s="27">
+        <f>IF(D36&lt;=0,0,I36/D36)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="32" t="n">
+      <c r="A37" s="26" t="n">
         <v>35.98</v>
       </c>
-      <c r="B37" s="32">
+      <c r="B37" s="26">
         <f>A37-$B$12</f>
         <v/>
       </c>
-      <c r="C37" s="32">
+      <c r="C37" s="26">
         <f>MAX(0,A37-$B$6)</f>
         <v/>
       </c>
@@ -8292,15 +9387,15 @@
         <f>IF(C37&lt;=0,0,($B$7+$B$9*C37)*C37)</f>
         <v/>
       </c>
-      <c r="E37" s="26">
+      <c r="E37" s="29">
         <f>IF($B$13=1,D37*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F37" s="26">
+      <c r="F37" s="29">
         <f>IF(A37&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A37&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A37,SS_Amont!$A$11:$A$18,1))+(A37-INDEX(SS_Amont!$A$11:$A$18,MATCH(A37,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A37,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A37,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A37,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A37,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G37" s="34">
+      <c r="G37" s="36">
         <f>F37+E37</f>
         <v/>
       </c>
@@ -8320,16 +9415,24 @@
         <f>IF(C37&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L37" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H37/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M37" s="27">
+        <f>IF(D37&lt;=0,0,I37/D37)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="n">
+      <c r="A38" s="26" t="n">
         <v>36.03</v>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="26">
         <f>A38-$B$12</f>
         <v/>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="26">
         <f>MAX(0,A38-$B$6)</f>
         <v/>
       </c>
@@ -8337,15 +9440,15 @@
         <f>IF(C38&lt;=0,0,($B$7+$B$9*C38)*C38)</f>
         <v/>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="29">
         <f>IF($B$13=1,D38*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F38" s="26">
+      <c r="F38" s="29">
         <f>IF(A38&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A38&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A38,SS_Amont!$A$11:$A$18,1))+(A38-INDEX(SS_Amont!$A$11:$A$18,MATCH(A38,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A38,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A38,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A38,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A38,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G38" s="34">
+      <c r="G38" s="36">
         <f>F38+E38</f>
         <v/>
       </c>
@@ -8365,16 +9468,24 @@
         <f>IF(C38&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L38" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H38/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M38" s="27">
+        <f>IF(D38&lt;=0,0,I38/D38)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="32" t="n">
+      <c r="A39" s="26" t="n">
         <v>36.08</v>
       </c>
-      <c r="B39" s="32">
+      <c r="B39" s="26">
         <f>A39-$B$12</f>
         <v/>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="26">
         <f>MAX(0,A39-$B$6)</f>
         <v/>
       </c>
@@ -8382,15 +9493,15 @@
         <f>IF(C39&lt;=0,0,($B$7+$B$9*C39)*C39)</f>
         <v/>
       </c>
-      <c r="E39" s="26">
+      <c r="E39" s="29">
         <f>IF($B$13=1,D39*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F39" s="26">
+      <c r="F39" s="29">
         <f>IF(A39&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A39&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A39,SS_Amont!$A$11:$A$18,1))+(A39-INDEX(SS_Amont!$A$11:$A$18,MATCH(A39,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A39,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A39,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A39,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A39,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G39" s="34">
+      <c r="G39" s="36">
         <f>F39+E39</f>
         <v/>
       </c>
@@ -8410,16 +9521,24 @@
         <f>IF(C39&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L39" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H39/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M39" s="27">
+        <f>IF(D39&lt;=0,0,I39/D39)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="32" t="n">
+      <c r="A40" s="26" t="n">
         <v>36.13</v>
       </c>
-      <c r="B40" s="32">
+      <c r="B40" s="26">
         <f>A40-$B$12</f>
         <v/>
       </c>
-      <c r="C40" s="32">
+      <c r="C40" s="26">
         <f>MAX(0,A40-$B$6)</f>
         <v/>
       </c>
@@ -8427,15 +9546,15 @@
         <f>IF(C40&lt;=0,0,($B$7+$B$9*C40)*C40)</f>
         <v/>
       </c>
-      <c r="E40" s="26">
+      <c r="E40" s="29">
         <f>IF($B$13=1,D40*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F40" s="26">
+      <c r="F40" s="29">
         <f>IF(A40&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A40&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A40,SS_Amont!$A$11:$A$18,1))+(A40-INDEX(SS_Amont!$A$11:$A$18,MATCH(A40,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A40,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A40,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A40,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A40,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G40" s="34">
+      <c r="G40" s="36">
         <f>F40+E40</f>
         <v/>
       </c>
@@ -8455,16 +9574,24 @@
         <f>IF(C40&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L40" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H40/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M40" s="27">
+        <f>IF(D40&lt;=0,0,I40/D40)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="32" t="n">
+      <c r="A41" s="26" t="n">
         <v>36.18</v>
       </c>
-      <c r="B41" s="32">
+      <c r="B41" s="26">
         <f>A41-$B$12</f>
         <v/>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="26">
         <f>MAX(0,A41-$B$6)</f>
         <v/>
       </c>
@@ -8472,15 +9599,15 @@
         <f>IF(C41&lt;=0,0,($B$7+$B$9*C41)*C41)</f>
         <v/>
       </c>
-      <c r="E41" s="26">
+      <c r="E41" s="29">
         <f>IF($B$13=1,D41*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F41" s="26">
+      <c r="F41" s="29">
         <f>IF(A41&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A41&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A41,SS_Amont!$A$11:$A$18,1))+(A41-INDEX(SS_Amont!$A$11:$A$18,MATCH(A41,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A41,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A41,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A41,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A41,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G41" s="34">
+      <c r="G41" s="36">
         <f>F41+E41</f>
         <v/>
       </c>
@@ -8500,16 +9627,24 @@
         <f>IF(C41&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L41" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H41/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M41" s="27">
+        <f>IF(D41&lt;=0,0,I41/D41)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="32" t="n">
+      <c r="A42" s="26" t="n">
         <v>36.23</v>
       </c>
-      <c r="B42" s="32">
+      <c r="B42" s="26">
         <f>A42-$B$12</f>
         <v/>
       </c>
-      <c r="C42" s="32">
+      <c r="C42" s="26">
         <f>MAX(0,A42-$B$6)</f>
         <v/>
       </c>
@@ -8517,15 +9652,15 @@
         <f>IF(C42&lt;=0,0,($B$7+$B$9*C42)*C42)</f>
         <v/>
       </c>
-      <c r="E42" s="26">
+      <c r="E42" s="29">
         <f>IF($B$13=1,D42*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F42" s="26">
+      <c r="F42" s="29">
         <f>IF(A42&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A42&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A42,SS_Amont!$A$11:$A$18,1))+(A42-INDEX(SS_Amont!$A$11:$A$18,MATCH(A42,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A42,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A42,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A42,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A42,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G42" s="34">
+      <c r="G42" s="36">
         <f>F42+E42</f>
         <v/>
       </c>
@@ -8545,16 +9680,24 @@
         <f>IF(C42&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L42" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H42/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M42" s="27">
+        <f>IF(D42&lt;=0,0,I42/D42)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="32" t="n">
+      <c r="A43" s="26" t="n">
         <v>36.28</v>
       </c>
-      <c r="B43" s="32">
+      <c r="B43" s="26">
         <f>A43-$B$12</f>
         <v/>
       </c>
-      <c r="C43" s="32">
+      <c r="C43" s="26">
         <f>MAX(0,A43-$B$6)</f>
         <v/>
       </c>
@@ -8562,15 +9705,15 @@
         <f>IF(C43&lt;=0,0,($B$7+$B$9*C43)*C43)</f>
         <v/>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="29">
         <f>IF($B$13=1,D43*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F43" s="26">
+      <c r="F43" s="29">
         <f>IF(A43&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A43&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A43,SS_Amont!$A$11:$A$18,1))+(A43-INDEX(SS_Amont!$A$11:$A$18,MATCH(A43,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A43,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A43,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A43,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A43,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G43" s="34">
+      <c r="G43" s="36">
         <f>F43+E43</f>
         <v/>
       </c>
@@ -8590,16 +9733,24 @@
         <f>IF(C43&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L43" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H43/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M43" s="27">
+        <f>IF(D43&lt;=0,0,I43/D43)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="32" t="n">
+      <c r="A44" s="26" t="n">
         <v>36.33</v>
       </c>
-      <c r="B44" s="32">
+      <c r="B44" s="26">
         <f>A44-$B$12</f>
         <v/>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="26">
         <f>MAX(0,A44-$B$6)</f>
         <v/>
       </c>
@@ -8607,15 +9758,15 @@
         <f>IF(C44&lt;=0,0,($B$7+$B$9*C44)*C44)</f>
         <v/>
       </c>
-      <c r="E44" s="26">
+      <c r="E44" s="29">
         <f>IF($B$13=1,D44*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F44" s="26">
+      <c r="F44" s="29">
         <f>IF(A44&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A44&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A44,SS_Amont!$A$11:$A$18,1))+(A44-INDEX(SS_Amont!$A$11:$A$18,MATCH(A44,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A44,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A44,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A44,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A44,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G44" s="34">
+      <c r="G44" s="36">
         <f>F44+E44</f>
         <v/>
       </c>
@@ -8635,16 +9786,24 @@
         <f>IF(C44&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L44" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H44/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M44" s="27">
+        <f>IF(D44&lt;=0,0,I44/D44)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="32" t="n">
+      <c r="A45" s="26" t="n">
         <v>36.38</v>
       </c>
-      <c r="B45" s="32">
+      <c r="B45" s="26">
         <f>A45-$B$12</f>
         <v/>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="26">
         <f>MAX(0,A45-$B$6)</f>
         <v/>
       </c>
@@ -8652,15 +9811,15 @@
         <f>IF(C45&lt;=0,0,($B$7+$B$9*C45)*C45)</f>
         <v/>
       </c>
-      <c r="E45" s="26">
+      <c r="E45" s="29">
         <f>IF($B$13=1,D45*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F45" s="26">
+      <c r="F45" s="29">
         <f>IF(A45&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A45&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A45,SS_Amont!$A$11:$A$18,1))+(A45-INDEX(SS_Amont!$A$11:$A$18,MATCH(A45,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A45,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A45,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A45,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A45,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G45" s="34">
+      <c r="G45" s="36">
         <f>F45+E45</f>
         <v/>
       </c>
@@ -8680,16 +9839,24 @@
         <f>IF(C45&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L45" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H45/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M45" s="27">
+        <f>IF(D45&lt;=0,0,I45/D45)</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="32" t="n">
+      <c r="A46" s="26" t="n">
         <v>36.43</v>
       </c>
-      <c r="B46" s="32">
+      <c r="B46" s="26">
         <f>A46-$B$12</f>
         <v/>
       </c>
-      <c r="C46" s="32">
+      <c r="C46" s="26">
         <f>MAX(0,A46-$B$6)</f>
         <v/>
       </c>
@@ -8697,15 +9864,15 @@
         <f>IF(C46&lt;=0,0,($B$7+$B$9*C46)*C46)</f>
         <v/>
       </c>
-      <c r="E46" s="26">
+      <c r="E46" s="29">
         <f>IF($B$13=1,D46*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F46" s="26">
+      <c r="F46" s="29">
         <f>IF(A46&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A46&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A46,SS_Amont!$A$11:$A$18,1))+(A46-INDEX(SS_Amont!$A$11:$A$18,MATCH(A46,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A46,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A46,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A46,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A46,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G46" s="34">
+      <c r="G46" s="36">
         <f>F46+E46</f>
         <v/>
       </c>
@@ -8725,16 +9892,24 @@
         <f>IF(C46&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L46" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H46/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M46" s="27">
+        <f>IF(D46&lt;=0,0,I46/D46)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="32" t="n">
+      <c r="A47" s="26" t="n">
         <v>36.48</v>
       </c>
-      <c r="B47" s="32">
+      <c r="B47" s="26">
         <f>A47-$B$12</f>
         <v/>
       </c>
-      <c r="C47" s="32">
+      <c r="C47" s="26">
         <f>MAX(0,A47-$B$6)</f>
         <v/>
       </c>
@@ -8742,15 +9917,15 @@
         <f>IF(C47&lt;=0,0,($B$7+$B$9*C47)*C47)</f>
         <v/>
       </c>
-      <c r="E47" s="26">
+      <c r="E47" s="29">
         <f>IF($B$13=1,D47*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F47" s="26">
+      <c r="F47" s="29">
         <f>IF(A47&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A47&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A47,SS_Amont!$A$11:$A$18,1))+(A47-INDEX(SS_Amont!$A$11:$A$18,MATCH(A47,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A47,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A47,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A47,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A47,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G47" s="34">
+      <c r="G47" s="36">
         <f>F47+E47</f>
         <v/>
       </c>
@@ -8770,16 +9945,24 @@
         <f>IF(C47&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L47" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H47/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M47" s="27">
+        <f>IF(D47&lt;=0,0,I47/D47)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="32" t="n">
+      <c r="A48" s="26" t="n">
         <v>36.53</v>
       </c>
-      <c r="B48" s="32">
+      <c r="B48" s="26">
         <f>A48-$B$12</f>
         <v/>
       </c>
-      <c r="C48" s="32">
+      <c r="C48" s="26">
         <f>MAX(0,A48-$B$6)</f>
         <v/>
       </c>
@@ -8787,15 +9970,15 @@
         <f>IF(C48&lt;=0,0,($B$7+$B$9*C48)*C48)</f>
         <v/>
       </c>
-      <c r="E48" s="26">
+      <c r="E48" s="29">
         <f>IF($B$13=1,D48*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F48" s="26">
+      <c r="F48" s="29">
         <f>IF(A48&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A48&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A48,SS_Amont!$A$11:$A$18,1))+(A48-INDEX(SS_Amont!$A$11:$A$18,MATCH(A48,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A48,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A48,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A48,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A48,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G48" s="34">
+      <c r="G48" s="36">
         <f>F48+E48</f>
         <v/>
       </c>
@@ -8815,16 +9998,24 @@
         <f>IF(C48&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L48" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H48/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M48" s="27">
+        <f>IF(D48&lt;=0,0,I48/D48)</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="32" t="n">
+      <c r="A49" s="26" t="n">
         <v>36.58</v>
       </c>
-      <c r="B49" s="32">
+      <c r="B49" s="26">
         <f>A49-$B$12</f>
         <v/>
       </c>
-      <c r="C49" s="32">
+      <c r="C49" s="26">
         <f>MAX(0,A49-$B$6)</f>
         <v/>
       </c>
@@ -8832,15 +10023,15 @@
         <f>IF(C49&lt;=0,0,($B$7+$B$9*C49)*C49)</f>
         <v/>
       </c>
-      <c r="E49" s="26">
+      <c r="E49" s="29">
         <f>IF($B$13=1,D49*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F49" s="26">
+      <c r="F49" s="29">
         <f>IF(A49&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A49&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A49,SS_Amont!$A$11:$A$18,1))+(A49-INDEX(SS_Amont!$A$11:$A$18,MATCH(A49,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A49,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A49,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A49,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A49,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G49" s="34">
+      <c r="G49" s="36">
         <f>F49+E49</f>
         <v/>
       </c>
@@ -8860,16 +10051,24 @@
         <f>IF(C49&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L49" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H49/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M49" s="27">
+        <f>IF(D49&lt;=0,0,I49/D49)</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="32" t="n">
+      <c r="A50" s="26" t="n">
         <v>36.63</v>
       </c>
-      <c r="B50" s="32">
+      <c r="B50" s="26">
         <f>A50-$B$12</f>
         <v/>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="26">
         <f>MAX(0,A50-$B$6)</f>
         <v/>
       </c>
@@ -8877,15 +10076,15 @@
         <f>IF(C50&lt;=0,0,($B$7+$B$9*C50)*C50)</f>
         <v/>
       </c>
-      <c r="E50" s="26">
+      <c r="E50" s="29">
         <f>IF($B$13=1,D50*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F50" s="26">
+      <c r="F50" s="29">
         <f>IF(A50&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A50&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A50,SS_Amont!$A$11:$A$18,1))+(A50-INDEX(SS_Amont!$A$11:$A$18,MATCH(A50,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A50,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A50,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A50,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A50,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G50" s="34">
+      <c r="G50" s="36">
         <f>F50+E50</f>
         <v/>
       </c>
@@ -8905,16 +10104,24 @@
         <f>IF(C50&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L50" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H50/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M50" s="27">
+        <f>IF(D50&lt;=0,0,I50/D50)</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="32" t="n">
+      <c r="A51" s="26" t="n">
         <v>36.68</v>
       </c>
-      <c r="B51" s="32">
+      <c r="B51" s="26">
         <f>A51-$B$12</f>
         <v/>
       </c>
-      <c r="C51" s="32">
+      <c r="C51" s="26">
         <f>MAX(0,A51-$B$6)</f>
         <v/>
       </c>
@@ -8922,15 +10129,15 @@
         <f>IF(C51&lt;=0,0,($B$7+$B$9*C51)*C51)</f>
         <v/>
       </c>
-      <c r="E51" s="26">
+      <c r="E51" s="29">
         <f>IF($B$13=1,D51*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F51" s="26">
+      <c r="F51" s="29">
         <f>IF(A51&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A51&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A51,SS_Amont!$A$11:$A$18,1))+(A51-INDEX(SS_Amont!$A$11:$A$18,MATCH(A51,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A51,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A51,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A51,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A51,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G51" s="34">
+      <c r="G51" s="36">
         <f>F51+E51</f>
         <v/>
       </c>
@@ -8950,16 +10157,24 @@
         <f>IF(C51&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L51" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H51/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M51" s="27">
+        <f>IF(D51&lt;=0,0,I51/D51)</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="32" t="n">
+      <c r="A52" s="26" t="n">
         <v>36.73</v>
       </c>
-      <c r="B52" s="32">
+      <c r="B52" s="26">
         <f>A52-$B$12</f>
         <v/>
       </c>
-      <c r="C52" s="32">
+      <c r="C52" s="26">
         <f>MAX(0,A52-$B$6)</f>
         <v/>
       </c>
@@ -8967,15 +10182,15 @@
         <f>IF(C52&lt;=0,0,($B$7+$B$9*C52)*C52)</f>
         <v/>
       </c>
-      <c r="E52" s="26">
+      <c r="E52" s="29">
         <f>IF($B$13=1,D52*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F52" s="26">
+      <c r="F52" s="29">
         <f>IF(A52&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A52&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A52,SS_Amont!$A$11:$A$18,1))+(A52-INDEX(SS_Amont!$A$11:$A$18,MATCH(A52,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A52,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A52,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A52,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A52,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G52" s="34">
+      <c r="G52" s="36">
         <f>F52+E52</f>
         <v/>
       </c>
@@ -8995,16 +10210,24 @@
         <f>IF(C52&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L52" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H52/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M52" s="27">
+        <f>IF(D52&lt;=0,0,I52/D52)</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="32" t="n">
+      <c r="A53" s="26" t="n">
         <v>36.78</v>
       </c>
-      <c r="B53" s="32">
+      <c r="B53" s="26">
         <f>A53-$B$12</f>
         <v/>
       </c>
-      <c r="C53" s="32">
+      <c r="C53" s="26">
         <f>MAX(0,A53-$B$6)</f>
         <v/>
       </c>
@@ -9012,15 +10235,15 @@
         <f>IF(C53&lt;=0,0,($B$7+$B$9*C53)*C53)</f>
         <v/>
       </c>
-      <c r="E53" s="26">
+      <c r="E53" s="29">
         <f>IF($B$13=1,D53*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F53" s="26">
+      <c r="F53" s="29">
         <f>IF(A53&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A53&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A53,SS_Amont!$A$11:$A$18,1))+(A53-INDEX(SS_Amont!$A$11:$A$18,MATCH(A53,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A53,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A53,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A53,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A53,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G53" s="34">
+      <c r="G53" s="36">
         <f>F53+E53</f>
         <v/>
       </c>
@@ -9040,16 +10263,24 @@
         <f>IF(C53&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L53" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H53/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M53" s="27">
+        <f>IF(D53&lt;=0,0,I53/D53)</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="32" t="n">
+      <c r="A54" s="26" t="n">
         <v>36.83</v>
       </c>
-      <c r="B54" s="32">
+      <c r="B54" s="26">
         <f>A54-$B$12</f>
         <v/>
       </c>
-      <c r="C54" s="32">
+      <c r="C54" s="26">
         <f>MAX(0,A54-$B$6)</f>
         <v/>
       </c>
@@ -9057,15 +10288,15 @@
         <f>IF(C54&lt;=0,0,($B$7+$B$9*C54)*C54)</f>
         <v/>
       </c>
-      <c r="E54" s="26">
+      <c r="E54" s="29">
         <f>IF($B$13=1,D54*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F54" s="26">
+      <c r="F54" s="29">
         <f>IF(A54&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A54&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A54,SS_Amont!$A$11:$A$18,1))+(A54-INDEX(SS_Amont!$A$11:$A$18,MATCH(A54,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A54,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A54,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A54,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A54,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G54" s="34">
+      <c r="G54" s="36">
         <f>F54+E54</f>
         <v/>
       </c>
@@ -9085,16 +10316,24 @@
         <f>IF(C54&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L54" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H54/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M54" s="27">
+        <f>IF(D54&lt;=0,0,I54/D54)</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="32" t="n">
+      <c r="A55" s="26" t="n">
         <v>36.88</v>
       </c>
-      <c r="B55" s="32">
+      <c r="B55" s="26">
         <f>A55-$B$12</f>
         <v/>
       </c>
-      <c r="C55" s="32">
+      <c r="C55" s="26">
         <f>MAX(0,A55-$B$6)</f>
         <v/>
       </c>
@@ -9102,15 +10341,15 @@
         <f>IF(C55&lt;=0,0,($B$7+$B$9*C55)*C55)</f>
         <v/>
       </c>
-      <c r="E55" s="26">
+      <c r="E55" s="29">
         <f>IF($B$13=1,D55*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F55" s="26">
+      <c r="F55" s="29">
         <f>IF(A55&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A55&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A55,SS_Amont!$A$11:$A$18,1))+(A55-INDEX(SS_Amont!$A$11:$A$18,MATCH(A55,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A55,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A55,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A55,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A55,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G55" s="34">
+      <c r="G55" s="36">
         <f>F55+E55</f>
         <v/>
       </c>
@@ -9130,16 +10369,24 @@
         <f>IF(C55&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L55" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H55/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M55" s="27">
+        <f>IF(D55&lt;=0,0,I55/D55)</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="32" t="n">
+      <c r="A56" s="26" t="n">
         <v>36.93</v>
       </c>
-      <c r="B56" s="32">
+      <c r="B56" s="26">
         <f>A56-$B$12</f>
         <v/>
       </c>
-      <c r="C56" s="32">
+      <c r="C56" s="26">
         <f>MAX(0,A56-$B$6)</f>
         <v/>
       </c>
@@ -9147,15 +10394,15 @@
         <f>IF(C56&lt;=0,0,($B$7+$B$9*C56)*C56)</f>
         <v/>
       </c>
-      <c r="E56" s="26">
+      <c r="E56" s="29">
         <f>IF($B$13=1,D56*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F56" s="26">
+      <c r="F56" s="29">
         <f>IF(A56&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A56&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A56,SS_Amont!$A$11:$A$18,1))+(A56-INDEX(SS_Amont!$A$11:$A$18,MATCH(A56,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A56,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A56,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A56,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A56,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G56" s="34">
+      <c r="G56" s="36">
         <f>F56+E56</f>
         <v/>
       </c>
@@ -9175,16 +10422,24 @@
         <f>IF(C56&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L56" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H56/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M56" s="27">
+        <f>IF(D56&lt;=0,0,I56/D56)</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="32" t="n">
+      <c r="A57" s="26" t="n">
         <v>36.98</v>
       </c>
-      <c r="B57" s="32">
+      <c r="B57" s="26">
         <f>A57-$B$12</f>
         <v/>
       </c>
-      <c r="C57" s="32">
+      <c r="C57" s="26">
         <f>MAX(0,A57-$B$6)</f>
         <v/>
       </c>
@@ -9192,15 +10447,15 @@
         <f>IF(C57&lt;=0,0,($B$7+$B$9*C57)*C57)</f>
         <v/>
       </c>
-      <c r="E57" s="26">
+      <c r="E57" s="29">
         <f>IF($B$13=1,D57*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F57" s="26">
+      <c r="F57" s="29">
         <f>IF(A57&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A57&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A57,SS_Amont!$A$11:$A$18,1))+(A57-INDEX(SS_Amont!$A$11:$A$18,MATCH(A57,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A57,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A57,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A57,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A57,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G57" s="34">
+      <c r="G57" s="36">
         <f>F57+E57</f>
         <v/>
       </c>
@@ -9220,16 +10475,24 @@
         <f>IF(C57&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L57" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H57/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M57" s="27">
+        <f>IF(D57&lt;=0,0,I57/D57)</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="32" t="n">
+      <c r="A58" s="26" t="n">
         <v>37.03</v>
       </c>
-      <c r="B58" s="32">
+      <c r="B58" s="26">
         <f>A58-$B$12</f>
         <v/>
       </c>
-      <c r="C58" s="32">
+      <c r="C58" s="26">
         <f>MAX(0,A58-$B$6)</f>
         <v/>
       </c>
@@ -9237,15 +10500,15 @@
         <f>IF(C58&lt;=0,0,($B$7+$B$9*C58)*C58)</f>
         <v/>
       </c>
-      <c r="E58" s="26">
+      <c r="E58" s="29">
         <f>IF($B$13=1,D58*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F58" s="26">
+      <c r="F58" s="29">
         <f>IF(A58&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A58&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A58,SS_Amont!$A$11:$A$18,1))+(A58-INDEX(SS_Amont!$A$11:$A$18,MATCH(A58,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A58,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A58,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A58,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A58,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G58" s="34">
+      <c r="G58" s="36">
         <f>F58+E58</f>
         <v/>
       </c>
@@ -9265,16 +10528,24 @@
         <f>IF(C58&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L58" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H58/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M58" s="27">
+        <f>IF(D58&lt;=0,0,I58/D58)</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="32" t="n">
+      <c r="A59" s="26" t="n">
         <v>37.08</v>
       </c>
-      <c r="B59" s="32">
+      <c r="B59" s="26">
         <f>A59-$B$12</f>
         <v/>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="26">
         <f>MAX(0,A59-$B$6)</f>
         <v/>
       </c>
@@ -9282,15 +10553,15 @@
         <f>IF(C59&lt;=0,0,($B$7+$B$9*C59)*C59)</f>
         <v/>
       </c>
-      <c r="E59" s="26">
+      <c r="E59" s="29">
         <f>IF($B$13=1,D59*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F59" s="26">
+      <c r="F59" s="29">
         <f>IF(A59&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A59&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A59,SS_Amont!$A$11:$A$18,1))+(A59-INDEX(SS_Amont!$A$11:$A$18,MATCH(A59,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A59,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A59,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A59,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A59,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G59" s="34">
+      <c r="G59" s="36">
         <f>F59+E59</f>
         <v/>
       </c>
@@ -9310,16 +10581,24 @@
         <f>IF(C59&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L59" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H59/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M59" s="27">
+        <f>IF(D59&lt;=0,0,I59/D59)</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="32" t="n">
+      <c r="A60" s="26" t="n">
         <v>37.13</v>
       </c>
-      <c r="B60" s="32">
+      <c r="B60" s="26">
         <f>A60-$B$12</f>
         <v/>
       </c>
-      <c r="C60" s="32">
+      <c r="C60" s="26">
         <f>MAX(0,A60-$B$6)</f>
         <v/>
       </c>
@@ -9327,15 +10606,15 @@
         <f>IF(C60&lt;=0,0,($B$7+$B$9*C60)*C60)</f>
         <v/>
       </c>
-      <c r="E60" s="26">
+      <c r="E60" s="29">
         <f>IF($B$13=1,D60*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F60" s="26">
+      <c r="F60" s="29">
         <f>IF(A60&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A60&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A60,SS_Amont!$A$11:$A$18,1))+(A60-INDEX(SS_Amont!$A$11:$A$18,MATCH(A60,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A60,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A60,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A60,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A60,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G60" s="34">
+      <c r="G60" s="36">
         <f>F60+E60</f>
         <v/>
       </c>
@@ -9355,16 +10634,24 @@
         <f>IF(C60&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L60" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H60/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M60" s="27">
+        <f>IF(D60&lt;=0,0,I60/D60)</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="32" t="n">
+      <c r="A61" s="26" t="n">
         <v>37.18</v>
       </c>
-      <c r="B61" s="32">
+      <c r="B61" s="26">
         <f>A61-$B$12</f>
         <v/>
       </c>
-      <c r="C61" s="32">
+      <c r="C61" s="26">
         <f>MAX(0,A61-$B$6)</f>
         <v/>
       </c>
@@ -9372,15 +10659,15 @@
         <f>IF(C61&lt;=0,0,($B$7+$B$9*C61)*C61)</f>
         <v/>
       </c>
-      <c r="E61" s="26">
+      <c r="E61" s="29">
         <f>IF($B$13=1,D61*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F61" s="26">
+      <c r="F61" s="29">
         <f>IF(A61&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A61&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A61,SS_Amont!$A$11:$A$18,1))+(A61-INDEX(SS_Amont!$A$11:$A$18,MATCH(A61,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A61,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A61,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A61,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A61,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G61" s="34">
+      <c r="G61" s="36">
         <f>F61+E61</f>
         <v/>
       </c>
@@ -9400,16 +10687,24 @@
         <f>IF(C61&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L61" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H61/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M61" s="27">
+        <f>IF(D61&lt;=0,0,I61/D61)</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="32" t="n">
+      <c r="A62" s="26" t="n">
         <v>37.23</v>
       </c>
-      <c r="B62" s="32">
+      <c r="B62" s="26">
         <f>A62-$B$12</f>
         <v/>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="26">
         <f>MAX(0,A62-$B$6)</f>
         <v/>
       </c>
@@ -9417,15 +10712,15 @@
         <f>IF(C62&lt;=0,0,($B$7+$B$9*C62)*C62)</f>
         <v/>
       </c>
-      <c r="E62" s="26">
+      <c r="E62" s="29">
         <f>IF($B$13=1,D62*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F62" s="26">
+      <c r="F62" s="29">
         <f>IF(A62&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A62&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A62,SS_Amont!$A$11:$A$18,1))+(A62-INDEX(SS_Amont!$A$11:$A$18,MATCH(A62,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A62,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A62,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A62,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A62,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G62" s="34">
+      <c r="G62" s="36">
         <f>F62+E62</f>
         <v/>
       </c>
@@ -9445,16 +10740,24 @@
         <f>IF(C62&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L62" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H62/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M62" s="27">
+        <f>IF(D62&lt;=0,0,I62/D62)</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="32" t="n">
+      <c r="A63" s="26" t="n">
         <v>37.28</v>
       </c>
-      <c r="B63" s="32">
+      <c r="B63" s="26">
         <f>A63-$B$12</f>
         <v/>
       </c>
-      <c r="C63" s="32">
+      <c r="C63" s="26">
         <f>MAX(0,A63-$B$6)</f>
         <v/>
       </c>
@@ -9462,15 +10765,15 @@
         <f>IF(C63&lt;=0,0,($B$7+$B$9*C63)*C63)</f>
         <v/>
       </c>
-      <c r="E63" s="26">
+      <c r="E63" s="29">
         <f>IF($B$13=1,D63*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F63" s="26">
+      <c r="F63" s="29">
         <f>IF(A63&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A63&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A63,SS_Amont!$A$11:$A$18,1))+(A63-INDEX(SS_Amont!$A$11:$A$18,MATCH(A63,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A63,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A63,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A63,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A63,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G63" s="34">
+      <c r="G63" s="36">
         <f>F63+E63</f>
         <v/>
       </c>
@@ -9490,16 +10793,24 @@
         <f>IF(C63&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L63" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H63/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M63" s="27">
+        <f>IF(D63&lt;=0,0,I63/D63)</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="32" t="n">
+      <c r="A64" s="26" t="n">
         <v>37.33</v>
       </c>
-      <c r="B64" s="32">
+      <c r="B64" s="26">
         <f>A64-$B$12</f>
         <v/>
       </c>
-      <c r="C64" s="32">
+      <c r="C64" s="26">
         <f>MAX(0,A64-$B$6)</f>
         <v/>
       </c>
@@ -9507,15 +10818,15 @@
         <f>IF(C64&lt;=0,0,($B$7+$B$9*C64)*C64)</f>
         <v/>
       </c>
-      <c r="E64" s="26">
+      <c r="E64" s="29">
         <f>IF($B$13=1,D64*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F64" s="26">
+      <c r="F64" s="29">
         <f>IF(A64&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A64&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A64,SS_Amont!$A$11:$A$18,1))+(A64-INDEX(SS_Amont!$A$11:$A$18,MATCH(A64,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A64,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A64,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A64,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A64,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G64" s="34">
+      <c r="G64" s="36">
         <f>F64+E64</f>
         <v/>
       </c>
@@ -9535,16 +10846,24 @@
         <f>IF(C64&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L64" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H64/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M64" s="27">
+        <f>IF(D64&lt;=0,0,I64/D64)</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="32" t="n">
+      <c r="A65" s="26" t="n">
         <v>37.38</v>
       </c>
-      <c r="B65" s="32">
+      <c r="B65" s="26">
         <f>A65-$B$12</f>
         <v/>
       </c>
-      <c r="C65" s="32">
+      <c r="C65" s="26">
         <f>MAX(0,A65-$B$6)</f>
         <v/>
       </c>
@@ -9552,15 +10871,15 @@
         <f>IF(C65&lt;=0,0,($B$7+$B$9*C65)*C65)</f>
         <v/>
       </c>
-      <c r="E65" s="26">
+      <c r="E65" s="29">
         <f>IF($B$13=1,D65*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F65" s="26">
+      <c r="F65" s="29">
         <f>IF(A65&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A65&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A65,SS_Amont!$A$11:$A$18,1))+(A65-INDEX(SS_Amont!$A$11:$A$18,MATCH(A65,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A65,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A65,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A65,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A65,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G65" s="34">
+      <c r="G65" s="36">
         <f>F65+E65</f>
         <v/>
       </c>
@@ -9580,16 +10899,24 @@
         <f>IF(C65&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L65" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H65/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M65" s="27">
+        <f>IF(D65&lt;=0,0,I65/D65)</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="32" t="n">
+      <c r="A66" s="26" t="n">
         <v>37.43</v>
       </c>
-      <c r="B66" s="32">
+      <c r="B66" s="26">
         <f>A66-$B$12</f>
         <v/>
       </c>
-      <c r="C66" s="32">
+      <c r="C66" s="26">
         <f>MAX(0,A66-$B$6)</f>
         <v/>
       </c>
@@ -9597,15 +10924,15 @@
         <f>IF(C66&lt;=0,0,($B$7+$B$9*C66)*C66)</f>
         <v/>
       </c>
-      <c r="E66" s="26">
+      <c r="E66" s="29">
         <f>IF($B$13=1,D66*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F66" s="26">
+      <c r="F66" s="29">
         <f>IF(A66&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A66&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A66,SS_Amont!$A$11:$A$18,1))+(A66-INDEX(SS_Amont!$A$11:$A$18,MATCH(A66,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A66,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A66,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A66,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A66,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G66" s="34">
+      <c r="G66" s="36">
         <f>F66+E66</f>
         <v/>
       </c>
@@ -9625,16 +10952,24 @@
         <f>IF(C66&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L66" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H66/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M66" s="27">
+        <f>IF(D66&lt;=0,0,I66/D66)</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="32" t="n">
+      <c r="A67" s="26" t="n">
         <v>37.48</v>
       </c>
-      <c r="B67" s="32">
+      <c r="B67" s="26">
         <f>A67-$B$12</f>
         <v/>
       </c>
-      <c r="C67" s="32">
+      <c r="C67" s="26">
         <f>MAX(0,A67-$B$6)</f>
         <v/>
       </c>
@@ -9642,15 +10977,15 @@
         <f>IF(C67&lt;=0,0,($B$7+$B$9*C67)*C67)</f>
         <v/>
       </c>
-      <c r="E67" s="26">
+      <c r="E67" s="29">
         <f>IF($B$13=1,D67*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F67" s="26">
+      <c r="F67" s="29">
         <f>IF(A67&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A67&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A67,SS_Amont!$A$11:$A$18,1))+(A67-INDEX(SS_Amont!$A$11:$A$18,MATCH(A67,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A67,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A67,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A67,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A67,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G67" s="34">
+      <c r="G67" s="36">
         <f>F67+E67</f>
         <v/>
       </c>
@@ -9670,16 +11005,24 @@
         <f>IF(C67&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L67" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H67/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M67" s="27">
+        <f>IF(D67&lt;=0,0,I67/D67)</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="32" t="n">
+      <c r="A68" s="26" t="n">
         <v>37.53</v>
       </c>
-      <c r="B68" s="32">
+      <c r="B68" s="26">
         <f>A68-$B$12</f>
         <v/>
       </c>
-      <c r="C68" s="32">
+      <c r="C68" s="26">
         <f>MAX(0,A68-$B$6)</f>
         <v/>
       </c>
@@ -9687,15 +11030,15 @@
         <f>IF(C68&lt;=0,0,($B$7+$B$9*C68)*C68)</f>
         <v/>
       </c>
-      <c r="E68" s="26">
+      <c r="E68" s="29">
         <f>IF($B$13=1,D68*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F68" s="26">
+      <c r="F68" s="29">
         <f>IF(A68&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A68&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A68,SS_Amont!$A$11:$A$18,1))+(A68-INDEX(SS_Amont!$A$11:$A$18,MATCH(A68,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A68,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A68,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A68,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A68,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G68" s="34">
+      <c r="G68" s="36">
         <f>F68+E68</f>
         <v/>
       </c>
@@ -9715,16 +11058,24 @@
         <f>IF(C68&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L68" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H68/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M68" s="27">
+        <f>IF(D68&lt;=0,0,I68/D68)</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="32" t="n">
+      <c r="A69" s="26" t="n">
         <v>37.58</v>
       </c>
-      <c r="B69" s="32">
+      <c r="B69" s="26">
         <f>A69-$B$12</f>
         <v/>
       </c>
-      <c r="C69" s="32">
+      <c r="C69" s="26">
         <f>MAX(0,A69-$B$6)</f>
         <v/>
       </c>
@@ -9732,15 +11083,15 @@
         <f>IF(C69&lt;=0,0,($B$7+$B$9*C69)*C69)</f>
         <v/>
       </c>
-      <c r="E69" s="26">
+      <c r="E69" s="29">
         <f>IF($B$13=1,D69*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F69" s="26">
+      <c r="F69" s="29">
         <f>IF(A69&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A69&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A69,SS_Amont!$A$11:$A$18,1))+(A69-INDEX(SS_Amont!$A$11:$A$18,MATCH(A69,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A69,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A69,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A69,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A69,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G69" s="34">
+      <c r="G69" s="36">
         <f>F69+E69</f>
         <v/>
       </c>
@@ -9760,16 +11111,24 @@
         <f>IF(C69&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L69" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H69/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M69" s="27">
+        <f>IF(D69&lt;=0,0,I69/D69)</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="32" t="n">
+      <c r="A70" s="26" t="n">
         <v>37.63</v>
       </c>
-      <c r="B70" s="32">
+      <c r="B70" s="26">
         <f>A70-$B$12</f>
         <v/>
       </c>
-      <c r="C70" s="32">
+      <c r="C70" s="26">
         <f>MAX(0,A70-$B$6)</f>
         <v/>
       </c>
@@ -9777,15 +11136,15 @@
         <f>IF(C70&lt;=0,0,($B$7+$B$9*C70)*C70)</f>
         <v/>
       </c>
-      <c r="E70" s="26">
+      <c r="E70" s="29">
         <f>IF($B$13=1,D70*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F70" s="26">
+      <c r="F70" s="29">
         <f>IF(A70&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A70&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A70,SS_Amont!$A$11:$A$18,1))+(A70-INDEX(SS_Amont!$A$11:$A$18,MATCH(A70,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A70,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A70,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A70,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A70,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G70" s="34">
+      <c r="G70" s="36">
         <f>F70+E70</f>
         <v/>
       </c>
@@ -9805,16 +11164,24 @@
         <f>IF(C70&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L70" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H70/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M70" s="27">
+        <f>IF(D70&lt;=0,0,I70/D70)</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="32" t="n">
+      <c r="A71" s="26" t="n">
         <v>37.68</v>
       </c>
-      <c r="B71" s="32">
+      <c r="B71" s="26">
         <f>A71-$B$12</f>
         <v/>
       </c>
-      <c r="C71" s="32">
+      <c r="C71" s="26">
         <f>MAX(0,A71-$B$6)</f>
         <v/>
       </c>
@@ -9822,15 +11189,15 @@
         <f>IF(C71&lt;=0,0,($B$7+$B$9*C71)*C71)</f>
         <v/>
       </c>
-      <c r="E71" s="26">
+      <c r="E71" s="29">
         <f>IF($B$13=1,D71*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F71" s="26">
+      <c r="F71" s="29">
         <f>IF(A71&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A71&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A71,SS_Amont!$A$11:$A$18,1))+(A71-INDEX(SS_Amont!$A$11:$A$18,MATCH(A71,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A71,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A71,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A71,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A71,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G71" s="34">
+      <c r="G71" s="36">
         <f>F71+E71</f>
         <v/>
       </c>
@@ -9850,16 +11217,24 @@
         <f>IF(C71&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L71" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H71/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M71" s="27">
+        <f>IF(D71&lt;=0,0,I71/D71)</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="32" t="n">
+      <c r="A72" s="26" t="n">
         <v>37.73</v>
       </c>
-      <c r="B72" s="32">
+      <c r="B72" s="26">
         <f>A72-$B$12</f>
         <v/>
       </c>
-      <c r="C72" s="32">
+      <c r="C72" s="26">
         <f>MAX(0,A72-$B$6)</f>
         <v/>
       </c>
@@ -9867,15 +11242,15 @@
         <f>IF(C72&lt;=0,0,($B$7+$B$9*C72)*C72)</f>
         <v/>
       </c>
-      <c r="E72" s="26">
+      <c r="E72" s="29">
         <f>IF($B$13=1,D72*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F72" s="26">
+      <c r="F72" s="29">
         <f>IF(A72&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A72&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A72,SS_Amont!$A$11:$A$18,1))+(A72-INDEX(SS_Amont!$A$11:$A$18,MATCH(A72,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A72,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A72,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A72,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A72,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G72" s="34">
+      <c r="G72" s="36">
         <f>F72+E72</f>
         <v/>
       </c>
@@ -9895,16 +11270,24 @@
         <f>IF(C72&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L72" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H72/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M72" s="27">
+        <f>IF(D72&lt;=0,0,I72/D72)</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="32" t="n">
+      <c r="A73" s="26" t="n">
         <v>37.78</v>
       </c>
-      <c r="B73" s="32">
+      <c r="B73" s="26">
         <f>A73-$B$12</f>
         <v/>
       </c>
-      <c r="C73" s="32">
+      <c r="C73" s="26">
         <f>MAX(0,A73-$B$6)</f>
         <v/>
       </c>
@@ -9912,15 +11295,15 @@
         <f>IF(C73&lt;=0,0,($B$7+$B$9*C73)*C73)</f>
         <v/>
       </c>
-      <c r="E73" s="26">
+      <c r="E73" s="29">
         <f>IF($B$13=1,D73*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F73" s="26">
+      <c r="F73" s="29">
         <f>IF(A73&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A73&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A73,SS_Amont!$A$11:$A$18,1))+(A73-INDEX(SS_Amont!$A$11:$A$18,MATCH(A73,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A73,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A73,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A73,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A73,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G73" s="34">
+      <c r="G73" s="36">
         <f>F73+E73</f>
         <v/>
       </c>
@@ -9940,16 +11323,24 @@
         <f>IF(C73&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L73" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H73/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M73" s="27">
+        <f>IF(D73&lt;=0,0,I73/D73)</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="32" t="n">
+      <c r="A74" s="26" t="n">
         <v>37.83</v>
       </c>
-      <c r="B74" s="32">
+      <c r="B74" s="26">
         <f>A74-$B$12</f>
         <v/>
       </c>
-      <c r="C74" s="32">
+      <c r="C74" s="26">
         <f>MAX(0,A74-$B$6)</f>
         <v/>
       </c>
@@ -9957,15 +11348,15 @@
         <f>IF(C74&lt;=0,0,($B$7+$B$9*C74)*C74)</f>
         <v/>
       </c>
-      <c r="E74" s="26">
+      <c r="E74" s="29">
         <f>IF($B$13=1,D74*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F74" s="26">
+      <c r="F74" s="29">
         <f>IF(A74&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A74&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A74,SS_Amont!$A$11:$A$18,1))+(A74-INDEX(SS_Amont!$A$11:$A$18,MATCH(A74,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A74,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A74,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A74,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A74,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G74" s="34">
+      <c r="G74" s="36">
         <f>F74+E74</f>
         <v/>
       </c>
@@ -9985,16 +11376,24 @@
         <f>IF(C74&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L74" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H74/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M74" s="27">
+        <f>IF(D74&lt;=0,0,I74/D74)</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="32" t="n">
+      <c r="A75" s="26" t="n">
         <v>37.88</v>
       </c>
-      <c r="B75" s="32">
+      <c r="B75" s="26">
         <f>A75-$B$12</f>
         <v/>
       </c>
-      <c r="C75" s="32">
+      <c r="C75" s="26">
         <f>MAX(0,A75-$B$6)</f>
         <v/>
       </c>
@@ -10002,15 +11401,15 @@
         <f>IF(C75&lt;=0,0,($B$7+$B$9*C75)*C75)</f>
         <v/>
       </c>
-      <c r="E75" s="26">
+      <c r="E75" s="29">
         <f>IF($B$13=1,D75*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F75" s="26">
+      <c r="F75" s="29">
         <f>IF(A75&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A75&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A75,SS_Amont!$A$11:$A$18,1))+(A75-INDEX(SS_Amont!$A$11:$A$18,MATCH(A75,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A75,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A75,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A75,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A75,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G75" s="34">
+      <c r="G75" s="36">
         <f>F75+E75</f>
         <v/>
       </c>
@@ -10030,16 +11429,24 @@
         <f>IF(C75&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L75" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H75/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M75" s="27">
+        <f>IF(D75&lt;=0,0,I75/D75)</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="32" t="n">
+      <c r="A76" s="26" t="n">
         <v>37.93</v>
       </c>
-      <c r="B76" s="32">
+      <c r="B76" s="26">
         <f>A76-$B$12</f>
         <v/>
       </c>
-      <c r="C76" s="32">
+      <c r="C76" s="26">
         <f>MAX(0,A76-$B$6)</f>
         <v/>
       </c>
@@ -10047,15 +11454,15 @@
         <f>IF(C76&lt;=0,0,($B$7+$B$9*C76)*C76)</f>
         <v/>
       </c>
-      <c r="E76" s="26">
+      <c r="E76" s="29">
         <f>IF($B$13=1,D76*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F76" s="26">
+      <c r="F76" s="29">
         <f>IF(A76&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A76&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A76,SS_Amont!$A$11:$A$18,1))+(A76-INDEX(SS_Amont!$A$11:$A$18,MATCH(A76,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A76,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A76,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A76,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A76,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G76" s="34">
+      <c r="G76" s="36">
         <f>F76+E76</f>
         <v/>
       </c>
@@ -10075,16 +11482,24 @@
         <f>IF(C76&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L76" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H76/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M76" s="27">
+        <f>IF(D76&lt;=0,0,I76/D76)</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="32" t="n">
+      <c r="A77" s="26" t="n">
         <v>37.98</v>
       </c>
-      <c r="B77" s="32">
+      <c r="B77" s="26">
         <f>A77-$B$12</f>
         <v/>
       </c>
-      <c r="C77" s="32">
+      <c r="C77" s="26">
         <f>MAX(0,A77-$B$6)</f>
         <v/>
       </c>
@@ -10092,15 +11507,15 @@
         <f>IF(C77&lt;=0,0,($B$7+$B$9*C77)*C77)</f>
         <v/>
       </c>
-      <c r="E77" s="26">
+      <c r="E77" s="29">
         <f>IF($B$13=1,D77*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F77" s="26">
+      <c r="F77" s="29">
         <f>IF(A77&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A77&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A77,SS_Amont!$A$11:$A$18,1))+(A77-INDEX(SS_Amont!$A$11:$A$18,MATCH(A77,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A77,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A77,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A77,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A77,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G77" s="34">
+      <c r="G77" s="36">
         <f>F77+E77</f>
         <v/>
       </c>
@@ -10120,16 +11535,24 @@
         <f>IF(C77&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L77" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H77/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M77" s="27">
+        <f>IF(D77&lt;=0,0,I77/D77)</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="32" t="n">
+      <c r="A78" s="26" t="n">
         <v>38.03</v>
       </c>
-      <c r="B78" s="32">
+      <c r="B78" s="26">
         <f>A78-$B$12</f>
         <v/>
       </c>
-      <c r="C78" s="32">
+      <c r="C78" s="26">
         <f>MAX(0,A78-$B$6)</f>
         <v/>
       </c>
@@ -10137,15 +11560,15 @@
         <f>IF(C78&lt;=0,0,($B$7+$B$9*C78)*C78)</f>
         <v/>
       </c>
-      <c r="E78" s="26">
+      <c r="E78" s="29">
         <f>IF($B$13=1,D78*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F78" s="26">
+      <c r="F78" s="29">
         <f>IF(A78&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A78&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A78,SS_Amont!$A$11:$A$18,1))+(A78-INDEX(SS_Amont!$A$11:$A$18,MATCH(A78,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A78,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A78,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A78,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A78,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G78" s="34">
+      <c r="G78" s="36">
         <f>F78+E78</f>
         <v/>
       </c>
@@ -10165,16 +11588,24 @@
         <f>IF(C78&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L78" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H78/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M78" s="27">
+        <f>IF(D78&lt;=0,0,I78/D78)</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="32" t="n">
+      <c r="A79" s="26" t="n">
         <v>38.08</v>
       </c>
-      <c r="B79" s="32">
+      <c r="B79" s="26">
         <f>A79-$B$12</f>
         <v/>
       </c>
-      <c r="C79" s="32">
+      <c r="C79" s="26">
         <f>MAX(0,A79-$B$6)</f>
         <v/>
       </c>
@@ -10182,15 +11613,15 @@
         <f>IF(C79&lt;=0,0,($B$7+$B$9*C79)*C79)</f>
         <v/>
       </c>
-      <c r="E79" s="26">
+      <c r="E79" s="29">
         <f>IF($B$13=1,D79*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F79" s="26">
+      <c r="F79" s="29">
         <f>IF(A79&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A79&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A79,SS_Amont!$A$11:$A$18,1))+(A79-INDEX(SS_Amont!$A$11:$A$18,MATCH(A79,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A79,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A79,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A79,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A79,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G79" s="34">
+      <c r="G79" s="36">
         <f>F79+E79</f>
         <v/>
       </c>
@@ -10210,16 +11641,24 @@
         <f>IF(C79&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L79" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H79/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M79" s="27">
+        <f>IF(D79&lt;=0,0,I79/D79)</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="32" t="n">
+      <c r="A80" s="26" t="n">
         <v>38.13</v>
       </c>
-      <c r="B80" s="32">
+      <c r="B80" s="26">
         <f>A80-$B$12</f>
         <v/>
       </c>
-      <c r="C80" s="32">
+      <c r="C80" s="26">
         <f>MAX(0,A80-$B$6)</f>
         <v/>
       </c>
@@ -10227,15 +11666,15 @@
         <f>IF(C80&lt;=0,0,($B$7+$B$9*C80)*C80)</f>
         <v/>
       </c>
-      <c r="E80" s="26">
+      <c r="E80" s="29">
         <f>IF($B$13=1,D80*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F80" s="26">
+      <c r="F80" s="29">
         <f>IF(A80&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A80&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A80,SS_Amont!$A$11:$A$18,1))+(A80-INDEX(SS_Amont!$A$11:$A$18,MATCH(A80,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A80,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A80,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A80,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A80,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G80" s="34">
+      <c r="G80" s="36">
         <f>F80+E80</f>
         <v/>
       </c>
@@ -10255,16 +11694,24 @@
         <f>IF(C80&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L80" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H80/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M80" s="27">
+        <f>IF(D80&lt;=0,0,I80/D80)</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="32" t="n">
+      <c r="A81" s="26" t="n">
         <v>38.18</v>
       </c>
-      <c r="B81" s="32">
+      <c r="B81" s="26">
         <f>A81-$B$12</f>
         <v/>
       </c>
-      <c r="C81" s="32">
+      <c r="C81" s="26">
         <f>MAX(0,A81-$B$6)</f>
         <v/>
       </c>
@@ -10272,15 +11719,15 @@
         <f>IF(C81&lt;=0,0,($B$7+$B$9*C81)*C81)</f>
         <v/>
       </c>
-      <c r="E81" s="26">
+      <c r="E81" s="29">
         <f>IF($B$13=1,D81*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F81" s="26">
+      <c r="F81" s="29">
         <f>IF(A81&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A81&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A81,SS_Amont!$A$11:$A$18,1))+(A81-INDEX(SS_Amont!$A$11:$A$18,MATCH(A81,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A81,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A81,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A81,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A81,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G81" s="34">
+      <c r="G81" s="36">
         <f>F81+E81</f>
         <v/>
       </c>
@@ -10300,16 +11747,24 @@
         <f>IF(C81&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L81" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H81/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M81" s="27">
+        <f>IF(D81&lt;=0,0,I81/D81)</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="32" t="n">
+      <c r="A82" s="26" t="n">
         <v>38.23</v>
       </c>
-      <c r="B82" s="32">
+      <c r="B82" s="26">
         <f>A82-$B$12</f>
         <v/>
       </c>
-      <c r="C82" s="32">
+      <c r="C82" s="26">
         <f>MAX(0,A82-$B$6)</f>
         <v/>
       </c>
@@ -10317,15 +11772,15 @@
         <f>IF(C82&lt;=0,0,($B$7+$B$9*C82)*C82)</f>
         <v/>
       </c>
-      <c r="E82" s="26">
+      <c r="E82" s="29">
         <f>IF($B$13=1,D82*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F82" s="26">
+      <c r="F82" s="29">
         <f>IF(A82&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A82&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A82,SS_Amont!$A$11:$A$18,1))+(A82-INDEX(SS_Amont!$A$11:$A$18,MATCH(A82,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A82,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A82,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A82,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A82,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G82" s="34">
+      <c r="G82" s="36">
         <f>F82+E82</f>
         <v/>
       </c>
@@ -10345,16 +11800,24 @@
         <f>IF(C82&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L82" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H82/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M82" s="27">
+        <f>IF(D82&lt;=0,0,I82/D82)</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="32" t="n">
+      <c r="A83" s="26" t="n">
         <v>38.28</v>
       </c>
-      <c r="B83" s="32">
+      <c r="B83" s="26">
         <f>A83-$B$12</f>
         <v/>
       </c>
-      <c r="C83" s="32">
+      <c r="C83" s="26">
         <f>MAX(0,A83-$B$6)</f>
         <v/>
       </c>
@@ -10362,15 +11825,15 @@
         <f>IF(C83&lt;=0,0,($B$7+$B$9*C83)*C83)</f>
         <v/>
       </c>
-      <c r="E83" s="26">
+      <c r="E83" s="29">
         <f>IF($B$13=1,D83*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F83" s="26">
+      <c r="F83" s="29">
         <f>IF(A83&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A83&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A83,SS_Amont!$A$11:$A$18,1))+(A83-INDEX(SS_Amont!$A$11:$A$18,MATCH(A83,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A83,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A83,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A83,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A83,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G83" s="34">
+      <c r="G83" s="36">
         <f>F83+E83</f>
         <v/>
       </c>
@@ -10390,16 +11853,24 @@
         <f>IF(C83&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L83" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H83/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M83" s="27">
+        <f>IF(D83&lt;=0,0,I83/D83)</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="32" t="n">
+      <c r="A84" s="26" t="n">
         <v>38.33</v>
       </c>
-      <c r="B84" s="32">
+      <c r="B84" s="26">
         <f>A84-$B$12</f>
         <v/>
       </c>
-      <c r="C84" s="32">
+      <c r="C84" s="26">
         <f>MAX(0,A84-$B$6)</f>
         <v/>
       </c>
@@ -10407,15 +11878,15 @@
         <f>IF(C84&lt;=0,0,($B$7+$B$9*C84)*C84)</f>
         <v/>
       </c>
-      <c r="E84" s="26">
+      <c r="E84" s="29">
         <f>IF($B$13=1,D84*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F84" s="26">
+      <c r="F84" s="29">
         <f>IF(A84&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A84&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A84,SS_Amont!$A$11:$A$18,1))+(A84-INDEX(SS_Amont!$A$11:$A$18,MATCH(A84,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A84,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A84,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A84,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A84,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G84" s="34">
+      <c r="G84" s="36">
         <f>F84+E84</f>
         <v/>
       </c>
@@ -10435,16 +11906,24 @@
         <f>IF(C84&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L84" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H84/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M84" s="27">
+        <f>IF(D84&lt;=0,0,I84/D84)</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="32" t="n">
+      <c r="A85" s="26" t="n">
         <v>38.38</v>
       </c>
-      <c r="B85" s="32">
+      <c r="B85" s="26">
         <f>A85-$B$12</f>
         <v/>
       </c>
-      <c r="C85" s="32">
+      <c r="C85" s="26">
         <f>MAX(0,A85-$B$6)</f>
         <v/>
       </c>
@@ -10452,15 +11931,15 @@
         <f>IF(C85&lt;=0,0,($B$7+$B$9*C85)*C85)</f>
         <v/>
       </c>
-      <c r="E85" s="26">
+      <c r="E85" s="29">
         <f>IF($B$13=1,D85*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F85" s="26">
+      <c r="F85" s="29">
         <f>IF(A85&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A85&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A85,SS_Amont!$A$11:$A$18,1))+(A85-INDEX(SS_Amont!$A$11:$A$18,MATCH(A85,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A85,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A85,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A85,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A85,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G85" s="34">
+      <c r="G85" s="36">
         <f>F85+E85</f>
         <v/>
       </c>
@@ -10480,16 +11959,24 @@
         <f>IF(C85&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L85" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H85/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M85" s="27">
+        <f>IF(D85&lt;=0,0,I85/D85)</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="32" t="n">
+      <c r="A86" s="26" t="n">
         <v>38.43</v>
       </c>
-      <c r="B86" s="32">
+      <c r="B86" s="26">
         <f>A86-$B$12</f>
         <v/>
       </c>
-      <c r="C86" s="32">
+      <c r="C86" s="26">
         <f>MAX(0,A86-$B$6)</f>
         <v/>
       </c>
@@ -10497,15 +11984,15 @@
         <f>IF(C86&lt;=0,0,($B$7+$B$9*C86)*C86)</f>
         <v/>
       </c>
-      <c r="E86" s="26">
+      <c r="E86" s="29">
         <f>IF($B$13=1,D86*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F86" s="26">
+      <c r="F86" s="29">
         <f>IF(A86&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A86&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A86,SS_Amont!$A$11:$A$18,1))+(A86-INDEX(SS_Amont!$A$11:$A$18,MATCH(A86,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A86,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A86,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A86,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A86,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G86" s="34">
+      <c r="G86" s="36">
         <f>F86+E86</f>
         <v/>
       </c>
@@ -10525,16 +12012,24 @@
         <f>IF(C86&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L86" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H86/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M86" s="27">
+        <f>IF(D86&lt;=0,0,I86/D86)</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="32" t="n">
+      <c r="A87" s="26" t="n">
         <v>38.48</v>
       </c>
-      <c r="B87" s="32">
+      <c r="B87" s="26">
         <f>A87-$B$12</f>
         <v/>
       </c>
-      <c r="C87" s="32">
+      <c r="C87" s="26">
         <f>MAX(0,A87-$B$6)</f>
         <v/>
       </c>
@@ -10542,15 +12037,15 @@
         <f>IF(C87&lt;=0,0,($B$7+$B$9*C87)*C87)</f>
         <v/>
       </c>
-      <c r="E87" s="26">
+      <c r="E87" s="29">
         <f>IF($B$13=1,D87*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F87" s="26">
+      <c r="F87" s="29">
         <f>IF(A87&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A87&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A87,SS_Amont!$A$11:$A$18,1))+(A87-INDEX(SS_Amont!$A$11:$A$18,MATCH(A87,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A87,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A87,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A87,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A87,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G87" s="34">
+      <c r="G87" s="36">
         <f>F87+E87</f>
         <v/>
       </c>
@@ -10570,16 +12065,24 @@
         <f>IF(C87&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L87" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H87/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M87" s="27">
+        <f>IF(D87&lt;=0,0,I87/D87)</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="32" t="n">
+      <c r="A88" s="26" t="n">
         <v>38.53</v>
       </c>
-      <c r="B88" s="32">
+      <c r="B88" s="26">
         <f>A88-$B$12</f>
         <v/>
       </c>
-      <c r="C88" s="32">
+      <c r="C88" s="26">
         <f>MAX(0,A88-$B$6)</f>
         <v/>
       </c>
@@ -10587,15 +12090,15 @@
         <f>IF(C88&lt;=0,0,($B$7+$B$9*C88)*C88)</f>
         <v/>
       </c>
-      <c r="E88" s="26">
+      <c r="E88" s="29">
         <f>IF($B$13=1,D88*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F88" s="26">
+      <c r="F88" s="29">
         <f>IF(A88&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A88&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A88,SS_Amont!$A$11:$A$18,1))+(A88-INDEX(SS_Amont!$A$11:$A$18,MATCH(A88,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A88,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A88,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A88,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A88,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G88" s="34">
+      <c r="G88" s="36">
         <f>F88+E88</f>
         <v/>
       </c>
@@ -10615,16 +12118,24 @@
         <f>IF(C88&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L88" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H88/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M88" s="27">
+        <f>IF(D88&lt;=0,0,I88/D88)</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="32" t="n">
+      <c r="A89" s="26" t="n">
         <v>38.58</v>
       </c>
-      <c r="B89" s="32">
+      <c r="B89" s="26">
         <f>A89-$B$12</f>
         <v/>
       </c>
-      <c r="C89" s="32">
+      <c r="C89" s="26">
         <f>MAX(0,A89-$B$6)</f>
         <v/>
       </c>
@@ -10632,15 +12143,15 @@
         <f>IF(C89&lt;=0,0,($B$7+$B$9*C89)*C89)</f>
         <v/>
       </c>
-      <c r="E89" s="26">
+      <c r="E89" s="29">
         <f>IF($B$13=1,D89*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F89" s="26">
+      <c r="F89" s="29">
         <f>IF(A89&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A89&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A89,SS_Amont!$A$11:$A$18,1))+(A89-INDEX(SS_Amont!$A$11:$A$18,MATCH(A89,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A89,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A89,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A89,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A89,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G89" s="34">
+      <c r="G89" s="36">
         <f>F89+E89</f>
         <v/>
       </c>
@@ -10660,16 +12171,24 @@
         <f>IF(C89&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L89" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H89/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M89" s="27">
+        <f>IF(D89&lt;=0,0,I89/D89)</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="32" t="n">
+      <c r="A90" s="26" t="n">
         <v>38.63</v>
       </c>
-      <c r="B90" s="32">
+      <c r="B90" s="26">
         <f>A90-$B$12</f>
         <v/>
       </c>
-      <c r="C90" s="32">
+      <c r="C90" s="26">
         <f>MAX(0,A90-$B$6)</f>
         <v/>
       </c>
@@ -10677,15 +12196,15 @@
         <f>IF(C90&lt;=0,0,($B$7+$B$9*C90)*C90)</f>
         <v/>
       </c>
-      <c r="E90" s="26">
+      <c r="E90" s="29">
         <f>IF($B$13=1,D90*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F90" s="26">
+      <c r="F90" s="29">
         <f>IF(A90&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A90&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A90,SS_Amont!$A$11:$A$18,1))+(A90-INDEX(SS_Amont!$A$11:$A$18,MATCH(A90,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A90,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A90,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A90,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A90,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G90" s="34">
+      <c r="G90" s="36">
         <f>F90+E90</f>
         <v/>
       </c>
@@ -10705,16 +12224,24 @@
         <f>IF(C90&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L90" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H90/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M90" s="27">
+        <f>IF(D90&lt;=0,0,I90/D90)</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="32" t="n">
+      <c r="A91" s="26" t="n">
         <v>38.68</v>
       </c>
-      <c r="B91" s="32">
+      <c r="B91" s="26">
         <f>A91-$B$12</f>
         <v/>
       </c>
-      <c r="C91" s="32">
+      <c r="C91" s="26">
         <f>MAX(0,A91-$B$6)</f>
         <v/>
       </c>
@@ -10722,15 +12249,15 @@
         <f>IF(C91&lt;=0,0,($B$7+$B$9*C91)*C91)</f>
         <v/>
       </c>
-      <c r="E91" s="26">
+      <c r="E91" s="29">
         <f>IF($B$13=1,D91*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F91" s="26">
+      <c r="F91" s="29">
         <f>IF(A91&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A91&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A91,SS_Amont!$A$11:$A$18,1))+(A91-INDEX(SS_Amont!$A$11:$A$18,MATCH(A91,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A91,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A91,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A91,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A91,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G91" s="34">
+      <c r="G91" s="36">
         <f>F91+E91</f>
         <v/>
       </c>
@@ -10750,16 +12277,24 @@
         <f>IF(C91&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L91" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H91/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M91" s="27">
+        <f>IF(D91&lt;=0,0,I91/D91)</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="32" t="n">
+      <c r="A92" s="26" t="n">
         <v>38.73</v>
       </c>
-      <c r="B92" s="32">
+      <c r="B92" s="26">
         <f>A92-$B$12</f>
         <v/>
       </c>
-      <c r="C92" s="32">
+      <c r="C92" s="26">
         <f>MAX(0,A92-$B$6)</f>
         <v/>
       </c>
@@ -10767,15 +12302,15 @@
         <f>IF(C92&lt;=0,0,($B$7+$B$9*C92)*C92)</f>
         <v/>
       </c>
-      <c r="E92" s="26">
+      <c r="E92" s="29">
         <f>IF($B$13=1,D92*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F92" s="26">
+      <c r="F92" s="29">
         <f>IF(A92&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A92&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A92,SS_Amont!$A$11:$A$18,1))+(A92-INDEX(SS_Amont!$A$11:$A$18,MATCH(A92,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A92,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A92,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A92,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A92,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G92" s="34">
+      <c r="G92" s="36">
         <f>F92+E92</f>
         <v/>
       </c>
@@ -10795,16 +12330,24 @@
         <f>IF(C92&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L92" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H92/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M92" s="27">
+        <f>IF(D92&lt;=0,0,I92/D92)</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="32" t="n">
+      <c r="A93" s="26" t="n">
         <v>38.78</v>
       </c>
-      <c r="B93" s="32">
+      <c r="B93" s="26">
         <f>A93-$B$12</f>
         <v/>
       </c>
-      <c r="C93" s="32">
+      <c r="C93" s="26">
         <f>MAX(0,A93-$B$6)</f>
         <v/>
       </c>
@@ -10812,15 +12355,15 @@
         <f>IF(C93&lt;=0,0,($B$7+$B$9*C93)*C93)</f>
         <v/>
       </c>
-      <c r="E93" s="26">
+      <c r="E93" s="29">
         <f>IF($B$13=1,D93*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F93" s="26">
+      <c r="F93" s="29">
         <f>IF(A93&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A93&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A93,SS_Amont!$A$11:$A$18,1))+(A93-INDEX(SS_Amont!$A$11:$A$18,MATCH(A93,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A93,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A93,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A93,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A93,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G93" s="34">
+      <c r="G93" s="36">
         <f>F93+E93</f>
         <v/>
       </c>
@@ -10840,16 +12383,24 @@
         <f>IF(C93&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L93" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H93/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M93" s="27">
+        <f>IF(D93&lt;=0,0,I93/D93)</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="32" t="n">
+      <c r="A94" s="26" t="n">
         <v>38.83</v>
       </c>
-      <c r="B94" s="32">
+      <c r="B94" s="26">
         <f>A94-$B$12</f>
         <v/>
       </c>
-      <c r="C94" s="32">
+      <c r="C94" s="26">
         <f>MAX(0,A94-$B$6)</f>
         <v/>
       </c>
@@ -10857,15 +12408,15 @@
         <f>IF(C94&lt;=0,0,($B$7+$B$9*C94)*C94)</f>
         <v/>
       </c>
-      <c r="E94" s="26">
+      <c r="E94" s="29">
         <f>IF($B$13=1,D94*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F94" s="26">
+      <c r="F94" s="29">
         <f>IF(A94&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A94&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A94,SS_Amont!$A$11:$A$18,1))+(A94-INDEX(SS_Amont!$A$11:$A$18,MATCH(A94,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A94,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A94,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A94,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A94,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G94" s="34">
+      <c r="G94" s="36">
         <f>F94+E94</f>
         <v/>
       </c>
@@ -10885,16 +12436,24 @@
         <f>IF(C94&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L94" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H94/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M94" s="27">
+        <f>IF(D94&lt;=0,0,I94/D94)</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="32" t="n">
+      <c r="A95" s="26" t="n">
         <v>38.88</v>
       </c>
-      <c r="B95" s="32">
+      <c r="B95" s="26">
         <f>A95-$B$12</f>
         <v/>
       </c>
-      <c r="C95" s="32">
+      <c r="C95" s="26">
         <f>MAX(0,A95-$B$6)</f>
         <v/>
       </c>
@@ -10902,15 +12461,15 @@
         <f>IF(C95&lt;=0,0,($B$7+$B$9*C95)*C95)</f>
         <v/>
       </c>
-      <c r="E95" s="26">
+      <c r="E95" s="29">
         <f>IF($B$13=1,D95*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F95" s="26">
+      <c r="F95" s="29">
         <f>IF(A95&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A95&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A95,SS_Amont!$A$11:$A$18,1))+(A95-INDEX(SS_Amont!$A$11:$A$18,MATCH(A95,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A95,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A95,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A95,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A95,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G95" s="34">
+      <c r="G95" s="36">
         <f>F95+E95</f>
         <v/>
       </c>
@@ -10930,16 +12489,24 @@
         <f>IF(C95&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L95" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H95/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M95" s="27">
+        <f>IF(D95&lt;=0,0,I95/D95)</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="32" t="n">
+      <c r="A96" s="26" t="n">
         <v>38.93</v>
       </c>
-      <c r="B96" s="32">
+      <c r="B96" s="26">
         <f>A96-$B$12</f>
         <v/>
       </c>
-      <c r="C96" s="32">
+      <c r="C96" s="26">
         <f>MAX(0,A96-$B$6)</f>
         <v/>
       </c>
@@ -10947,15 +12514,15 @@
         <f>IF(C96&lt;=0,0,($B$7+$B$9*C96)*C96)</f>
         <v/>
       </c>
-      <c r="E96" s="26">
+      <c r="E96" s="29">
         <f>IF($B$13=1,D96*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F96" s="26">
+      <c r="F96" s="29">
         <f>IF(A96&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A96&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A96,SS_Amont!$A$11:$A$18,1))+(A96-INDEX(SS_Amont!$A$11:$A$18,MATCH(A96,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A96,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A96,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A96,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A96,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G96" s="34">
+      <c r="G96" s="36">
         <f>F96+E96</f>
         <v/>
       </c>
@@ -10975,16 +12542,24 @@
         <f>IF(C96&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L96" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H96/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M96" s="27">
+        <f>IF(D96&lt;=0,0,I96/D96)</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="32" t="n">
+      <c r="A97" s="26" t="n">
         <v>38.98</v>
       </c>
-      <c r="B97" s="32">
+      <c r="B97" s="26">
         <f>A97-$B$12</f>
         <v/>
       </c>
-      <c r="C97" s="32">
+      <c r="C97" s="26">
         <f>MAX(0,A97-$B$6)</f>
         <v/>
       </c>
@@ -10992,15 +12567,15 @@
         <f>IF(C97&lt;=0,0,($B$7+$B$9*C97)*C97)</f>
         <v/>
       </c>
-      <c r="E97" s="26">
+      <c r="E97" s="29">
         <f>IF($B$13=1,D97*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F97" s="26">
+      <c r="F97" s="29">
         <f>IF(A97&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A97&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A97,SS_Amont!$A$11:$A$18,1))+(A97-INDEX(SS_Amont!$A$11:$A$18,MATCH(A97,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A97,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A97,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A97,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A97,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G97" s="34">
+      <c r="G97" s="36">
         <f>F97+E97</f>
         <v/>
       </c>
@@ -11020,16 +12595,24 @@
         <f>IF(C97&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L97" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H97/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M97" s="27">
+        <f>IF(D97&lt;=0,0,I97/D97)</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="32" t="n">
+      <c r="A98" s="26" t="n">
         <v>39.03</v>
       </c>
-      <c r="B98" s="32">
+      <c r="B98" s="26">
         <f>A98-$B$12</f>
         <v/>
       </c>
-      <c r="C98" s="32">
+      <c r="C98" s="26">
         <f>MAX(0,A98-$B$6)</f>
         <v/>
       </c>
@@ -11037,15 +12620,15 @@
         <f>IF(C98&lt;=0,0,($B$7+$B$9*C98)*C98)</f>
         <v/>
       </c>
-      <c r="E98" s="26">
+      <c r="E98" s="29">
         <f>IF($B$13=1,D98*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F98" s="26">
+      <c r="F98" s="29">
         <f>IF(A98&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A98&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A98,SS_Amont!$A$11:$A$18,1))+(A98-INDEX(SS_Amont!$A$11:$A$18,MATCH(A98,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A98,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A98,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A98,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A98,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G98" s="34">
+      <c r="G98" s="36">
         <f>F98+E98</f>
         <v/>
       </c>
@@ -11065,16 +12648,24 @@
         <f>IF(C98&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L98" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H98/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M98" s="27">
+        <f>IF(D98&lt;=0,0,I98/D98)</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="32" t="n">
+      <c r="A99" s="26" t="n">
         <v>39.08</v>
       </c>
-      <c r="B99" s="32">
+      <c r="B99" s="26">
         <f>A99-$B$12</f>
         <v/>
       </c>
-      <c r="C99" s="32">
+      <c r="C99" s="26">
         <f>MAX(0,A99-$B$6)</f>
         <v/>
       </c>
@@ -11082,15 +12673,15 @@
         <f>IF(C99&lt;=0,0,($B$7+$B$9*C99)*C99)</f>
         <v/>
       </c>
-      <c r="E99" s="26">
+      <c r="E99" s="29">
         <f>IF($B$13=1,D99*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F99" s="26">
+      <c r="F99" s="29">
         <f>IF(A99&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A99&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A99,SS_Amont!$A$11:$A$18,1))+(A99-INDEX(SS_Amont!$A$11:$A$18,MATCH(A99,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A99,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A99,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A99,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A99,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G99" s="34">
+      <c r="G99" s="36">
         <f>F99+E99</f>
         <v/>
       </c>
@@ -11110,16 +12701,24 @@
         <f>IF(C99&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L99" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H99/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M99" s="27">
+        <f>IF(D99&lt;=0,0,I99/D99)</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="32" t="n">
+      <c r="A100" s="26" t="n">
         <v>39.13</v>
       </c>
-      <c r="B100" s="32">
+      <c r="B100" s="26">
         <f>A100-$B$12</f>
         <v/>
       </c>
-      <c r="C100" s="32">
+      <c r="C100" s="26">
         <f>MAX(0,A100-$B$6)</f>
         <v/>
       </c>
@@ -11127,15 +12726,15 @@
         <f>IF(C100&lt;=0,0,($B$7+$B$9*C100)*C100)</f>
         <v/>
       </c>
-      <c r="E100" s="26">
+      <c r="E100" s="29">
         <f>IF($B$13=1,D100*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F100" s="26">
+      <c r="F100" s="29">
         <f>IF(A100&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A100&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A100,SS_Amont!$A$11:$A$18,1))+(A100-INDEX(SS_Amont!$A$11:$A$18,MATCH(A100,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A100,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A100,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A100,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A100,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G100" s="34">
+      <c r="G100" s="36">
         <f>F100+E100</f>
         <v/>
       </c>
@@ -11155,16 +12754,24 @@
         <f>IF(C100&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L100" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H100/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M100" s="27">
+        <f>IF(D100&lt;=0,0,I100/D100)</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="32" t="n">
+      <c r="A101" s="26" t="n">
         <v>39.18</v>
       </c>
-      <c r="B101" s="32">
+      <c r="B101" s="26">
         <f>A101-$B$12</f>
         <v/>
       </c>
-      <c r="C101" s="32">
+      <c r="C101" s="26">
         <f>MAX(0,A101-$B$6)</f>
         <v/>
       </c>
@@ -11172,15 +12779,15 @@
         <f>IF(C101&lt;=0,0,($B$7+$B$9*C101)*C101)</f>
         <v/>
       </c>
-      <c r="E101" s="26">
+      <c r="E101" s="29">
         <f>IF($B$13=1,D101*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F101" s="26">
+      <c r="F101" s="29">
         <f>IF(A101&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A101&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A101,SS_Amont!$A$11:$A$18,1))+(A101-INDEX(SS_Amont!$A$11:$A$18,MATCH(A101,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A101,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A101,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A101,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A101,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G101" s="34">
+      <c r="G101" s="36">
         <f>F101+E101</f>
         <v/>
       </c>
@@ -11200,16 +12807,24 @@
         <f>IF(C101&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L101" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H101/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M101" s="27">
+        <f>IF(D101&lt;=0,0,I101/D101)</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="32" t="n">
+      <c r="A102" s="26" t="n">
         <v>39.23</v>
       </c>
-      <c r="B102" s="32">
+      <c r="B102" s="26">
         <f>A102-$B$12</f>
         <v/>
       </c>
-      <c r="C102" s="32">
+      <c r="C102" s="26">
         <f>MAX(0,A102-$B$6)</f>
         <v/>
       </c>
@@ -11217,15 +12832,15 @@
         <f>IF(C102&lt;=0,0,($B$7+$B$9*C102)*C102)</f>
         <v/>
       </c>
-      <c r="E102" s="26">
+      <c r="E102" s="29">
         <f>IF($B$13=1,D102*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F102" s="26">
+      <c r="F102" s="29">
         <f>IF(A102&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A102&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A102,SS_Amont!$A$11:$A$18,1))+(A102-INDEX(SS_Amont!$A$11:$A$18,MATCH(A102,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A102,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A102,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A102,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A102,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G102" s="34">
+      <c r="G102" s="36">
         <f>F102+E102</f>
         <v/>
       </c>
@@ -11245,16 +12860,24 @@
         <f>IF(C102&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L102" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H102/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M102" s="27">
+        <f>IF(D102&lt;=0,0,I102/D102)</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="32" t="n">
+      <c r="A103" s="26" t="n">
         <v>39.28</v>
       </c>
-      <c r="B103" s="32">
+      <c r="B103" s="26">
         <f>A103-$B$12</f>
         <v/>
       </c>
-      <c r="C103" s="32">
+      <c r="C103" s="26">
         <f>MAX(0,A103-$B$6)</f>
         <v/>
       </c>
@@ -11262,15 +12885,15 @@
         <f>IF(C103&lt;=0,0,($B$7+$B$9*C103)*C103)</f>
         <v/>
       </c>
-      <c r="E103" s="26">
+      <c r="E103" s="29">
         <f>IF($B$13=1,D103*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F103" s="26">
+      <c r="F103" s="29">
         <f>IF(A103&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A103&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A103,SS_Amont!$A$11:$A$18,1))+(A103-INDEX(SS_Amont!$A$11:$A$18,MATCH(A103,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A103,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A103,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A103,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A103,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G103" s="34">
+      <c r="G103" s="36">
         <f>F103+E103</f>
         <v/>
       </c>
@@ -11290,16 +12913,24 @@
         <f>IF(C103&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L103" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H103/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M103" s="27">
+        <f>IF(D103&lt;=0,0,I103/D103)</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="32" t="n">
+      <c r="A104" s="26" t="n">
         <v>39.33</v>
       </c>
-      <c r="B104" s="32">
+      <c r="B104" s="26">
         <f>A104-$B$12</f>
         <v/>
       </c>
-      <c r="C104" s="32">
+      <c r="C104" s="26">
         <f>MAX(0,A104-$B$6)</f>
         <v/>
       </c>
@@ -11307,15 +12938,15 @@
         <f>IF(C104&lt;=0,0,($B$7+$B$9*C104)*C104)</f>
         <v/>
       </c>
-      <c r="E104" s="26">
+      <c r="E104" s="29">
         <f>IF($B$13=1,D104*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F104" s="26">
+      <c r="F104" s="29">
         <f>IF(A104&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A104&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A104,SS_Amont!$A$11:$A$18,1))+(A104-INDEX(SS_Amont!$A$11:$A$18,MATCH(A104,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A104,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A104,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A104,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A104,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G104" s="34">
+      <c r="G104" s="36">
         <f>F104+E104</f>
         <v/>
       </c>
@@ -11335,16 +12966,24 @@
         <f>IF(C104&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L104" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H104/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M104" s="27">
+        <f>IF(D104&lt;=0,0,I104/D104)</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="32" t="n">
+      <c r="A105" s="26" t="n">
         <v>39.38</v>
       </c>
-      <c r="B105" s="32">
+      <c r="B105" s="26">
         <f>A105-$B$12</f>
         <v/>
       </c>
-      <c r="C105" s="32">
+      <c r="C105" s="26">
         <f>MAX(0,A105-$B$6)</f>
         <v/>
       </c>
@@ -11352,15 +12991,15 @@
         <f>IF(C105&lt;=0,0,($B$7+$B$9*C105)*C105)</f>
         <v/>
       </c>
-      <c r="E105" s="26">
+      <c r="E105" s="29">
         <f>IF($B$13=1,D105*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F105" s="26">
+      <c r="F105" s="29">
         <f>IF(A105&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A105&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A105,SS_Amont!$A$11:$A$18,1))+(A105-INDEX(SS_Amont!$A$11:$A$18,MATCH(A105,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A105,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A105,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A105,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A105,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G105" s="34">
+      <c r="G105" s="36">
         <f>F105+E105</f>
         <v/>
       </c>
@@ -11380,16 +13019,24 @@
         <f>IF(C105&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L105" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H105/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M105" s="27">
+        <f>IF(D105&lt;=0,0,I105/D105)</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="32" t="n">
+      <c r="A106" s="26" t="n">
         <v>39.43</v>
       </c>
-      <c r="B106" s="32">
+      <c r="B106" s="26">
         <f>A106-$B$12</f>
         <v/>
       </c>
-      <c r="C106" s="32">
+      <c r="C106" s="26">
         <f>MAX(0,A106-$B$6)</f>
         <v/>
       </c>
@@ -11397,15 +13044,15 @@
         <f>IF(C106&lt;=0,0,($B$7+$B$9*C106)*C106)</f>
         <v/>
       </c>
-      <c r="E106" s="26">
+      <c r="E106" s="29">
         <f>IF($B$13=1,D106*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F106" s="26">
+      <c r="F106" s="29">
         <f>IF(A106&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A106&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A106,SS_Amont!$A$11:$A$18,1))+(A106-INDEX(SS_Amont!$A$11:$A$18,MATCH(A106,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A106,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A106,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A106,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A106,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G106" s="34">
+      <c r="G106" s="36">
         <f>F106+E106</f>
         <v/>
       </c>
@@ -11425,16 +13072,24 @@
         <f>IF(C106&gt;0,"oui","non")</f>
         <v/>
       </c>
+      <c r="L106" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H106/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M106" s="27">
+        <f>IF(D106&lt;=0,0,I106/D106)</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="32" t="n">
+      <c r="A107" s="26" t="n">
         <v>39.48</v>
       </c>
-      <c r="B107" s="32">
+      <c r="B107" s="26">
         <f>A107-$B$12</f>
         <v/>
       </c>
-      <c r="C107" s="32">
+      <c r="C107" s="26">
         <f>MAX(0,A107-$B$6)</f>
         <v/>
       </c>
@@ -11442,15 +13097,15 @@
         <f>IF(C107&lt;=0,0,($B$7+$B$9*C107)*C107)</f>
         <v/>
       </c>
-      <c r="E107" s="26">
+      <c r="E107" s="29">
         <f>IF($B$13=1,D107*$B$11,0)</f>
         <v/>
       </c>
-      <c r="F107" s="26">
+      <c r="F107" s="29">
         <f>IF(A107&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A107&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A107,SS_Amont!$A$11:$A$18,1))+(A107-INDEX(SS_Amont!$A$11:$A$18,MATCH(A107,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A107,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A107,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A107,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A107,SS_Amont!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G107" s="34">
+      <c r="G107" s="36">
         <f>F107+E107</f>
         <v/>
       </c>
@@ -11468,6 +13123,14 @@
       </c>
       <c r="K107" s="4">
         <f>IF(C107&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="L107" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,H107/Parametres!$C$87)</f>
+        <v/>
+      </c>
+      <c r="M107" s="27">
+        <f>IF(D107&lt;=0,0,I107/D107)</f>
         <v/>
       </c>
     </row>
@@ -11496,6 +13159,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11506,7 +13170,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="40" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>À chaque pas: WSE lu sur Compose_900!V_total → Qout sur Compose_900. V_total = V_pond + V_ditch seulement si Parametres!B25=1; sinon V=levé SS_Amont. Q_overflow reste actif (b,z,L,n,S). ΔV = (Qin_moy − Qout)×Δt.</t>
         </is>
@@ -11519,7 +13183,7 @@
           <t>Q_plein réf. (m³/s)</t>
         </is>
       </c>
-      <c r="B5" s="41">
+      <c r="B5" s="42">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -11530,7 +13194,7 @@
           <t>Crest (m)</t>
         </is>
       </c>
-      <c r="B6" s="41">
+      <c r="B6" s="42">
         <f>Parametres!B27</f>
         <v/>
       </c>
@@ -11541,7 +13205,7 @@
           <t>Vmax_C (m³)</t>
         </is>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="34">
         <f>MAX(F12:F24)</f>
         <v/>
       </c>
@@ -11568,6 +13232,13 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>V_eq_Ø900 = Qout_total/A_plein Ø900 (indicatif; si overflow, une partie du débit n'est pas dans le tuyau)</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -11602,6 +13273,11 @@
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Overflow?</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>V_eq_Ø900 (m/s)</t>
         </is>
       </c>
     </row>
@@ -11622,16 +13298,20 @@
         <f>MIN(B12,$B$5)</f>
         <v/>
       </c>
-      <c r="E12" s="26" t="n">
+      <c r="E12" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="34" t="n">
+      <c r="F12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>non</t>
         </is>
+      </c>
+      <c r="H12" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,D12/Parametres!$C$87)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -11651,16 +13331,20 @@
         <f>IF(F12&lt;=0.01,MIN(0.5*(B12+B13),$B$5),IF(C13&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C13&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C13,Compose_900!$A$15:$A$107,1))+(C13-INDEX(Compose_900!$A$15:$A$107,MATCH(C13,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C13,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C13,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C13,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C13,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="29">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="36">
         <f>MAX(0,F12+(0.5*(B12+B13)-D13)*E13)</f>
         <v/>
       </c>
       <c r="G13" s="4">
         <f>IF(C13&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H13" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,D13/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -11681,16 +13365,20 @@
         <f>IF(F13&lt;=0.01,MIN(0.5*(B13+B14),$B$5),IF(C14&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C14&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C14,Compose_900!$A$15:$A$107,1))+(C14-INDEX(Compose_900!$A$15:$A$107,MATCH(C14,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C14,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C14,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C14,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C14,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="29">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="36">
         <f>MAX(0,F13+(0.5*(B13+B14)-D14)*E14)</f>
         <v/>
       </c>
       <c r="G14" s="4">
         <f>IF(C14&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H14" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,D14/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -11711,16 +13399,20 @@
         <f>IF(F14&lt;=0.01,MIN(0.5*(B14+B15),$B$5),IF(C15&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C15&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C15,Compose_900!$A$15:$A$107,1))+(C15-INDEX(Compose_900!$A$15:$A$107,MATCH(C15,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C15,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C15,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C15,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C15,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="29">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="36">
         <f>MAX(0,F14+(0.5*(B14+B15)-D15)*E15)</f>
         <v/>
       </c>
       <c r="G15" s="4">
         <f>IF(C15&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H15" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,D15/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -11741,16 +13433,20 @@
         <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$5),IF(C16&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C16&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C16,Compose_900!$A$15:$A$107,1))+(C16-INDEX(Compose_900!$A$15:$A$107,MATCH(C16,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C16,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C16,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C16,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C16,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="29">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="36">
         <f>MAX(0,F15+(0.5*(B15+B16)-D16)*E16)</f>
         <v/>
       </c>
       <c r="G16" s="4">
         <f>IF(C16&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H16" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,D16/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -11771,16 +13467,20 @@
         <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$5),IF(C17&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C17&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C17,Compose_900!$A$15:$A$107,1))+(C17-INDEX(Compose_900!$A$15:$A$107,MATCH(C17,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C17,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C17,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C17,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C17,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="29">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="36">
         <f>MAX(0,F16+(0.5*(B16+B17)-D17)*E17)</f>
         <v/>
       </c>
       <c r="G17" s="4">
         <f>IF(C17&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H17" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,D17/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -11801,16 +13501,20 @@
         <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$5),IF(C18&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C18&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C18,Compose_900!$A$15:$A$107,1))+(C18-INDEX(Compose_900!$A$15:$A$107,MATCH(C18,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C18,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C18,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C18,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C18,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="29">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="36">
         <f>MAX(0,F17+(0.5*(B17+B18)-D18)*E18)</f>
         <v/>
       </c>
       <c r="G18" s="4">
         <f>IF(C18&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H18" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,D18/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -11831,16 +13535,20 @@
         <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$5),IF(C19&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C19&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C19,Compose_900!$A$15:$A$107,1))+(C19-INDEX(Compose_900!$A$15:$A$107,MATCH(C19,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C19,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C19,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C19,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C19,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="29">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="36">
         <f>MAX(0,F18+(0.5*(B18+B19)-D19)*E19)</f>
         <v/>
       </c>
       <c r="G19" s="4">
         <f>IF(C19&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H19" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,D19/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -11861,16 +13569,20 @@
         <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$5),IF(C20&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C20&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C20,Compose_900!$A$15:$A$107,1))+(C20-INDEX(Compose_900!$A$15:$A$107,MATCH(C20,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C20,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C20,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C20,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C20,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="29">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="36">
         <f>MAX(0,F19+(0.5*(B19+B20)-D20)*E20)</f>
         <v/>
       </c>
       <c r="G20" s="4">
         <f>IF(C20&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H20" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,D20/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -11891,16 +13603,20 @@
         <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$5),IF(C21&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C21&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C21,Compose_900!$A$15:$A$107,1))+(C21-INDEX(Compose_900!$A$15:$A$107,MATCH(C21,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C21,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C21,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C21,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C21,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="29">
         <f>(A21-A20)*60</f>
         <v/>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="36">
         <f>MAX(0,F20+(0.5*(B20+B21)-D21)*E21)</f>
         <v/>
       </c>
       <c r="G21" s="4">
         <f>IF(C21&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H21" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,D21/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -11921,16 +13637,20 @@
         <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$5),IF(C22&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C22&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C22,Compose_900!$A$15:$A$107,1))+(C22-INDEX(Compose_900!$A$15:$A$107,MATCH(C22,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C22,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C22,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C22,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C22,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="29">
         <f>(A22-A21)*60</f>
         <v/>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="36">
         <f>MAX(0,F21+(0.5*(B21+B22)-D22)*E22)</f>
         <v/>
       </c>
       <c r="G22" s="4">
         <f>IF(C22&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H22" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,D22/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -11951,16 +13671,20 @@
         <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$5),IF(C23&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C23&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C23,Compose_900!$A$15:$A$107,1))+(C23-INDEX(Compose_900!$A$15:$A$107,MATCH(C23,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C23,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C23,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C23,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C23,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="29">
         <f>(A23-A22)*60</f>
         <v/>
       </c>
-      <c r="F23" s="34">
+      <c r="F23" s="36">
         <f>MAX(0,F22+(0.5*(B22+B23)-D23)*E23)</f>
         <v/>
       </c>
       <c r="G23" s="4">
         <f>IF(C23&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H23" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,D23/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -11981,16 +13705,20 @@
         <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$5),IF(C24&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C24&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C24,Compose_900!$A$15:$A$107,1))+(C24-INDEX(Compose_900!$A$15:$A$107,MATCH(C24,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C24,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C24,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C24,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C24,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="29">
         <f>(A24-A23)*60</f>
         <v/>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="36">
         <f>MAX(0,F23+(0.5*(B23+B24)-D24)*E24)</f>
         <v/>
       </c>
       <c r="G24" s="4">
         <f>IF(C24&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H24" s="27">
+        <f>IF(Parametres!$C$87&lt;=0,0,D24/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -12043,7 +13771,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>V_pas (m³) = (A_basse + A_haute) / 2 × (WSE_haute − WSE_basse)</t>
         </is>
@@ -12117,15 +13845,15 @@
       <c r="B12" s="17" t="n">
         <v>56</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="26">
         <f>A12-A11</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="29">
         <f>0.5*(B11+B12)*C12</f>
         <v/>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="36">
         <f>E11+D12</f>
         <v/>
       </c>
@@ -12142,15 +13870,15 @@
       <c r="B13" s="17" t="n">
         <v>210</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="26">
         <f>A13-A12</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="29">
         <f>0.5*(B12+B13)*C13</f>
         <v/>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="36">
         <f>E12+D13</f>
         <v/>
       </c>
@@ -12167,15 +13895,15 @@
       <c r="B14" s="17" t="n">
         <v>380</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="26">
         <f>A14-A13</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="29">
         <f>0.5*(B13+B14)*C14</f>
         <v/>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="36">
         <f>E13+D14</f>
         <v/>
       </c>
@@ -12192,15 +13920,15 @@
       <c r="B15" s="17" t="n">
         <v>400</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="26">
         <f>A15-A14</f>
         <v/>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="29">
         <f>0.5*(B14+B15)*C15</f>
         <v/>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="36">
         <f>E14+D15</f>
         <v/>
       </c>
@@ -12217,15 +13945,15 @@
       <c r="B16" s="17" t="n">
         <v>500</v>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="41">
         <f>A16-A15</f>
         <v/>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="43">
         <f>0.5*(B15+B16)*C16</f>
         <v/>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="43">
         <f>E15+D16</f>
         <v/>
       </c>
@@ -12242,15 +13970,15 @@
       <c r="B17" s="17" t="n">
         <v>860</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="26">
         <f>A17-A16</f>
         <v/>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="29">
         <f>0.5*(B16+B17)*C17</f>
         <v/>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="36">
         <f>E16+D17</f>
         <v/>
       </c>
@@ -12267,15 +13995,15 @@
       <c r="B18" s="17" t="n">
         <v>2100</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="26">
         <f>A18-A17</f>
         <v/>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="29">
         <f>0.5*(B17+B18)*C18</f>
         <v/>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="36">
         <f>E17+D18</f>
         <v/>
       </c>
@@ -12291,7 +14019,7 @@
           <t>V @ 37.28 m (m³)</t>
         </is>
       </c>
-      <c r="B21" s="44">
+      <c r="B21" s="45">
         <f>E16</f>
         <v/>
       </c>
@@ -12307,7 +14035,7 @@
           <t>V @ sommet table (m³)</t>
         </is>
       </c>
-      <c r="B22" s="44">
+      <c r="B22" s="45">
         <f>E18</f>
         <v/>
       </c>
@@ -12413,7 +14141,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>V_pas (m³) = (A_basse + A_haute) / 2 × (WSE_haute − WSE_basse)</t>
         </is>
@@ -12487,15 +14215,15 @@
       <c r="B12" s="17" t="n">
         <v>60</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="26">
         <f>A12-A11</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="29">
         <f>0.5*(B11+B12)*C12</f>
         <v/>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="36">
         <f>E11+D12</f>
         <v/>
       </c>
@@ -12512,15 +14240,15 @@
       <c r="B13" s="17" t="n">
         <v>219</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="26">
         <f>A13-A12</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="29">
         <f>0.5*(B12+B13)*C13</f>
         <v/>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="36">
         <f>E12+D13</f>
         <v/>
       </c>
@@ -12537,15 +14265,15 @@
       <c r="B14" s="17" t="n">
         <v>150</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="26">
         <f>A14-A13</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="29">
         <f>0.5*(B13+B14)*C14</f>
         <v/>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="36">
         <f>E13+D14</f>
         <v/>
       </c>
@@ -12562,15 +14290,15 @@
       <c r="B15" s="17" t="n">
         <v>340</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="26">
         <f>A15-A14</f>
         <v/>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="29">
         <f>0.5*(B14+B15)*C15</f>
         <v/>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="36">
         <f>E14+D15</f>
         <v/>
       </c>
@@ -12587,15 +14315,15 @@
       <c r="B16" s="17" t="n">
         <v>1700</v>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="41">
         <f>A16-A15</f>
         <v/>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="43">
         <f>0.5*(B15+B16)*C16</f>
         <v/>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="43">
         <f>E15+D16</f>
         <v/>
       </c>
@@ -12612,15 +14340,15 @@
       <c r="B17" s="17" t="n">
         <v>1460</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="26">
         <f>A17-A16</f>
         <v/>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="29">
         <f>0.5*(B16+B17)*C17</f>
         <v/>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="36">
         <f>E16+D17</f>
         <v/>
       </c>
@@ -12637,15 +14365,15 @@
       <c r="B18" s="17" t="n">
         <v>1632</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="26">
         <f>A18-A17</f>
         <v/>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="29">
         <f>0.5*(B17+B18)*C18</f>
         <v/>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="36">
         <f>E17+D18</f>
         <v/>
       </c>
@@ -12661,7 +14389,7 @@
           <t>V @ 37.28 m (m³)</t>
         </is>
       </c>
-      <c r="B21" s="44">
+      <c r="B21" s="45">
         <f>E16</f>
         <v/>
       </c>
@@ -12677,7 +14405,7 @@
           <t>V @ sommet table (m³)</t>
         </is>
       </c>
-      <c r="B22" s="44">
+      <c r="B22" s="45">
         <f>E18</f>
         <v/>
       </c>

--- a/engineering/drainage-design/retention_volume/Volume_Retention_Deux_Zones_1500_900_1200.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Deux_Zones_1500_900_1200.xlsx
@@ -1704,7 +1704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2734,11 +2734,20 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="25" t="inlineStr">
+        <is>
+          <t>ATTENTION: des V &gt;&gt; 5–6 m/s ne sont PAS physiques. Souvent Q_overflow+Q_pipe divisé par A_tuyau, ou Q/A_fossé trop petit. Vitesses tuyau réalistes typ. ~1–4 m/s; lire Compose_900 (V_Ø900) et Courbe_QH_900.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92"/>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="A67:H67"/>
     <mergeCell ref="A77:H77"/>
     <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A91:H92"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A79:H79"/>
     <mergeCell ref="A61:H61"/>
@@ -8254,7 +8263,7 @@
         <v/>
       </c>
       <c r="M15" s="27">
-        <f>IF(D15&lt;=0,0,I15/D15)</f>
+        <f>IF(OR(C15&lt;0.05,D15&lt;0.05),"",I15/D15)</f>
         <v/>
       </c>
     </row>
@@ -8307,7 +8316,7 @@
         <v/>
       </c>
       <c r="M16" s="27">
-        <f>IF(D16&lt;=0,0,I16/D16)</f>
+        <f>IF(OR(C16&lt;0.05,D16&lt;0.05),"",I16/D16)</f>
         <v/>
       </c>
     </row>
@@ -8360,7 +8369,7 @@
         <v/>
       </c>
       <c r="M17" s="27">
-        <f>IF(D17&lt;=0,0,I17/D17)</f>
+        <f>IF(OR(C17&lt;0.05,D17&lt;0.05),"",I17/D17)</f>
         <v/>
       </c>
     </row>
@@ -8413,7 +8422,7 @@
         <v/>
       </c>
       <c r="M18" s="27">
-        <f>IF(D18&lt;=0,0,I18/D18)</f>
+        <f>IF(OR(C18&lt;0.05,D18&lt;0.05),"",I18/D18)</f>
         <v/>
       </c>
     </row>
@@ -8466,7 +8475,7 @@
         <v/>
       </c>
       <c r="M19" s="27">
-        <f>IF(D19&lt;=0,0,I19/D19)</f>
+        <f>IF(OR(C19&lt;0.05,D19&lt;0.05),"",I19/D19)</f>
         <v/>
       </c>
     </row>
@@ -8519,7 +8528,7 @@
         <v/>
       </c>
       <c r="M20" s="27">
-        <f>IF(D20&lt;=0,0,I20/D20)</f>
+        <f>IF(OR(C20&lt;0.05,D20&lt;0.05),"",I20/D20)</f>
         <v/>
       </c>
     </row>
@@ -8572,7 +8581,7 @@
         <v/>
       </c>
       <c r="M21" s="27">
-        <f>IF(D21&lt;=0,0,I21/D21)</f>
+        <f>IF(OR(C21&lt;0.05,D21&lt;0.05),"",I21/D21)</f>
         <v/>
       </c>
     </row>
@@ -8625,7 +8634,7 @@
         <v/>
       </c>
       <c r="M22" s="27">
-        <f>IF(D22&lt;=0,0,I22/D22)</f>
+        <f>IF(OR(C22&lt;0.05,D22&lt;0.05),"",I22/D22)</f>
         <v/>
       </c>
     </row>
@@ -8678,7 +8687,7 @@
         <v/>
       </c>
       <c r="M23" s="27">
-        <f>IF(D23&lt;=0,0,I23/D23)</f>
+        <f>IF(OR(C23&lt;0.05,D23&lt;0.05),"",I23/D23)</f>
         <v/>
       </c>
     </row>
@@ -8731,7 +8740,7 @@
         <v/>
       </c>
       <c r="M24" s="27">
-        <f>IF(D24&lt;=0,0,I24/D24)</f>
+        <f>IF(OR(C24&lt;0.05,D24&lt;0.05),"",I24/D24)</f>
         <v/>
       </c>
     </row>
@@ -8784,7 +8793,7 @@
         <v/>
       </c>
       <c r="M25" s="27">
-        <f>IF(D25&lt;=0,0,I25/D25)</f>
+        <f>IF(OR(C25&lt;0.05,D25&lt;0.05),"",I25/D25)</f>
         <v/>
       </c>
     </row>
@@ -8837,7 +8846,7 @@
         <v/>
       </c>
       <c r="M26" s="27">
-        <f>IF(D26&lt;=0,0,I26/D26)</f>
+        <f>IF(OR(C26&lt;0.05,D26&lt;0.05),"",I26/D26)</f>
         <v/>
       </c>
     </row>
@@ -8890,7 +8899,7 @@
         <v/>
       </c>
       <c r="M27" s="27">
-        <f>IF(D27&lt;=0,0,I27/D27)</f>
+        <f>IF(OR(C27&lt;0.05,D27&lt;0.05),"",I27/D27)</f>
         <v/>
       </c>
     </row>
@@ -8943,7 +8952,7 @@
         <v/>
       </c>
       <c r="M28" s="27">
-        <f>IF(D28&lt;=0,0,I28/D28)</f>
+        <f>IF(OR(C28&lt;0.05,D28&lt;0.05),"",I28/D28)</f>
         <v/>
       </c>
     </row>
@@ -8996,7 +9005,7 @@
         <v/>
       </c>
       <c r="M29" s="27">
-        <f>IF(D29&lt;=0,0,I29/D29)</f>
+        <f>IF(OR(C29&lt;0.05,D29&lt;0.05),"",I29/D29)</f>
         <v/>
       </c>
     </row>
@@ -9049,7 +9058,7 @@
         <v/>
       </c>
       <c r="M30" s="27">
-        <f>IF(D30&lt;=0,0,I30/D30)</f>
+        <f>IF(OR(C30&lt;0.05,D30&lt;0.05),"",I30/D30)</f>
         <v/>
       </c>
     </row>
@@ -9102,7 +9111,7 @@
         <v/>
       </c>
       <c r="M31" s="27">
-        <f>IF(D31&lt;=0,0,I31/D31)</f>
+        <f>IF(OR(C31&lt;0.05,D31&lt;0.05),"",I31/D31)</f>
         <v/>
       </c>
     </row>
@@ -9155,7 +9164,7 @@
         <v/>
       </c>
       <c r="M32" s="27">
-        <f>IF(D32&lt;=0,0,I32/D32)</f>
+        <f>IF(OR(C32&lt;0.05,D32&lt;0.05),"",I32/D32)</f>
         <v/>
       </c>
     </row>
@@ -9208,7 +9217,7 @@
         <v/>
       </c>
       <c r="M33" s="27">
-        <f>IF(D33&lt;=0,0,I33/D33)</f>
+        <f>IF(OR(C33&lt;0.05,D33&lt;0.05),"",I33/D33)</f>
         <v/>
       </c>
     </row>
@@ -9261,7 +9270,7 @@
         <v/>
       </c>
       <c r="M34" s="27">
-        <f>IF(D34&lt;=0,0,I34/D34)</f>
+        <f>IF(OR(C34&lt;0.05,D34&lt;0.05),"",I34/D34)</f>
         <v/>
       </c>
     </row>
@@ -9314,7 +9323,7 @@
         <v/>
       </c>
       <c r="M35" s="27">
-        <f>IF(D35&lt;=0,0,I35/D35)</f>
+        <f>IF(OR(C35&lt;0.05,D35&lt;0.05),"",I35/D35)</f>
         <v/>
       </c>
     </row>
@@ -9367,7 +9376,7 @@
         <v/>
       </c>
       <c r="M36" s="27">
-        <f>IF(D36&lt;=0,0,I36/D36)</f>
+        <f>IF(OR(C36&lt;0.05,D36&lt;0.05),"",I36/D36)</f>
         <v/>
       </c>
     </row>
@@ -9420,7 +9429,7 @@
         <v/>
       </c>
       <c r="M37" s="27">
-        <f>IF(D37&lt;=0,0,I37/D37)</f>
+        <f>IF(OR(C37&lt;0.05,D37&lt;0.05),"",I37/D37)</f>
         <v/>
       </c>
     </row>
@@ -9473,7 +9482,7 @@
         <v/>
       </c>
       <c r="M38" s="27">
-        <f>IF(D38&lt;=0,0,I38/D38)</f>
+        <f>IF(OR(C38&lt;0.05,D38&lt;0.05),"",I38/D38)</f>
         <v/>
       </c>
     </row>
@@ -9526,7 +9535,7 @@
         <v/>
       </c>
       <c r="M39" s="27">
-        <f>IF(D39&lt;=0,0,I39/D39)</f>
+        <f>IF(OR(C39&lt;0.05,D39&lt;0.05),"",I39/D39)</f>
         <v/>
       </c>
     </row>
@@ -9579,7 +9588,7 @@
         <v/>
       </c>
       <c r="M40" s="27">
-        <f>IF(D40&lt;=0,0,I40/D40)</f>
+        <f>IF(OR(C40&lt;0.05,D40&lt;0.05),"",I40/D40)</f>
         <v/>
       </c>
     </row>
@@ -9632,7 +9641,7 @@
         <v/>
       </c>
       <c r="M41" s="27">
-        <f>IF(D41&lt;=0,0,I41/D41)</f>
+        <f>IF(OR(C41&lt;0.05,D41&lt;0.05),"",I41/D41)</f>
         <v/>
       </c>
     </row>
@@ -9685,7 +9694,7 @@
         <v/>
       </c>
       <c r="M42" s="27">
-        <f>IF(D42&lt;=0,0,I42/D42)</f>
+        <f>IF(OR(C42&lt;0.05,D42&lt;0.05),"",I42/D42)</f>
         <v/>
       </c>
     </row>
@@ -9738,7 +9747,7 @@
         <v/>
       </c>
       <c r="M43" s="27">
-        <f>IF(D43&lt;=0,0,I43/D43)</f>
+        <f>IF(OR(C43&lt;0.05,D43&lt;0.05),"",I43/D43)</f>
         <v/>
       </c>
     </row>
@@ -9791,7 +9800,7 @@
         <v/>
       </c>
       <c r="M44" s="27">
-        <f>IF(D44&lt;=0,0,I44/D44)</f>
+        <f>IF(OR(C44&lt;0.05,D44&lt;0.05),"",I44/D44)</f>
         <v/>
       </c>
     </row>
@@ -9844,7 +9853,7 @@
         <v/>
       </c>
       <c r="M45" s="27">
-        <f>IF(D45&lt;=0,0,I45/D45)</f>
+        <f>IF(OR(C45&lt;0.05,D45&lt;0.05),"",I45/D45)</f>
         <v/>
       </c>
     </row>
@@ -9897,7 +9906,7 @@
         <v/>
       </c>
       <c r="M46" s="27">
-        <f>IF(D46&lt;=0,0,I46/D46)</f>
+        <f>IF(OR(C46&lt;0.05,D46&lt;0.05),"",I46/D46)</f>
         <v/>
       </c>
     </row>
@@ -9950,7 +9959,7 @@
         <v/>
       </c>
       <c r="M47" s="27">
-        <f>IF(D47&lt;=0,0,I47/D47)</f>
+        <f>IF(OR(C47&lt;0.05,D47&lt;0.05),"",I47/D47)</f>
         <v/>
       </c>
     </row>
@@ -10003,7 +10012,7 @@
         <v/>
       </c>
       <c r="M48" s="27">
-        <f>IF(D48&lt;=0,0,I48/D48)</f>
+        <f>IF(OR(C48&lt;0.05,D48&lt;0.05),"",I48/D48)</f>
         <v/>
       </c>
     </row>
@@ -10056,7 +10065,7 @@
         <v/>
       </c>
       <c r="M49" s="27">
-        <f>IF(D49&lt;=0,0,I49/D49)</f>
+        <f>IF(OR(C49&lt;0.05,D49&lt;0.05),"",I49/D49)</f>
         <v/>
       </c>
     </row>
@@ -10109,7 +10118,7 @@
         <v/>
       </c>
       <c r="M50" s="27">
-        <f>IF(D50&lt;=0,0,I50/D50)</f>
+        <f>IF(OR(C50&lt;0.05,D50&lt;0.05),"",I50/D50)</f>
         <v/>
       </c>
     </row>
@@ -10162,7 +10171,7 @@
         <v/>
       </c>
       <c r="M51" s="27">
-        <f>IF(D51&lt;=0,0,I51/D51)</f>
+        <f>IF(OR(C51&lt;0.05,D51&lt;0.05),"",I51/D51)</f>
         <v/>
       </c>
     </row>
@@ -10215,7 +10224,7 @@
         <v/>
       </c>
       <c r="M52" s="27">
-        <f>IF(D52&lt;=0,0,I52/D52)</f>
+        <f>IF(OR(C52&lt;0.05,D52&lt;0.05),"",I52/D52)</f>
         <v/>
       </c>
     </row>
@@ -10268,7 +10277,7 @@
         <v/>
       </c>
       <c r="M53" s="27">
-        <f>IF(D53&lt;=0,0,I53/D53)</f>
+        <f>IF(OR(C53&lt;0.05,D53&lt;0.05),"",I53/D53)</f>
         <v/>
       </c>
     </row>
@@ -10321,7 +10330,7 @@
         <v/>
       </c>
       <c r="M54" s="27">
-        <f>IF(D54&lt;=0,0,I54/D54)</f>
+        <f>IF(OR(C54&lt;0.05,D54&lt;0.05),"",I54/D54)</f>
         <v/>
       </c>
     </row>
@@ -10374,7 +10383,7 @@
         <v/>
       </c>
       <c r="M55" s="27">
-        <f>IF(D55&lt;=0,0,I55/D55)</f>
+        <f>IF(OR(C55&lt;0.05,D55&lt;0.05),"",I55/D55)</f>
         <v/>
       </c>
     </row>
@@ -10427,7 +10436,7 @@
         <v/>
       </c>
       <c r="M56" s="27">
-        <f>IF(D56&lt;=0,0,I56/D56)</f>
+        <f>IF(OR(C56&lt;0.05,D56&lt;0.05),"",I56/D56)</f>
         <v/>
       </c>
     </row>
@@ -10480,7 +10489,7 @@
         <v/>
       </c>
       <c r="M57" s="27">
-        <f>IF(D57&lt;=0,0,I57/D57)</f>
+        <f>IF(OR(C57&lt;0.05,D57&lt;0.05),"",I57/D57)</f>
         <v/>
       </c>
     </row>
@@ -10533,7 +10542,7 @@
         <v/>
       </c>
       <c r="M58" s="27">
-        <f>IF(D58&lt;=0,0,I58/D58)</f>
+        <f>IF(OR(C58&lt;0.05,D58&lt;0.05),"",I58/D58)</f>
         <v/>
       </c>
     </row>
@@ -10586,7 +10595,7 @@
         <v/>
       </c>
       <c r="M59" s="27">
-        <f>IF(D59&lt;=0,0,I59/D59)</f>
+        <f>IF(OR(C59&lt;0.05,D59&lt;0.05),"",I59/D59)</f>
         <v/>
       </c>
     </row>
@@ -10639,7 +10648,7 @@
         <v/>
       </c>
       <c r="M60" s="27">
-        <f>IF(D60&lt;=0,0,I60/D60)</f>
+        <f>IF(OR(C60&lt;0.05,D60&lt;0.05),"",I60/D60)</f>
         <v/>
       </c>
     </row>
@@ -10692,7 +10701,7 @@
         <v/>
       </c>
       <c r="M61" s="27">
-        <f>IF(D61&lt;=0,0,I61/D61)</f>
+        <f>IF(OR(C61&lt;0.05,D61&lt;0.05),"",I61/D61)</f>
         <v/>
       </c>
     </row>
@@ -10745,7 +10754,7 @@
         <v/>
       </c>
       <c r="M62" s="27">
-        <f>IF(D62&lt;=0,0,I62/D62)</f>
+        <f>IF(OR(C62&lt;0.05,D62&lt;0.05),"",I62/D62)</f>
         <v/>
       </c>
     </row>
@@ -10798,7 +10807,7 @@
         <v/>
       </c>
       <c r="M63" s="27">
-        <f>IF(D63&lt;=0,0,I63/D63)</f>
+        <f>IF(OR(C63&lt;0.05,D63&lt;0.05),"",I63/D63)</f>
         <v/>
       </c>
     </row>
@@ -10851,7 +10860,7 @@
         <v/>
       </c>
       <c r="M64" s="27">
-        <f>IF(D64&lt;=0,0,I64/D64)</f>
+        <f>IF(OR(C64&lt;0.05,D64&lt;0.05),"",I64/D64)</f>
         <v/>
       </c>
     </row>
@@ -10904,7 +10913,7 @@
         <v/>
       </c>
       <c r="M65" s="27">
-        <f>IF(D65&lt;=0,0,I65/D65)</f>
+        <f>IF(OR(C65&lt;0.05,D65&lt;0.05),"",I65/D65)</f>
         <v/>
       </c>
     </row>
@@ -10957,7 +10966,7 @@
         <v/>
       </c>
       <c r="M66" s="27">
-        <f>IF(D66&lt;=0,0,I66/D66)</f>
+        <f>IF(OR(C66&lt;0.05,D66&lt;0.05),"",I66/D66)</f>
         <v/>
       </c>
     </row>
@@ -11010,7 +11019,7 @@
         <v/>
       </c>
       <c r="M67" s="27">
-        <f>IF(D67&lt;=0,0,I67/D67)</f>
+        <f>IF(OR(C67&lt;0.05,D67&lt;0.05),"",I67/D67)</f>
         <v/>
       </c>
     </row>
@@ -11063,7 +11072,7 @@
         <v/>
       </c>
       <c r="M68" s="27">
-        <f>IF(D68&lt;=0,0,I68/D68)</f>
+        <f>IF(OR(C68&lt;0.05,D68&lt;0.05),"",I68/D68)</f>
         <v/>
       </c>
     </row>
@@ -11116,7 +11125,7 @@
         <v/>
       </c>
       <c r="M69" s="27">
-        <f>IF(D69&lt;=0,0,I69/D69)</f>
+        <f>IF(OR(C69&lt;0.05,D69&lt;0.05),"",I69/D69)</f>
         <v/>
       </c>
     </row>
@@ -11169,7 +11178,7 @@
         <v/>
       </c>
       <c r="M70" s="27">
-        <f>IF(D70&lt;=0,0,I70/D70)</f>
+        <f>IF(OR(C70&lt;0.05,D70&lt;0.05),"",I70/D70)</f>
         <v/>
       </c>
     </row>
@@ -11222,7 +11231,7 @@
         <v/>
       </c>
       <c r="M71" s="27">
-        <f>IF(D71&lt;=0,0,I71/D71)</f>
+        <f>IF(OR(C71&lt;0.05,D71&lt;0.05),"",I71/D71)</f>
         <v/>
       </c>
     </row>
@@ -11275,7 +11284,7 @@
         <v/>
       </c>
       <c r="M72" s="27">
-        <f>IF(D72&lt;=0,0,I72/D72)</f>
+        <f>IF(OR(C72&lt;0.05,D72&lt;0.05),"",I72/D72)</f>
         <v/>
       </c>
     </row>
@@ -11328,7 +11337,7 @@
         <v/>
       </c>
       <c r="M73" s="27">
-        <f>IF(D73&lt;=0,0,I73/D73)</f>
+        <f>IF(OR(C73&lt;0.05,D73&lt;0.05),"",I73/D73)</f>
         <v/>
       </c>
     </row>
@@ -11381,7 +11390,7 @@
         <v/>
       </c>
       <c r="M74" s="27">
-        <f>IF(D74&lt;=0,0,I74/D74)</f>
+        <f>IF(OR(C74&lt;0.05,D74&lt;0.05),"",I74/D74)</f>
         <v/>
       </c>
     </row>
@@ -11434,7 +11443,7 @@
         <v/>
       </c>
       <c r="M75" s="27">
-        <f>IF(D75&lt;=0,0,I75/D75)</f>
+        <f>IF(OR(C75&lt;0.05,D75&lt;0.05),"",I75/D75)</f>
         <v/>
       </c>
     </row>
@@ -11487,7 +11496,7 @@
         <v/>
       </c>
       <c r="M76" s="27">
-        <f>IF(D76&lt;=0,0,I76/D76)</f>
+        <f>IF(OR(C76&lt;0.05,D76&lt;0.05),"",I76/D76)</f>
         <v/>
       </c>
     </row>
@@ -11540,7 +11549,7 @@
         <v/>
       </c>
       <c r="M77" s="27">
-        <f>IF(D77&lt;=0,0,I77/D77)</f>
+        <f>IF(OR(C77&lt;0.05,D77&lt;0.05),"",I77/D77)</f>
         <v/>
       </c>
     </row>
@@ -11593,7 +11602,7 @@
         <v/>
       </c>
       <c r="M78" s="27">
-        <f>IF(D78&lt;=0,0,I78/D78)</f>
+        <f>IF(OR(C78&lt;0.05,D78&lt;0.05),"",I78/D78)</f>
         <v/>
       </c>
     </row>
@@ -11646,7 +11655,7 @@
         <v/>
       </c>
       <c r="M79" s="27">
-        <f>IF(D79&lt;=0,0,I79/D79)</f>
+        <f>IF(OR(C79&lt;0.05,D79&lt;0.05),"",I79/D79)</f>
         <v/>
       </c>
     </row>
@@ -11699,7 +11708,7 @@
         <v/>
       </c>
       <c r="M80" s="27">
-        <f>IF(D80&lt;=0,0,I80/D80)</f>
+        <f>IF(OR(C80&lt;0.05,D80&lt;0.05),"",I80/D80)</f>
         <v/>
       </c>
     </row>
@@ -11752,7 +11761,7 @@
         <v/>
       </c>
       <c r="M81" s="27">
-        <f>IF(D81&lt;=0,0,I81/D81)</f>
+        <f>IF(OR(C81&lt;0.05,D81&lt;0.05),"",I81/D81)</f>
         <v/>
       </c>
     </row>
@@ -11805,7 +11814,7 @@
         <v/>
       </c>
       <c r="M82" s="27">
-        <f>IF(D82&lt;=0,0,I82/D82)</f>
+        <f>IF(OR(C82&lt;0.05,D82&lt;0.05),"",I82/D82)</f>
         <v/>
       </c>
     </row>
@@ -11858,7 +11867,7 @@
         <v/>
       </c>
       <c r="M83" s="27">
-        <f>IF(D83&lt;=0,0,I83/D83)</f>
+        <f>IF(OR(C83&lt;0.05,D83&lt;0.05),"",I83/D83)</f>
         <v/>
       </c>
     </row>
@@ -11911,7 +11920,7 @@
         <v/>
       </c>
       <c r="M84" s="27">
-        <f>IF(D84&lt;=0,0,I84/D84)</f>
+        <f>IF(OR(C84&lt;0.05,D84&lt;0.05),"",I84/D84)</f>
         <v/>
       </c>
     </row>
@@ -11964,7 +11973,7 @@
         <v/>
       </c>
       <c r="M85" s="27">
-        <f>IF(D85&lt;=0,0,I85/D85)</f>
+        <f>IF(OR(C85&lt;0.05,D85&lt;0.05),"",I85/D85)</f>
         <v/>
       </c>
     </row>
@@ -12017,7 +12026,7 @@
         <v/>
       </c>
       <c r="M86" s="27">
-        <f>IF(D86&lt;=0,0,I86/D86)</f>
+        <f>IF(OR(C86&lt;0.05,D86&lt;0.05),"",I86/D86)</f>
         <v/>
       </c>
     </row>
@@ -12070,7 +12079,7 @@
         <v/>
       </c>
       <c r="M87" s="27">
-        <f>IF(D87&lt;=0,0,I87/D87)</f>
+        <f>IF(OR(C87&lt;0.05,D87&lt;0.05),"",I87/D87)</f>
         <v/>
       </c>
     </row>
@@ -12123,7 +12132,7 @@
         <v/>
       </c>
       <c r="M88" s="27">
-        <f>IF(D88&lt;=0,0,I88/D88)</f>
+        <f>IF(OR(C88&lt;0.05,D88&lt;0.05),"",I88/D88)</f>
         <v/>
       </c>
     </row>
@@ -12176,7 +12185,7 @@
         <v/>
       </c>
       <c r="M89" s="27">
-        <f>IF(D89&lt;=0,0,I89/D89)</f>
+        <f>IF(OR(C89&lt;0.05,D89&lt;0.05),"",I89/D89)</f>
         <v/>
       </c>
     </row>
@@ -12229,7 +12238,7 @@
         <v/>
       </c>
       <c r="M90" s="27">
-        <f>IF(D90&lt;=0,0,I90/D90)</f>
+        <f>IF(OR(C90&lt;0.05,D90&lt;0.05),"",I90/D90)</f>
         <v/>
       </c>
     </row>
@@ -12282,7 +12291,7 @@
         <v/>
       </c>
       <c r="M91" s="27">
-        <f>IF(D91&lt;=0,0,I91/D91)</f>
+        <f>IF(OR(C91&lt;0.05,D91&lt;0.05),"",I91/D91)</f>
         <v/>
       </c>
     </row>
@@ -12335,7 +12344,7 @@
         <v/>
       </c>
       <c r="M92" s="27">
-        <f>IF(D92&lt;=0,0,I92/D92)</f>
+        <f>IF(OR(C92&lt;0.05,D92&lt;0.05),"",I92/D92)</f>
         <v/>
       </c>
     </row>
@@ -12388,7 +12397,7 @@
         <v/>
       </c>
       <c r="M93" s="27">
-        <f>IF(D93&lt;=0,0,I93/D93)</f>
+        <f>IF(OR(C93&lt;0.05,D93&lt;0.05),"",I93/D93)</f>
         <v/>
       </c>
     </row>
@@ -12441,7 +12450,7 @@
         <v/>
       </c>
       <c r="M94" s="27">
-        <f>IF(D94&lt;=0,0,I94/D94)</f>
+        <f>IF(OR(C94&lt;0.05,D94&lt;0.05),"",I94/D94)</f>
         <v/>
       </c>
     </row>
@@ -12494,7 +12503,7 @@
         <v/>
       </c>
       <c r="M95" s="27">
-        <f>IF(D95&lt;=0,0,I95/D95)</f>
+        <f>IF(OR(C95&lt;0.05,D95&lt;0.05),"",I95/D95)</f>
         <v/>
       </c>
     </row>
@@ -12547,7 +12556,7 @@
         <v/>
       </c>
       <c r="M96" s="27">
-        <f>IF(D96&lt;=0,0,I96/D96)</f>
+        <f>IF(OR(C96&lt;0.05,D96&lt;0.05),"",I96/D96)</f>
         <v/>
       </c>
     </row>
@@ -12600,7 +12609,7 @@
         <v/>
       </c>
       <c r="M97" s="27">
-        <f>IF(D97&lt;=0,0,I97/D97)</f>
+        <f>IF(OR(C97&lt;0.05,D97&lt;0.05),"",I97/D97)</f>
         <v/>
       </c>
     </row>
@@ -12653,7 +12662,7 @@
         <v/>
       </c>
       <c r="M98" s="27">
-        <f>IF(D98&lt;=0,0,I98/D98)</f>
+        <f>IF(OR(C98&lt;0.05,D98&lt;0.05),"",I98/D98)</f>
         <v/>
       </c>
     </row>
@@ -12706,7 +12715,7 @@
         <v/>
       </c>
       <c r="M99" s="27">
-        <f>IF(D99&lt;=0,0,I99/D99)</f>
+        <f>IF(OR(C99&lt;0.05,D99&lt;0.05),"",I99/D99)</f>
         <v/>
       </c>
     </row>
@@ -12759,7 +12768,7 @@
         <v/>
       </c>
       <c r="M100" s="27">
-        <f>IF(D100&lt;=0,0,I100/D100)</f>
+        <f>IF(OR(C100&lt;0.05,D100&lt;0.05),"",I100/D100)</f>
         <v/>
       </c>
     </row>
@@ -12812,7 +12821,7 @@
         <v/>
       </c>
       <c r="M101" s="27">
-        <f>IF(D101&lt;=0,0,I101/D101)</f>
+        <f>IF(OR(C101&lt;0.05,D101&lt;0.05),"",I101/D101)</f>
         <v/>
       </c>
     </row>
@@ -12865,7 +12874,7 @@
         <v/>
       </c>
       <c r="M102" s="27">
-        <f>IF(D102&lt;=0,0,I102/D102)</f>
+        <f>IF(OR(C102&lt;0.05,D102&lt;0.05),"",I102/D102)</f>
         <v/>
       </c>
     </row>
@@ -12918,7 +12927,7 @@
         <v/>
       </c>
       <c r="M103" s="27">
-        <f>IF(D103&lt;=0,0,I103/D103)</f>
+        <f>IF(OR(C103&lt;0.05,D103&lt;0.05),"",I103/D103)</f>
         <v/>
       </c>
     </row>
@@ -12971,7 +12980,7 @@
         <v/>
       </c>
       <c r="M104" s="27">
-        <f>IF(D104&lt;=0,0,I104/D104)</f>
+        <f>IF(OR(C104&lt;0.05,D104&lt;0.05),"",I104/D104)</f>
         <v/>
       </c>
     </row>
@@ -13024,7 +13033,7 @@
         <v/>
       </c>
       <c r="M105" s="27">
-        <f>IF(D105&lt;=0,0,I105/D105)</f>
+        <f>IF(OR(C105&lt;0.05,D105&lt;0.05),"",I105/D105)</f>
         <v/>
       </c>
     </row>
@@ -13077,7 +13086,7 @@
         <v/>
       </c>
       <c r="M106" s="27">
-        <f>IF(D106&lt;=0,0,I106/D106)</f>
+        <f>IF(OR(C106&lt;0.05,D106&lt;0.05),"",I106/D106)</f>
         <v/>
       </c>
     </row>
@@ -13130,7 +13139,7 @@
         <v/>
       </c>
       <c r="M107" s="27">
-        <f>IF(D107&lt;=0,0,I107/D107)</f>
+        <f>IF(OR(C107&lt;0.05,D107&lt;0.05),"",I107/D107)</f>
         <v/>
       </c>
     </row>
@@ -13235,7 +13244,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V_eq_Ø900 = Qout_total/A_plein Ø900 (indicatif; si overflow, une partie du débit n'est pas dans le tuyau)</t>
+          <t>V_pipe_seul = Qout/A_plein Ø900 seulement si WSE≤crest (pas d'overflow). Si Overflow=oui → cellule vide: lire V_Ø900 et V_overflow sur Compose_900 (ne pas diviser Qout total par A_tuyau).</t>
         </is>
       </c>
     </row>
@@ -13277,7 +13286,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>V_eq_Ø900 (m/s)</t>
+          <t>V_pipe_seul (m/s)</t>
         </is>
       </c>
     </row>
@@ -13310,7 +13319,7 @@
         </is>
       </c>
       <c r="H12" s="27">
-        <f>IF(Parametres!$C$87&lt;=0,0,D12/Parametres!$C$87)</f>
+        <f>IF(OR(Parametres!$C$87&lt;=0,C12&gt;$B$6),"",D12/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -13344,7 +13353,7 @@
         <v/>
       </c>
       <c r="H13" s="27">
-        <f>IF(Parametres!$C$87&lt;=0,0,D13/Parametres!$C$87)</f>
+        <f>IF(OR(Parametres!$C$87&lt;=0,C13&gt;$B$6),"",D13/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -13378,7 +13387,7 @@
         <v/>
       </c>
       <c r="H14" s="27">
-        <f>IF(Parametres!$C$87&lt;=0,0,D14/Parametres!$C$87)</f>
+        <f>IF(OR(Parametres!$C$87&lt;=0,C14&gt;$B$6),"",D14/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -13412,7 +13421,7 @@
         <v/>
       </c>
       <c r="H15" s="27">
-        <f>IF(Parametres!$C$87&lt;=0,0,D15/Parametres!$C$87)</f>
+        <f>IF(OR(Parametres!$C$87&lt;=0,C15&gt;$B$6),"",D15/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -13446,7 +13455,7 @@
         <v/>
       </c>
       <c r="H16" s="27">
-        <f>IF(Parametres!$C$87&lt;=0,0,D16/Parametres!$C$87)</f>
+        <f>IF(OR(Parametres!$C$87&lt;=0,C16&gt;$B$6),"",D16/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -13480,7 +13489,7 @@
         <v/>
       </c>
       <c r="H17" s="27">
-        <f>IF(Parametres!$C$87&lt;=0,0,D17/Parametres!$C$87)</f>
+        <f>IF(OR(Parametres!$C$87&lt;=0,C17&gt;$B$6),"",D17/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -13514,7 +13523,7 @@
         <v/>
       </c>
       <c r="H18" s="27">
-        <f>IF(Parametres!$C$87&lt;=0,0,D18/Parametres!$C$87)</f>
+        <f>IF(OR(Parametres!$C$87&lt;=0,C18&gt;$B$6),"",D18/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -13548,7 +13557,7 @@
         <v/>
       </c>
       <c r="H19" s="27">
-        <f>IF(Parametres!$C$87&lt;=0,0,D19/Parametres!$C$87)</f>
+        <f>IF(OR(Parametres!$C$87&lt;=0,C19&gt;$B$6),"",D19/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -13582,7 +13591,7 @@
         <v/>
       </c>
       <c r="H20" s="27">
-        <f>IF(Parametres!$C$87&lt;=0,0,D20/Parametres!$C$87)</f>
+        <f>IF(OR(Parametres!$C$87&lt;=0,C20&gt;$B$6),"",D20/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -13616,7 +13625,7 @@
         <v/>
       </c>
       <c r="H21" s="27">
-        <f>IF(Parametres!$C$87&lt;=0,0,D21/Parametres!$C$87)</f>
+        <f>IF(OR(Parametres!$C$87&lt;=0,C21&gt;$B$6),"",D21/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -13650,7 +13659,7 @@
         <v/>
       </c>
       <c r="H22" s="27">
-        <f>IF(Parametres!$C$87&lt;=0,0,D22/Parametres!$C$87)</f>
+        <f>IF(OR(Parametres!$C$87&lt;=0,C22&gt;$B$6),"",D22/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -13684,7 +13693,7 @@
         <v/>
       </c>
       <c r="H23" s="27">
-        <f>IF(Parametres!$C$87&lt;=0,0,D23/Parametres!$C$87)</f>
+        <f>IF(OR(Parametres!$C$87&lt;=0,C23&gt;$B$6),"",D23/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>
@@ -13718,7 +13727,7 @@
         <v/>
       </c>
       <c r="H24" s="27">
-        <f>IF(Parametres!$C$87&lt;=0,0,D24/Parametres!$C$87)</f>
+        <f>IF(OR(Parametres!$C$87&lt;=0,C24&gt;$B$6),"",D24/Parametres!$C$87)</f>
         <v/>
       </c>
     </row>

--- a/engineering/drainage-design/retention_volume/Volume_Retention_Deux_Zones_1500_900_1200.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Deux_Zones_1500_900_1200.xlsx
@@ -1830,7 +1830,7 @@
         <v>0.008489634748272452</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>1.668</v>
+        <v>0.986</v>
       </c>
     </row>
     <row r="7">
@@ -1874,7 +1874,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Capacité Ø900 — Manning pleine section (n = 0,013)</t>
+          <t>Capacité Ø900 — Manning pleine section (TOG n = 0,022)</t>
         </is>
       </c>
     </row>
@@ -1885,11 +1885,11 @@
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>0.013</v>
+        <v>0.022</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fourni (béton typique ~0,012–0,015)</t>
+          <t>TOG (tuyau ondulé galvanisé) n=0,022 — pas béton</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>• Méthode A: Qout fixe = Q_plein Manning Ø900 (n=0,013).</t>
+          <t>• Méthode A: Qout fixe = Q_plein Manning Ø900 (TOG n=0,022).</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   A) Q_plein Manning (n=0.013) ≈ 1.668 m³/s → Méthode A (constant).</t>
+          <t xml:space="preserve">   A) Q_plein Manning (TOG n=0.022) ≈ 0.986 m³/s → Méthode A (constant).</t>
         </is>
       </c>
     </row>
@@ -5115,11 +5115,11 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>0.013</v>
+        <v>0.022</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>béton typ. 0.012–0.015</t>
+          <t>TOG n=0,022 (ondulé galvanisé)</t>
         </is>
       </c>
       <c r="E6" s="37" t="inlineStr">
